--- a/BaseTraining/unit13_protocall.bus.controller_driver/unit13_protocall.bus.controller_driver.xlsx
+++ b/BaseTraining/unit13_protocall.bus.controller_driver/unit13_protocall.bus.controller_driver.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685500D7-F8C4-4EDF-90B2-F239BAE99963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14283197-0FEF-4E1F-ABA6-9A1752FFBB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Các loại driver" sheetId="3" r:id="rId1"/>
     <sheet name="Các hàm đăng ký" sheetId="1" r:id="rId2"/>
-    <sheet name="Controller_driver share API" sheetId="4" r:id="rId3"/>
-    <sheet name="protocal_driver" sheetId="2" r:id="rId4"/>
-    <sheet name="debug controller driver" sheetId="5" r:id="rId5"/>
+    <sheet name="Controller vs protocall" sheetId="5" r:id="rId3"/>
+    <sheet name="Controller_driver share API" sheetId="4" r:id="rId4"/>
+    <sheet name="protocal_driver" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="458">
   <si>
     <t>1. Đọc document trong linux kernel</t>
   </si>
@@ -2494,13 +2494,3286 @@
   </si>
   <si>
     <t>sau đó define các hàm probe đúng theo file.h kernel sẽ tự lấy tham số khi gọi hàm probe giúp bạn</t>
+  </si>
+  <si>
+    <t>Loại bus</t>
+  </si>
+  <si>
+    <t>Controller Driver (tạo/tổ chức bus)</t>
+  </si>
+  <si>
+    <t>Ví dụ phần cứng (SoC / IP block)</t>
+  </si>
+  <si>
+    <t>Protocol Driver (thiết bị sử dụng bus)</t>
+  </si>
+  <si>
+    <t>Ví dụ thiết bị thực tế</t>
+  </si>
+  <si>
+    <t>UART</t>
+  </si>
+  <si>
+    <r>
+      <t>8250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>omap_uart</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>meson_uart</t>
+    </r>
+  </si>
+  <si>
+    <t>16550, 8250, OMAP UART, PL011 UART</t>
+  </si>
+  <si>
+    <t>(thường không có protocol driver)</t>
+  </si>
+  <si>
+    <t>GPS module, modem, debug console</t>
+  </si>
+  <si>
+    <r>
+      <t>omap_i2c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i2c-imx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i2c-bcm2835</t>
+    </r>
+  </si>
+  <si>
+    <t>AM335x I2C, i.MX I2C, BCM2835 I2C</t>
+  </si>
+  <si>
+    <r>
+      <t>at24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tmp102</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tps65910</t>
+    </r>
+  </si>
+  <si>
+    <t>EEPROM AT24C, TMP102 sensor, PMIC</t>
+  </si>
+  <si>
+    <r>
+      <t>spi-omap2-mcspi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>spi-pl022</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>spi-imx</t>
+    </r>
+  </si>
+  <si>
+    <t>OMAP McSPI, PL022, i.MX SPI</t>
+  </si>
+  <si>
+    <r>
+      <t>spidev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mcp3008</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>w25q32</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC MCP3008, SPI Flash W25Q32</t>
+  </si>
+  <si>
+    <r>
+      <t>ehci-hcd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ohci-hcd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>xhci-hcd</t>
+    </r>
+  </si>
+  <si>
+    <t>USB EHCI/XHCI/OHCI controller (x86, ARM)</t>
+  </si>
+  <si>
+    <r>
+      <t>uvcvideo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cdc_ether</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>usbhid</t>
+    </r>
+  </si>
+  <si>
+    <t>USB webcam, USB LAN, USB mouse</t>
+  </si>
+  <si>
+    <t>MMC/SD</t>
+  </si>
+  <si>
+    <r>
+      <t>sdhci</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>omap_hsmmc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dw_mmc</t>
+    </r>
+  </si>
+  <si>
+    <t>eMMC/SD controller IP</t>
+  </si>
+  <si>
+    <r>
+      <t>mmc_block</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mmc_spi</t>
+    </r>
+  </si>
+  <si>
+    <t>SD card, eMMC chip</t>
+  </si>
+  <si>
+    <r>
+      <t>pci_host_generic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pcie-designware</t>
+    </r>
+  </si>
+  <si>
+    <t>PCI host controller (x86, ARM64 SoC)</t>
+  </si>
+  <si>
+    <r>
+      <t>e1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtl8169</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>nvme</t>
+    </r>
+  </si>
+  <si>
+    <t>NIC card, NVMe SSD, VGA card</t>
+  </si>
+  <si>
+    <t>I2S</t>
+  </si>
+  <si>
+    <r>
+      <t>soc-dai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> driver (tùy SoC)</t>
+    </r>
+  </si>
+  <si>
+    <t>I2S controller (TI, Rockchip, NXP...)</t>
+  </si>
+  <si>
+    <r>
+      <t>sgtl5000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>wm8960</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>adau1977</t>
+    </r>
+  </si>
+  <si>
+    <t>Audio CODEC IC</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <r>
+      <t>ti_hecc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>flexcan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mcp251x</t>
+    </r>
+  </si>
+  <si>
+    <t>CAN controller on SoC or external</t>
+  </si>
+  <si>
+    <r>
+      <t>can-dev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gs_usb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>slcan</t>
+    </r>
+  </si>
+  <si>
+    <t>CAN transceiver, USB-CAN adapters</t>
+  </si>
+  <si>
+    <t>GPIO</t>
+  </si>
+  <si>
+    <r>
+      <t>gpio-omap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gpio-pl061</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gpio-mxc</t>
+    </r>
+  </si>
+  <si>
+    <t>SoC GPIO controller</t>
+  </si>
+  <si>
+    <r>
+      <t>gpio-keys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>leds-gpio</t>
+    </r>
+  </si>
+  <si>
+    <t>Button matrix, LED, etc.</t>
+  </si>
+  <si>
+    <t>PWM</t>
+  </si>
+  <si>
+    <r>
+      <t>pwm-omap-dmtimer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pwm-imx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pwm-rockchip</t>
+    </r>
+  </si>
+  <si>
+    <t>SoC PWM controller</t>
+  </si>
+  <si>
+    <r>
+      <t>pwm-fan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>leds-pwm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, etc.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quạt, LED điều khiển độ sáng</t>
+  </si>
+  <si>
+    <t>ADC</t>
+  </si>
+  <si>
+    <r>
+      <t>ti-adc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>imx27-adc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>stm32-adc</t>
+    </r>
+  </si>
+  <si>
+    <t>On-chip ADC controller</t>
+  </si>
+  <si>
+    <r>
+      <t>iio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> devices (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ina219</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ads1015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Cảm biến điện áp/dòng I2C/SPI/ADC</t>
+  </si>
+  <si>
+    <t>🔎 Ghi chú:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Với </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UART</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, do thiết bị UART thường chỉ là ống truyền dữ liệu, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>protocol driver hiếm khi cần</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, user-space tự nói chuyện với thiết bị.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Với </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I2C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>USB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: thiết bị gắn vào thường là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IC chuyên dụng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc thiết bị cắm ngoài, nên </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>protocol driver là bắt buộc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Với </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GPIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PWM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ADC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: protocol driver thường được gom theo nhóm lớn như </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hwmon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iio</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>leds</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, v.v.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Controller driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (còn gọi là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>host driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adapter driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bus driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) → điều khiển phần cứng tạo ra bus (ví dụ như UART controller, I2C controller, SPI controller...).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Protocol driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (còn gọi là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>client driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>device driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) → điều khiển </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thiết bị ngoại vi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sử dụng giao tiếp qua loại bus đó.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dưới đây là phiên bản mô tả lại ý hiểu của bạn một cách </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chính xác, rõ ràng và sát với kiến trúc thật của Linux kernel driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>🧠 Ý Hiểu Chính Xác Về Kiến Trúc Driver Trong Linux Kernel</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kiến trúc driver trong Linux được chia thành </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nhiều tầng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, mỗi tầng đảm nhận một vai trò cụ thể nhằm đảm bảo tính </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>modular</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>portable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reusable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Cụ thể:</t>
+    </r>
+  </si>
+  <si>
+    <t>🧩 Tầng 1: Bus Controller Drivers</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đây là các </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>driver điều khiển phần cứng controller/host</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quản lý các loại bus như UART, I2C, SPI.</t>
+    </r>
+  </si>
+  <si>
+    <t>Chúng chịu trách nhiệm:</t>
+  </si>
+  <si>
+    <t>Khởi tạo controller</t>
+  </si>
+  <si>
+    <t>Điều khiển truyền nhận dữ liệu</t>
+  </si>
+  <si>
+    <t>Cung cấp các callback/hook cho core sử dụng</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thường được viết dưới dạng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>platform driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nếu controller tích hợp trên SoC (on-chip).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ví dụ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">UART: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>8250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pl011</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I2C: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>designware-i2c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>imx-i2c</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SPI: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dw-spi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pl022</t>
+    </r>
+  </si>
+  <si>
+    <t>🧠 Tầng 2: Subsystem Core Layer</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>phần cốt lõi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của từng subsystem (UART/I2C/SPI) – chứa logic chung.</t>
+    </r>
+  </si>
+  <si>
+    <t>Nhiệm vụ:</t>
+  </si>
+  <si>
+    <t>Quản lý danh sách controller drivers và device drivers</t>
+  </si>
+  <si>
+    <t>Quét và match device ↔ driver</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cung cấp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>APIs chuẩn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho device drivers sử dụng để giao tiếp với controller</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(Tùy subsystem)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Có thể tạo các node </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/dev/...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc đăng ký vào các subsystem khác như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>hwmon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>...</t>
+    </r>
+  </si>
+  <si>
+    <t>🔌 Tầng 3: Device Drivers</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tương ứng với </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>các thiết bị ngoại vi cụ thể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kết nối qua bus (I2C/SPI/UART).</t>
+    </r>
+  </si>
+  <si>
+    <t>Mỗi device driver sử dụng APIs do core cung cấp để:</t>
+  </si>
+  <si>
+    <t>Gửi/nhận dữ liệu thông qua controller</t>
+  </si>
+  <si>
+    <t>Tùy subsystem, có thể:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tạo node </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/dev/...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để giao tiếp với userspace</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hoặc đăng ký vào subsystem như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>input</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>hwmon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>net</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>block</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>…</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I2C: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtc-ds1307</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tmp102</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>eeprom</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SPI: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>spidev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>oled display</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>adc</t>
+    </r>
+  </si>
+  <si>
+    <t>UART: ít device driver riêng, chủ yếu dùng qua TTY layer</t>
+  </si>
+  <si>
+    <t>👤 Tầng 4: Giao diện Userspace</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Giao diện mà </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user application</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> có thể truy cập bằng các lệnh như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>open()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>read()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>write()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ioctl()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ứng dụng giao tiếp qua:</t>
+  </si>
+  <si>
+    <r>
+      <t>/dev/...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: khi device tạo character/block device</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/sys/...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: khi thiết bị chỉ xuất hiện dưới dạng attribute</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nhờ tầng core và driver, ứng dụng có thể hoạt động </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mà không cần biết controller cụ thể là gì</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>🔁 Luồng hoạt động tổng quát:</t>
+  </si>
+  <si>
+    <t>[User App]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ↓ system calls (open, read...)</t>
+  </si>
+  <si>
+    <t>[/dev/ttyS0 or /dev/i2c-1 or /sys/...]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ↓</t>
+  </si>
+  <si>
+    <t>[Core Layer (i2c-core.c, uart-core.c...)]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ↓       ↓</t>
+  </si>
+  <si>
+    <t>[Controller Driver]   [Device Driver]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   (pl011)               (ds1307)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ↓                       ↓</t>
+  </si>
+  <si>
+    <t>[Hardware controller]    [Peripheral Device]</t>
+  </si>
+  <si>
+    <t>✅ Tóm tắt lại ý hiểu của bạn:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bạn đã hiểu rất đúng cách mà </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linux kernel tách biệt phần điều khiển controller (host)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>phần điều khiển thiết bị (device)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, qua một tầng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>core trung gian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Việc tạo ra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/dev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, xử lý </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>system calls</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, match driver/device và cung cấp APIs là nhiệm vụ của tầng core. Nhờ vậy, các device driver có thể hoạt động được với nhiều loại controller khác nhau, và người dùng không cần quan tâm đến phần cứng cụ thể phía dưới.</t>
+    </r>
+  </si>
+  <si>
+    <t>Nếu bạn cần, mình có thể tiếp tục:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Giải thích rõ cách hoạt động của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>platform bus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>device tree</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, hay </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ACPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi binding driver ↔ device</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Phân tích cụ thể hơn các ví dụ như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtc-ds1307</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>spidev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, hay </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>8250</t>
+    </r>
+  </si>
+  <si>
+    <t>Hoặc hướng dẫn bạn tự viết một driver đơn giản</t>
+  </si>
+  <si>
+    <t>Bạn muốn đi tiếp hướng nào?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Core layer trong Linux driver architecture là nơi chứa </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>logic trung gian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> giữa controller drivers và device drivers — nó </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không tương tác trực tiếp với phần cứng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, nhưng cung cấp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>API chuẩn, cơ chế đăng ký/match, quản lý device, tạo sysfs/dev entries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, v.v.</t>
+    </r>
+  </si>
+  <si>
+    <t>📂 Các file trong Core Layer thường có các đặc điểm:</t>
+  </si>
+  <si>
+    <r>
+      <t>Nằm trong thư mục subsystem tương ứng (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>drivers/i2c/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>drivers/spi/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>drivers/tty/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ...)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tên file thường chứa chữ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>core</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, hoặc là một file trung tâm điều phối.</t>
+    </r>
+  </si>
+  <si>
+    <t>Không gắn với phần cứng cụ thể (hardware-agnostic).</t>
+  </si>
+  <si>
+    <t>📚 Danh sách Core Layer file phổ biến theo subsystem</t>
+  </si>
+  <si>
+    <t>🔹 I2C:</t>
+  </si>
+  <si>
+    <t>drivers/i2c/i2c-core-base.c</t>
+  </si>
+  <si>
+    <t>drivers/i2c/i2c-core-of.c</t>
+  </si>
+  <si>
+    <t>drivers/i2c/i2c-core-smbus.c</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⤷ Chứa API như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i2c_add_adapter()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i2c_add_driver()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i2c_transfer()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>of_i2c_register_devices()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>...</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 SPI:</t>
+  </si>
+  <si>
+    <t>drivers/spi/spi.c</t>
+  </si>
+  <si>
+    <t>drivers/spi/spi-master.c</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⤷ Chứa các API như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>spi_register_driver()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>spi_sync()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>spi_new_device()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>...</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 UART / Serial:</t>
+  </si>
+  <si>
+    <t>drivers/tty/serial/serial_core.c</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⤷ Cung cấp API chuẩn như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>uart_register_driver()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>uart_write()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>uart_tx()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>drivers/tty/tty_io.c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tty_core.c</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⤷ Cốt lõi của TTY subsystem, quản lý </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/dev/tty*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, xử lý input/output</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 Input subsystem (cho các driver bàn phím, touch, button...):</t>
+  </si>
+  <si>
+    <t>drivers/input/input.c</t>
+  </si>
+  <si>
+    <r>
+      <t>drivers/input/evdev.c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tạo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/dev/input/eventX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 RTC:</t>
+  </si>
+  <si>
+    <t>drivers/rtc/rtc-core.c</t>
+  </si>
+  <si>
+    <t>⤷ Đăng ký thiết bị RTC, quản lý callbacks từ các rtc driver</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⤷ API: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtc_register_device()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtc_read_time()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rtc_set_time()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>...</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 HWMon (sensor nhiệt độ, điện áp...):</t>
+  </si>
+  <si>
+    <t>drivers/hwmon/hwmon.c</t>
+  </si>
+  <si>
+    <t>⤷ API cho driver sensor đăng ký</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⤷ Tạo file trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/sys/class/hwmon/...</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 Block (cho MMC, SD, USB mass storage...):</t>
+  </si>
+  <si>
+    <r>
+      <t>drivers/block/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nhiều file core như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>genhd.c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>partitions/core.c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Các subsystem như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>drivers/mmc/core/mmc_core.c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cũng là core layer</t>
+    </r>
+  </si>
+  <si>
+    <t>✅ Nhận diện Core Layer:</t>
+  </si>
+  <si>
+    <t>Bạn có thể xem code và nếu thấy các hàm như:</t>
+  </si>
+  <si>
+    <r>
+      <t>*_register_driver()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>*_add_driver()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>device_register()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bus_register()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sysfs_create_*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dev_set_drvdata()</t>
+    </r>
+  </si>
+  <si>
+    <t>Thì nhiều khả năng bạn đang nhìn vào phần Core Layer.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu bạn cần danh sách file core tương ứng cho một </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>subsystem cụ thể</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, ví dụ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>USB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PCI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Sound</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Media</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, mình có thể liệt kê chi tiết hơn. Bạn muốn subsystem nào?</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2581,6 +5854,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3035,7 +6316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3198,16 +6479,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3216,24 +6497,46 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3249,37 +6552,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3290,6 +6571,67 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4415,72 +7757,72 @@
     </row>
     <row r="11" spans="1:82" ht="15" thickBot="1"/>
     <row r="12" spans="1:82" ht="15">
-      <c r="D12" s="120" t="s">
+      <c r="D12" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="108"/>
-      <c r="F12" s="108"/>
-      <c r="G12" s="108"/>
-      <c r="H12" s="108"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108" t="s">
+      <c r="E12" s="106"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="108"/>
-      <c r="N12" s="108"/>
-      <c r="O12" s="108"/>
-      <c r="P12" s="108"/>
-      <c r="Q12" s="108"/>
-      <c r="R12" s="108"/>
-      <c r="S12" s="108"/>
-      <c r="T12" s="108"/>
-      <c r="U12" s="108"/>
-      <c r="V12" s="108"/>
-      <c r="W12" s="108"/>
-      <c r="X12" s="108"/>
-      <c r="Y12" s="108"/>
-      <c r="Z12" s="108"/>
-      <c r="AA12" s="108"/>
-      <c r="AB12" s="108"/>
-      <c r="AC12" s="108"/>
-      <c r="AD12" s="108"/>
-      <c r="AE12" s="108"/>
-      <c r="AF12" s="108"/>
-      <c r="AG12" s="108"/>
-      <c r="AH12" s="108" t="s">
+      <c r="M12" s="106"/>
+      <c r="N12" s="106"/>
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
+      <c r="R12" s="106"/>
+      <c r="S12" s="106"/>
+      <c r="T12" s="106"/>
+      <c r="U12" s="106"/>
+      <c r="V12" s="106"/>
+      <c r="W12" s="106"/>
+      <c r="X12" s="106"/>
+      <c r="Y12" s="106"/>
+      <c r="Z12" s="106"/>
+      <c r="AA12" s="106"/>
+      <c r="AB12" s="106"/>
+      <c r="AC12" s="106"/>
+      <c r="AD12" s="106"/>
+      <c r="AE12" s="106"/>
+      <c r="AF12" s="106"/>
+      <c r="AG12" s="106"/>
+      <c r="AH12" s="106" t="s">
         <v>208</v>
       </c>
-      <c r="AI12" s="108"/>
-      <c r="AJ12" s="108"/>
-      <c r="AK12" s="108"/>
-      <c r="AL12" s="108"/>
-      <c r="AM12" s="108"/>
-      <c r="AN12" s="108"/>
-      <c r="AO12" s="108"/>
-      <c r="AP12" s="108"/>
-      <c r="AQ12" s="108"/>
-      <c r="AR12" s="108"/>
-      <c r="AS12" s="108"/>
-      <c r="AT12" s="108"/>
-      <c r="AU12" s="108"/>
-      <c r="AV12" s="108"/>
-      <c r="AW12" s="108"/>
-      <c r="AX12" s="108"/>
-      <c r="AY12" s="108"/>
-      <c r="AZ12" s="121" t="s">
+      <c r="AI12" s="106"/>
+      <c r="AJ12" s="106"/>
+      <c r="AK12" s="106"/>
+      <c r="AL12" s="106"/>
+      <c r="AM12" s="106"/>
+      <c r="AN12" s="106"/>
+      <c r="AO12" s="106"/>
+      <c r="AP12" s="106"/>
+      <c r="AQ12" s="106"/>
+      <c r="AR12" s="106"/>
+      <c r="AS12" s="106"/>
+      <c r="AT12" s="106"/>
+      <c r="AU12" s="106"/>
+      <c r="AV12" s="106"/>
+      <c r="AW12" s="106"/>
+      <c r="AX12" s="106"/>
+      <c r="AY12" s="106"/>
+      <c r="AZ12" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="BA12" s="121"/>
-      <c r="BB12" s="121"/>
-      <c r="BC12" s="121"/>
-      <c r="BD12" s="121"/>
-      <c r="BE12" s="121"/>
-      <c r="BF12" s="121"/>
-      <c r="BG12" s="121"/>
-      <c r="BH12" s="121"/>
-      <c r="BI12" s="122"/>
+      <c r="BA12" s="127"/>
+      <c r="BB12" s="127"/>
+      <c r="BC12" s="127"/>
+      <c r="BD12" s="127"/>
+      <c r="BE12" s="127"/>
+      <c r="BF12" s="127"/>
+      <c r="BG12" s="127"/>
+      <c r="BH12" s="127"/>
+      <c r="BI12" s="128"/>
     </row>
     <row r="13" spans="1:82" ht="29.45" customHeight="1">
       <c r="D13" s="110" t="s">
@@ -4493,62 +7835,62 @@
       <c r="I13" s="111"/>
       <c r="J13" s="111"/>
       <c r="K13" s="111"/>
-      <c r="L13" s="109" t="s">
+      <c r="L13" s="115" t="s">
         <v>205</v>
       </c>
-      <c r="M13" s="109"/>
-      <c r="N13" s="109"/>
-      <c r="O13" s="109"/>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="109"/>
-      <c r="R13" s="109"/>
-      <c r="S13" s="109"/>
-      <c r="T13" s="109"/>
-      <c r="U13" s="109"/>
-      <c r="V13" s="109"/>
-      <c r="W13" s="109"/>
-      <c r="X13" s="109"/>
-      <c r="Y13" s="109"/>
-      <c r="Z13" s="109"/>
-      <c r="AA13" s="109"/>
-      <c r="AB13" s="109"/>
-      <c r="AC13" s="109"/>
-      <c r="AD13" s="109"/>
-      <c r="AE13" s="109"/>
-      <c r="AF13" s="109"/>
-      <c r="AG13" s="109"/>
-      <c r="AH13" s="137" t="s">
+      <c r="M13" s="115"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="115"/>
+      <c r="P13" s="115"/>
+      <c r="Q13" s="115"/>
+      <c r="R13" s="115"/>
+      <c r="S13" s="115"/>
+      <c r="T13" s="115"/>
+      <c r="U13" s="115"/>
+      <c r="V13" s="115"/>
+      <c r="W13" s="115"/>
+      <c r="X13" s="115"/>
+      <c r="Y13" s="115"/>
+      <c r="Z13" s="115"/>
+      <c r="AA13" s="115"/>
+      <c r="AB13" s="115"/>
+      <c r="AC13" s="115"/>
+      <c r="AD13" s="115"/>
+      <c r="AE13" s="115"/>
+      <c r="AF13" s="115"/>
+      <c r="AG13" s="115"/>
+      <c r="AH13" s="113" t="s">
         <v>210</v>
       </c>
-      <c r="AI13" s="137"/>
-      <c r="AJ13" s="137"/>
-      <c r="AK13" s="137"/>
-      <c r="AL13" s="137"/>
-      <c r="AM13" s="137"/>
-      <c r="AN13" s="137"/>
-      <c r="AO13" s="137"/>
-      <c r="AP13" s="137"/>
-      <c r="AQ13" s="137"/>
-      <c r="AR13" s="137"/>
-      <c r="AS13" s="137"/>
-      <c r="AT13" s="137"/>
-      <c r="AU13" s="137"/>
-      <c r="AV13" s="137"/>
-      <c r="AW13" s="137"/>
-      <c r="AX13" s="137"/>
-      <c r="AY13" s="137"/>
-      <c r="AZ13" s="123" t="s">
+      <c r="AI13" s="113"/>
+      <c r="AJ13" s="113"/>
+      <c r="AK13" s="113"/>
+      <c r="AL13" s="113"/>
+      <c r="AM13" s="113"/>
+      <c r="AN13" s="113"/>
+      <c r="AO13" s="113"/>
+      <c r="AP13" s="113"/>
+      <c r="AQ13" s="113"/>
+      <c r="AR13" s="113"/>
+      <c r="AS13" s="113"/>
+      <c r="AT13" s="113"/>
+      <c r="AU13" s="113"/>
+      <c r="AV13" s="113"/>
+      <c r="AW13" s="113"/>
+      <c r="AX13" s="113"/>
+      <c r="AY13" s="113"/>
+      <c r="AZ13" s="129" t="s">
         <v>43</v>
       </c>
-      <c r="BA13" s="123"/>
-      <c r="BB13" s="123"/>
-      <c r="BC13" s="123"/>
-      <c r="BD13" s="123"/>
-      <c r="BE13" s="123"/>
-      <c r="BF13" s="123"/>
-      <c r="BG13" s="123"/>
-      <c r="BH13" s="123"/>
-      <c r="BI13" s="124"/>
+      <c r="BA13" s="129"/>
+      <c r="BB13" s="129"/>
+      <c r="BC13" s="129"/>
+      <c r="BD13" s="129"/>
+      <c r="BE13" s="129"/>
+      <c r="BF13" s="129"/>
+      <c r="BG13" s="129"/>
+      <c r="BH13" s="129"/>
+      <c r="BI13" s="130"/>
       <c r="BJ13" s="57" t="s">
         <v>207</v>
       </c>
@@ -4584,62 +7926,62 @@
       <c r="I14" s="111"/>
       <c r="J14" s="111"/>
       <c r="K14" s="111"/>
-      <c r="L14" s="109" t="s">
+      <c r="L14" s="115" t="s">
         <v>219</v>
       </c>
-      <c r="M14" s="109"/>
-      <c r="N14" s="109"/>
-      <c r="O14" s="109"/>
-      <c r="P14" s="109"/>
-      <c r="Q14" s="109"/>
-      <c r="R14" s="109"/>
-      <c r="S14" s="109"/>
-      <c r="T14" s="109"/>
-      <c r="U14" s="109"/>
-      <c r="V14" s="109"/>
-      <c r="W14" s="109"/>
-      <c r="X14" s="109"/>
-      <c r="Y14" s="109"/>
-      <c r="Z14" s="109"/>
-      <c r="AA14" s="109"/>
-      <c r="AB14" s="109"/>
-      <c r="AC14" s="109"/>
-      <c r="AD14" s="109"/>
-      <c r="AE14" s="109"/>
-      <c r="AF14" s="109"/>
-      <c r="AG14" s="109"/>
-      <c r="AH14" s="137" t="s">
+      <c r="M14" s="115"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="115"/>
+      <c r="S14" s="115"/>
+      <c r="T14" s="115"/>
+      <c r="U14" s="115"/>
+      <c r="V14" s="115"/>
+      <c r="W14" s="115"/>
+      <c r="X14" s="115"/>
+      <c r="Y14" s="115"/>
+      <c r="Z14" s="115"/>
+      <c r="AA14" s="115"/>
+      <c r="AB14" s="115"/>
+      <c r="AC14" s="115"/>
+      <c r="AD14" s="115"/>
+      <c r="AE14" s="115"/>
+      <c r="AF14" s="115"/>
+      <c r="AG14" s="115"/>
+      <c r="AH14" s="113" t="s">
         <v>209</v>
       </c>
-      <c r="AI14" s="137"/>
-      <c r="AJ14" s="137"/>
-      <c r="AK14" s="137"/>
-      <c r="AL14" s="137"/>
-      <c r="AM14" s="137"/>
-      <c r="AN14" s="137"/>
-      <c r="AO14" s="137"/>
-      <c r="AP14" s="137"/>
-      <c r="AQ14" s="137"/>
-      <c r="AR14" s="137"/>
-      <c r="AS14" s="137"/>
-      <c r="AT14" s="137"/>
-      <c r="AU14" s="137"/>
-      <c r="AV14" s="137"/>
-      <c r="AW14" s="137"/>
-      <c r="AX14" s="137"/>
-      <c r="AY14" s="137"/>
-      <c r="AZ14" s="123" t="s">
+      <c r="AI14" s="113"/>
+      <c r="AJ14" s="113"/>
+      <c r="AK14" s="113"/>
+      <c r="AL14" s="113"/>
+      <c r="AM14" s="113"/>
+      <c r="AN14" s="113"/>
+      <c r="AO14" s="113"/>
+      <c r="AP14" s="113"/>
+      <c r="AQ14" s="113"/>
+      <c r="AR14" s="113"/>
+      <c r="AS14" s="113"/>
+      <c r="AT14" s="113"/>
+      <c r="AU14" s="113"/>
+      <c r="AV14" s="113"/>
+      <c r="AW14" s="113"/>
+      <c r="AX14" s="113"/>
+      <c r="AY14" s="113"/>
+      <c r="AZ14" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="BA14" s="123"/>
-      <c r="BB14" s="123"/>
-      <c r="BC14" s="123"/>
-      <c r="BD14" s="123"/>
-      <c r="BE14" s="123"/>
-      <c r="BF14" s="123"/>
-      <c r="BG14" s="123"/>
-      <c r="BH14" s="123"/>
-      <c r="BI14" s="124"/>
+      <c r="BA14" s="129"/>
+      <c r="BB14" s="129"/>
+      <c r="BC14" s="129"/>
+      <c r="BD14" s="129"/>
+      <c r="BE14" s="129"/>
+      <c r="BF14" s="129"/>
+      <c r="BG14" s="129"/>
+      <c r="BH14" s="129"/>
+      <c r="BI14" s="130"/>
       <c r="BJ14" s="57" t="s">
         <v>46</v>
       </c>
@@ -4665,72 +8007,72 @@
       <c r="CD14" s="57"/>
     </row>
     <row r="15" spans="1:82" ht="28.9" customHeight="1" thickBot="1">
-      <c r="D15" s="106" t="s">
+      <c r="D15" s="108" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="107"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="107"/>
-      <c r="J15" s="107"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="112" t="s">
+      <c r="E15" s="109"/>
+      <c r="F15" s="109"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="114" t="s">
         <v>206</v>
       </c>
-      <c r="M15" s="112"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="112"/>
-      <c r="P15" s="112"/>
-      <c r="Q15" s="112"/>
-      <c r="R15" s="112"/>
-      <c r="S15" s="112"/>
-      <c r="T15" s="112"/>
-      <c r="U15" s="112"/>
-      <c r="V15" s="112"/>
-      <c r="W15" s="112"/>
-      <c r="X15" s="112"/>
-      <c r="Y15" s="112"/>
-      <c r="Z15" s="112"/>
-      <c r="AA15" s="112"/>
-      <c r="AB15" s="112"/>
-      <c r="AC15" s="112"/>
-      <c r="AD15" s="112"/>
-      <c r="AE15" s="112"/>
-      <c r="AF15" s="112"/>
-      <c r="AG15" s="112"/>
-      <c r="AH15" s="136" t="s">
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="114"/>
+      <c r="V15" s="114"/>
+      <c r="W15" s="114"/>
+      <c r="X15" s="114"/>
+      <c r="Y15" s="114"/>
+      <c r="Z15" s="114"/>
+      <c r="AA15" s="114"/>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="114"/>
+      <c r="AD15" s="114"/>
+      <c r="AE15" s="114"/>
+      <c r="AF15" s="114"/>
+      <c r="AG15" s="114"/>
+      <c r="AH15" s="112" t="s">
         <v>211</v>
       </c>
-      <c r="AI15" s="136"/>
-      <c r="AJ15" s="136"/>
-      <c r="AK15" s="136"/>
-      <c r="AL15" s="136"/>
-      <c r="AM15" s="136"/>
-      <c r="AN15" s="136"/>
-      <c r="AO15" s="136"/>
-      <c r="AP15" s="136"/>
-      <c r="AQ15" s="136"/>
-      <c r="AR15" s="136"/>
-      <c r="AS15" s="136"/>
-      <c r="AT15" s="136"/>
-      <c r="AU15" s="136"/>
-      <c r="AV15" s="136"/>
-      <c r="AW15" s="136"/>
-      <c r="AX15" s="136"/>
-      <c r="AY15" s="136"/>
-      <c r="AZ15" s="125" t="s">
+      <c r="AI15" s="112"/>
+      <c r="AJ15" s="112"/>
+      <c r="AK15" s="112"/>
+      <c r="AL15" s="112"/>
+      <c r="AM15" s="112"/>
+      <c r="AN15" s="112"/>
+      <c r="AO15" s="112"/>
+      <c r="AP15" s="112"/>
+      <c r="AQ15" s="112"/>
+      <c r="AR15" s="112"/>
+      <c r="AS15" s="112"/>
+      <c r="AT15" s="112"/>
+      <c r="AU15" s="112"/>
+      <c r="AV15" s="112"/>
+      <c r="AW15" s="112"/>
+      <c r="AX15" s="112"/>
+      <c r="AY15" s="112"/>
+      <c r="AZ15" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="BA15" s="125"/>
-      <c r="BB15" s="125"/>
-      <c r="BC15" s="125"/>
-      <c r="BD15" s="125"/>
-      <c r="BE15" s="125"/>
-      <c r="BF15" s="125"/>
-      <c r="BG15" s="125"/>
-      <c r="BH15" s="125"/>
-      <c r="BI15" s="126"/>
+      <c r="BA15" s="131"/>
+      <c r="BB15" s="131"/>
+      <c r="BC15" s="131"/>
+      <c r="BD15" s="131"/>
+      <c r="BE15" s="131"/>
+      <c r="BF15" s="131"/>
+      <c r="BG15" s="131"/>
+      <c r="BH15" s="131"/>
+      <c r="BI15" s="132"/>
       <c r="BJ15" s="58" t="s">
         <v>47</v>
       </c>
@@ -4875,130 +8217,130 @@
     </row>
     <row r="26" spans="1:70" ht="15" thickBot="1"/>
     <row r="27" spans="1:70" ht="15">
-      <c r="D27" s="132" t="s">
+      <c r="D27" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="127"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="135" t="s">
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
+      <c r="G27" s="117"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="122" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="135"/>
-      <c r="K27" s="135"/>
-      <c r="L27" s="135"/>
-      <c r="M27" s="135"/>
-      <c r="N27" s="135"/>
-      <c r="O27" s="135"/>
-      <c r="P27" s="135"/>
-      <c r="Q27" s="127" t="s">
+      <c r="J27" s="122"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
+      <c r="M27" s="122"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="122"/>
+      <c r="P27" s="122"/>
+      <c r="Q27" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="R27" s="127"/>
-      <c r="S27" s="127"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="127"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="127"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="127"/>
-      <c r="Z27" s="127"/>
-      <c r="AA27" s="127"/>
-      <c r="AB27" s="127"/>
-      <c r="AC27" s="127"/>
-      <c r="AD27" s="127" t="s">
+      <c r="R27" s="117"/>
+      <c r="S27" s="117"/>
+      <c r="T27" s="117"/>
+      <c r="U27" s="117"/>
+      <c r="V27" s="117"/>
+      <c r="W27" s="117"/>
+      <c r="X27" s="117"/>
+      <c r="Y27" s="117"/>
+      <c r="Z27" s="117"/>
+      <c r="AA27" s="117"/>
+      <c r="AB27" s="117"/>
+      <c r="AC27" s="117"/>
+      <c r="AD27" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="AE27" s="127"/>
-      <c r="AF27" s="127"/>
-      <c r="AG27" s="127"/>
-      <c r="AH27" s="127"/>
-      <c r="AI27" s="127"/>
-      <c r="AJ27" s="127"/>
-      <c r="AK27" s="127"/>
-      <c r="AL27" s="127"/>
-      <c r="AM27" s="127"/>
-      <c r="AN27" s="127"/>
-      <c r="AO27" s="127"/>
-      <c r="AP27" s="127"/>
-      <c r="AQ27" s="121" t="s">
+      <c r="AE27" s="117"/>
+      <c r="AF27" s="117"/>
+      <c r="AG27" s="117"/>
+      <c r="AH27" s="117"/>
+      <c r="AI27" s="117"/>
+      <c r="AJ27" s="117"/>
+      <c r="AK27" s="117"/>
+      <c r="AL27" s="117"/>
+      <c r="AM27" s="117"/>
+      <c r="AN27" s="117"/>
+      <c r="AO27" s="117"/>
+      <c r="AP27" s="117"/>
+      <c r="AQ27" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="AR27" s="121"/>
-      <c r="AS27" s="121"/>
-      <c r="AT27" s="121"/>
-      <c r="AU27" s="121"/>
-      <c r="AV27" s="121"/>
-      <c r="AW27" s="121"/>
-      <c r="AX27" s="121"/>
-      <c r="AY27" s="121"/>
-      <c r="AZ27" s="121"/>
-      <c r="BA27" s="121"/>
-      <c r="BB27" s="122"/>
+      <c r="AR27" s="127"/>
+      <c r="AS27" s="127"/>
+      <c r="AT27" s="127"/>
+      <c r="AU27" s="127"/>
+      <c r="AV27" s="127"/>
+      <c r="AW27" s="127"/>
+      <c r="AX27" s="127"/>
+      <c r="AY27" s="127"/>
+      <c r="AZ27" s="127"/>
+      <c r="BA27" s="127"/>
+      <c r="BB27" s="128"/>
     </row>
     <row r="28" spans="1:70">
-      <c r="D28" s="133" t="s">
+      <c r="D28" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="128"/>
-      <c r="F28" s="128"/>
-      <c r="G28" s="128"/>
-      <c r="H28" s="128"/>
-      <c r="I28" s="130" t="s">
+      <c r="E28" s="119"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="123" t="s">
         <v>29</v>
       </c>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
-      <c r="L28" s="130"/>
-      <c r="M28" s="130"/>
-      <c r="N28" s="130"/>
-      <c r="O28" s="130"/>
-      <c r="P28" s="130"/>
-      <c r="Q28" s="128" t="s">
+      <c r="J28" s="123"/>
+      <c r="K28" s="123"/>
+      <c r="L28" s="123"/>
+      <c r="M28" s="123"/>
+      <c r="N28" s="123"/>
+      <c r="O28" s="123"/>
+      <c r="P28" s="123"/>
+      <c r="Q28" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="R28" s="128"/>
-      <c r="S28" s="128"/>
-      <c r="T28" s="128"/>
-      <c r="U28" s="128"/>
-      <c r="V28" s="128"/>
-      <c r="W28" s="128"/>
-      <c r="X28" s="128"/>
-      <c r="Y28" s="128"/>
-      <c r="Z28" s="128"/>
-      <c r="AA28" s="128"/>
-      <c r="AB28" s="128"/>
-      <c r="AC28" s="128"/>
-      <c r="AD28" s="130" t="s">
+      <c r="R28" s="119"/>
+      <c r="S28" s="119"/>
+      <c r="T28" s="119"/>
+      <c r="U28" s="119"/>
+      <c r="V28" s="119"/>
+      <c r="W28" s="119"/>
+      <c r="X28" s="119"/>
+      <c r="Y28" s="119"/>
+      <c r="Z28" s="119"/>
+      <c r="AA28" s="119"/>
+      <c r="AB28" s="119"/>
+      <c r="AC28" s="119"/>
+      <c r="AD28" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="AE28" s="130"/>
-      <c r="AF28" s="130"/>
-      <c r="AG28" s="130"/>
-      <c r="AH28" s="130"/>
-      <c r="AI28" s="130"/>
-      <c r="AJ28" s="130"/>
-      <c r="AK28" s="130"/>
-      <c r="AL28" s="130"/>
-      <c r="AM28" s="130"/>
-      <c r="AN28" s="130"/>
-      <c r="AO28" s="130"/>
-      <c r="AP28" s="130"/>
-      <c r="AQ28" s="116" t="s">
+      <c r="AE28" s="123"/>
+      <c r="AF28" s="123"/>
+      <c r="AG28" s="123"/>
+      <c r="AH28" s="123"/>
+      <c r="AI28" s="123"/>
+      <c r="AJ28" s="123"/>
+      <c r="AK28" s="123"/>
+      <c r="AL28" s="123"/>
+      <c r="AM28" s="123"/>
+      <c r="AN28" s="123"/>
+      <c r="AO28" s="123"/>
+      <c r="AP28" s="123"/>
+      <c r="AQ28" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="AR28" s="116"/>
-      <c r="AS28" s="116"/>
-      <c r="AT28" s="116"/>
-      <c r="AU28" s="116"/>
-      <c r="AV28" s="116"/>
-      <c r="AW28" s="116"/>
-      <c r="AX28" s="116"/>
-      <c r="AY28" s="116"/>
-      <c r="AZ28" s="116"/>
-      <c r="BA28" s="116"/>
-      <c r="BB28" s="117"/>
+      <c r="AR28" s="124"/>
+      <c r="AS28" s="124"/>
+      <c r="AT28" s="124"/>
+      <c r="AU28" s="124"/>
+      <c r="AV28" s="124"/>
+      <c r="AW28" s="124"/>
+      <c r="AX28" s="124"/>
+      <c r="AY28" s="124"/>
+      <c r="AZ28" s="124"/>
+      <c r="BA28" s="124"/>
+      <c r="BB28" s="125"/>
       <c r="BC28" s="13" t="s">
         <v>48</v>
       </c>
@@ -5019,67 +8361,67 @@
       <c r="BR28" s="13"/>
     </row>
     <row r="29" spans="1:70">
-      <c r="D29" s="133" t="s">
+      <c r="D29" s="118" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="128"/>
-      <c r="I29" s="130" t="s">
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
+      <c r="I29" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="J29" s="130"/>
-      <c r="K29" s="130"/>
-      <c r="L29" s="130"/>
-      <c r="M29" s="130"/>
-      <c r="N29" s="130"/>
-      <c r="O29" s="130"/>
-      <c r="P29" s="130"/>
-      <c r="Q29" s="128" t="s">
+      <c r="J29" s="123"/>
+      <c r="K29" s="123"/>
+      <c r="L29" s="123"/>
+      <c r="M29" s="123"/>
+      <c r="N29" s="123"/>
+      <c r="O29" s="123"/>
+      <c r="P29" s="123"/>
+      <c r="Q29" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="R29" s="128"/>
-      <c r="S29" s="128"/>
-      <c r="T29" s="128"/>
-      <c r="U29" s="128"/>
-      <c r="V29" s="128"/>
-      <c r="W29" s="128"/>
-      <c r="X29" s="128"/>
-      <c r="Y29" s="128"/>
-      <c r="Z29" s="128"/>
-      <c r="AA29" s="128"/>
-      <c r="AB29" s="128"/>
-      <c r="AC29" s="128"/>
-      <c r="AD29" s="130" t="s">
+      <c r="R29" s="119"/>
+      <c r="S29" s="119"/>
+      <c r="T29" s="119"/>
+      <c r="U29" s="119"/>
+      <c r="V29" s="119"/>
+      <c r="W29" s="119"/>
+      <c r="X29" s="119"/>
+      <c r="Y29" s="119"/>
+      <c r="Z29" s="119"/>
+      <c r="AA29" s="119"/>
+      <c r="AB29" s="119"/>
+      <c r="AC29" s="119"/>
+      <c r="AD29" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="AE29" s="130"/>
-      <c r="AF29" s="130"/>
-      <c r="AG29" s="130"/>
-      <c r="AH29" s="130"/>
-      <c r="AI29" s="130"/>
-      <c r="AJ29" s="130"/>
-      <c r="AK29" s="130"/>
-      <c r="AL29" s="130"/>
-      <c r="AM29" s="130"/>
-      <c r="AN29" s="130"/>
-      <c r="AO29" s="130"/>
-      <c r="AP29" s="130"/>
-      <c r="AQ29" s="116" t="s">
+      <c r="AE29" s="123"/>
+      <c r="AF29" s="123"/>
+      <c r="AG29" s="123"/>
+      <c r="AH29" s="123"/>
+      <c r="AI29" s="123"/>
+      <c r="AJ29" s="123"/>
+      <c r="AK29" s="123"/>
+      <c r="AL29" s="123"/>
+      <c r="AM29" s="123"/>
+      <c r="AN29" s="123"/>
+      <c r="AO29" s="123"/>
+      <c r="AP29" s="123"/>
+      <c r="AQ29" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="AR29" s="116"/>
-      <c r="AS29" s="116"/>
-      <c r="AT29" s="116"/>
-      <c r="AU29" s="116"/>
-      <c r="AV29" s="116"/>
-      <c r="AW29" s="116"/>
-      <c r="AX29" s="116"/>
-      <c r="AY29" s="116"/>
-      <c r="AZ29" s="116"/>
-      <c r="BA29" s="116"/>
-      <c r="BB29" s="117"/>
+      <c r="AR29" s="124"/>
+      <c r="AS29" s="124"/>
+      <c r="AT29" s="124"/>
+      <c r="AU29" s="124"/>
+      <c r="AV29" s="124"/>
+      <c r="AW29" s="124"/>
+      <c r="AX29" s="124"/>
+      <c r="AY29" s="124"/>
+      <c r="AZ29" s="124"/>
+      <c r="BA29" s="124"/>
+      <c r="BB29" s="125"/>
       <c r="BC29" s="13" t="s">
         <v>49</v>
       </c>
@@ -5100,67 +8442,67 @@
       <c r="BR29" s="13"/>
     </row>
     <row r="30" spans="1:70" ht="15" thickBot="1">
-      <c r="D30" s="134" t="s">
+      <c r="D30" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="129"/>
-      <c r="F30" s="129"/>
-      <c r="G30" s="129"/>
-      <c r="H30" s="129"/>
-      <c r="I30" s="129" t="s">
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="121"/>
+      <c r="H30" s="121"/>
+      <c r="I30" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="J30" s="129"/>
-      <c r="K30" s="129"/>
-      <c r="L30" s="129"/>
-      <c r="M30" s="129"/>
-      <c r="N30" s="129"/>
-      <c r="O30" s="129"/>
-      <c r="P30" s="129"/>
-      <c r="Q30" s="129" t="s">
+      <c r="J30" s="121"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="R30" s="129"/>
-      <c r="S30" s="129"/>
-      <c r="T30" s="129"/>
-      <c r="U30" s="129"/>
-      <c r="V30" s="129"/>
-      <c r="W30" s="129"/>
-      <c r="X30" s="129"/>
-      <c r="Y30" s="129"/>
-      <c r="Z30" s="129"/>
-      <c r="AA30" s="129"/>
-      <c r="AB30" s="129"/>
-      <c r="AC30" s="129"/>
-      <c r="AD30" s="131" t="s">
+      <c r="R30" s="121"/>
+      <c r="S30" s="121"/>
+      <c r="T30" s="121"/>
+      <c r="U30" s="121"/>
+      <c r="V30" s="121"/>
+      <c r="W30" s="121"/>
+      <c r="X30" s="121"/>
+      <c r="Y30" s="121"/>
+      <c r="Z30" s="121"/>
+      <c r="AA30" s="121"/>
+      <c r="AB30" s="121"/>
+      <c r="AC30" s="121"/>
+      <c r="AD30" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="AE30" s="131"/>
-      <c r="AF30" s="131"/>
-      <c r="AG30" s="131"/>
-      <c r="AH30" s="131"/>
-      <c r="AI30" s="131"/>
-      <c r="AJ30" s="131"/>
-      <c r="AK30" s="131"/>
-      <c r="AL30" s="131"/>
-      <c r="AM30" s="131"/>
-      <c r="AN30" s="131"/>
-      <c r="AO30" s="131"/>
-      <c r="AP30" s="131"/>
-      <c r="AQ30" s="118" t="s">
+      <c r="AE30" s="126"/>
+      <c r="AF30" s="126"/>
+      <c r="AG30" s="126"/>
+      <c r="AH30" s="126"/>
+      <c r="AI30" s="126"/>
+      <c r="AJ30" s="126"/>
+      <c r="AK30" s="126"/>
+      <c r="AL30" s="126"/>
+      <c r="AM30" s="126"/>
+      <c r="AN30" s="126"/>
+      <c r="AO30" s="126"/>
+      <c r="AP30" s="126"/>
+      <c r="AQ30" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="AR30" s="118"/>
-      <c r="AS30" s="118"/>
-      <c r="AT30" s="118"/>
-      <c r="AU30" s="118"/>
-      <c r="AV30" s="118"/>
-      <c r="AW30" s="118"/>
-      <c r="AX30" s="118"/>
-      <c r="AY30" s="118"/>
-      <c r="AZ30" s="118"/>
-      <c r="BA30" s="118"/>
-      <c r="BB30" s="119"/>
+      <c r="AR30" s="133"/>
+      <c r="AS30" s="133"/>
+      <c r="AT30" s="133"/>
+      <c r="AU30" s="133"/>
+      <c r="AV30" s="133"/>
+      <c r="AW30" s="133"/>
+      <c r="AX30" s="133"/>
+      <c r="AY30" s="133"/>
+      <c r="AZ30" s="133"/>
+      <c r="BA30" s="133"/>
+      <c r="BB30" s="134"/>
       <c r="BC30" s="13" t="s">
         <v>50</v>
       </c>
@@ -5189,76 +8531,76 @@
     </row>
     <row r="33" spans="1:68" ht="15" thickBot="1"/>
     <row r="34" spans="1:68" ht="15">
-      <c r="E34" s="120" t="s">
+      <c r="E34" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="108"/>
-      <c r="I34" s="108"/>
-      <c r="J34" s="108"/>
-      <c r="K34" s="108"/>
-      <c r="L34" s="108"/>
-      <c r="M34" s="108"/>
-      <c r="N34" s="108"/>
-      <c r="O34" s="108"/>
-      <c r="P34" s="108"/>
-      <c r="Q34" s="108"/>
-      <c r="R34" s="108" t="s">
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="106"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="106"/>
+      <c r="N34" s="106"/>
+      <c r="O34" s="106"/>
+      <c r="P34" s="106"/>
+      <c r="Q34" s="106"/>
+      <c r="R34" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="S34" s="108"/>
-      <c r="T34" s="108"/>
-      <c r="U34" s="108"/>
-      <c r="V34" s="108"/>
-      <c r="W34" s="108"/>
-      <c r="X34" s="108"/>
-      <c r="Y34" s="108"/>
-      <c r="Z34" s="108"/>
-      <c r="AA34" s="108"/>
-      <c r="AB34" s="108"/>
-      <c r="AC34" s="108"/>
-      <c r="AD34" s="108"/>
-      <c r="AE34" s="108"/>
-      <c r="AF34" s="108"/>
-      <c r="AG34" s="108"/>
-      <c r="AH34" s="108"/>
-      <c r="AI34" s="108"/>
-      <c r="AJ34" s="108"/>
-      <c r="AK34" s="108"/>
-      <c r="AL34" s="108"/>
-      <c r="AM34" s="108"/>
-      <c r="AN34" s="108"/>
-      <c r="AO34" s="108"/>
-      <c r="AP34" s="108" t="s">
+      <c r="S34" s="106"/>
+      <c r="T34" s="106"/>
+      <c r="U34" s="106"/>
+      <c r="V34" s="106"/>
+      <c r="W34" s="106"/>
+      <c r="X34" s="106"/>
+      <c r="Y34" s="106"/>
+      <c r="Z34" s="106"/>
+      <c r="AA34" s="106"/>
+      <c r="AB34" s="106"/>
+      <c r="AC34" s="106"/>
+      <c r="AD34" s="106"/>
+      <c r="AE34" s="106"/>
+      <c r="AF34" s="106"/>
+      <c r="AG34" s="106"/>
+      <c r="AH34" s="106"/>
+      <c r="AI34" s="106"/>
+      <c r="AJ34" s="106"/>
+      <c r="AK34" s="106"/>
+      <c r="AL34" s="106"/>
+      <c r="AM34" s="106"/>
+      <c r="AN34" s="106"/>
+      <c r="AO34" s="106"/>
+      <c r="AP34" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="AQ34" s="108"/>
-      <c r="AR34" s="108"/>
-      <c r="AS34" s="108"/>
-      <c r="AT34" s="108"/>
-      <c r="AU34" s="108"/>
-      <c r="AV34" s="108"/>
-      <c r="AW34" s="108"/>
-      <c r="AX34" s="108"/>
-      <c r="AY34" s="108"/>
-      <c r="AZ34" s="108"/>
-      <c r="BA34" s="108"/>
-      <c r="BB34" s="108"/>
-      <c r="BC34" s="108"/>
-      <c r="BD34" s="108"/>
-      <c r="BE34" s="108"/>
-      <c r="BF34" s="108"/>
-      <c r="BG34" s="108"/>
-      <c r="BH34" s="108"/>
-      <c r="BI34" s="108"/>
-      <c r="BJ34" s="108"/>
-      <c r="BK34" s="108"/>
-      <c r="BL34" s="108"/>
-      <c r="BM34" s="108"/>
-      <c r="BN34" s="108"/>
-      <c r="BO34" s="108"/>
-      <c r="BP34" s="113"/>
+      <c r="AQ34" s="106"/>
+      <c r="AR34" s="106"/>
+      <c r="AS34" s="106"/>
+      <c r="AT34" s="106"/>
+      <c r="AU34" s="106"/>
+      <c r="AV34" s="106"/>
+      <c r="AW34" s="106"/>
+      <c r="AX34" s="106"/>
+      <c r="AY34" s="106"/>
+      <c r="AZ34" s="106"/>
+      <c r="BA34" s="106"/>
+      <c r="BB34" s="106"/>
+      <c r="BC34" s="106"/>
+      <c r="BD34" s="106"/>
+      <c r="BE34" s="106"/>
+      <c r="BF34" s="106"/>
+      <c r="BG34" s="106"/>
+      <c r="BH34" s="106"/>
+      <c r="BI34" s="106"/>
+      <c r="BJ34" s="106"/>
+      <c r="BK34" s="106"/>
+      <c r="BL34" s="106"/>
+      <c r="BM34" s="106"/>
+      <c r="BN34" s="106"/>
+      <c r="BO34" s="106"/>
+      <c r="BP34" s="137"/>
     </row>
     <row r="35" spans="1:68" ht="15">
       <c r="E35" s="110" t="s">
@@ -5276,61 +8618,61 @@
       <c r="O35" s="111"/>
       <c r="P35" s="111"/>
       <c r="Q35" s="111"/>
-      <c r="R35" s="109" t="s">
+      <c r="R35" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="S35" s="109"/>
-      <c r="T35" s="109"/>
-      <c r="U35" s="109"/>
-      <c r="V35" s="109"/>
-      <c r="W35" s="109"/>
-      <c r="X35" s="109"/>
-      <c r="Y35" s="109"/>
-      <c r="Z35" s="109"/>
-      <c r="AA35" s="109"/>
-      <c r="AB35" s="109"/>
-      <c r="AC35" s="109"/>
-      <c r="AD35" s="109"/>
-      <c r="AE35" s="109"/>
-      <c r="AF35" s="109"/>
-      <c r="AG35" s="109"/>
-      <c r="AH35" s="109"/>
-      <c r="AI35" s="109"/>
-      <c r="AJ35" s="109"/>
-      <c r="AK35" s="109"/>
-      <c r="AL35" s="109"/>
-      <c r="AM35" s="109"/>
-      <c r="AN35" s="109"/>
-      <c r="AO35" s="109"/>
-      <c r="AP35" s="109" t="s">
+      <c r="S35" s="115"/>
+      <c r="T35" s="115"/>
+      <c r="U35" s="115"/>
+      <c r="V35" s="115"/>
+      <c r="W35" s="115"/>
+      <c r="X35" s="115"/>
+      <c r="Y35" s="115"/>
+      <c r="Z35" s="115"/>
+      <c r="AA35" s="115"/>
+      <c r="AB35" s="115"/>
+      <c r="AC35" s="115"/>
+      <c r="AD35" s="115"/>
+      <c r="AE35" s="115"/>
+      <c r="AF35" s="115"/>
+      <c r="AG35" s="115"/>
+      <c r="AH35" s="115"/>
+      <c r="AI35" s="115"/>
+      <c r="AJ35" s="115"/>
+      <c r="AK35" s="115"/>
+      <c r="AL35" s="115"/>
+      <c r="AM35" s="115"/>
+      <c r="AN35" s="115"/>
+      <c r="AO35" s="115"/>
+      <c r="AP35" s="115" t="s">
         <v>57</v>
       </c>
-      <c r="AQ35" s="109"/>
-      <c r="AR35" s="109"/>
-      <c r="AS35" s="109"/>
-      <c r="AT35" s="109"/>
-      <c r="AU35" s="109"/>
-      <c r="AV35" s="109"/>
-      <c r="AW35" s="109"/>
-      <c r="AX35" s="109"/>
-      <c r="AY35" s="109"/>
-      <c r="AZ35" s="109"/>
-      <c r="BA35" s="109"/>
-      <c r="BB35" s="109"/>
-      <c r="BC35" s="109"/>
-      <c r="BD35" s="109"/>
-      <c r="BE35" s="109"/>
-      <c r="BF35" s="109"/>
-      <c r="BG35" s="109"/>
-      <c r="BH35" s="109"/>
-      <c r="BI35" s="109"/>
-      <c r="BJ35" s="109"/>
-      <c r="BK35" s="109"/>
-      <c r="BL35" s="109"/>
-      <c r="BM35" s="109"/>
-      <c r="BN35" s="109"/>
-      <c r="BO35" s="109"/>
-      <c r="BP35" s="114"/>
+      <c r="AQ35" s="115"/>
+      <c r="AR35" s="115"/>
+      <c r="AS35" s="115"/>
+      <c r="AT35" s="115"/>
+      <c r="AU35" s="115"/>
+      <c r="AV35" s="115"/>
+      <c r="AW35" s="115"/>
+      <c r="AX35" s="115"/>
+      <c r="AY35" s="115"/>
+      <c r="AZ35" s="115"/>
+      <c r="BA35" s="115"/>
+      <c r="BB35" s="115"/>
+      <c r="BC35" s="115"/>
+      <c r="BD35" s="115"/>
+      <c r="BE35" s="115"/>
+      <c r="BF35" s="115"/>
+      <c r="BG35" s="115"/>
+      <c r="BH35" s="115"/>
+      <c r="BI35" s="115"/>
+      <c r="BJ35" s="115"/>
+      <c r="BK35" s="115"/>
+      <c r="BL35" s="115"/>
+      <c r="BM35" s="115"/>
+      <c r="BN35" s="115"/>
+      <c r="BO35" s="115"/>
+      <c r="BP35" s="136"/>
     </row>
     <row r="36" spans="1:68" ht="15">
       <c r="E36" s="110" t="s">
@@ -5348,61 +8690,61 @@
       <c r="O36" s="111"/>
       <c r="P36" s="111"/>
       <c r="Q36" s="111"/>
-      <c r="R36" s="109" t="s">
+      <c r="R36" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="S36" s="109"/>
-      <c r="T36" s="109"/>
-      <c r="U36" s="109"/>
-      <c r="V36" s="109"/>
-      <c r="W36" s="109"/>
-      <c r="X36" s="109"/>
-      <c r="Y36" s="109"/>
-      <c r="Z36" s="109"/>
-      <c r="AA36" s="109"/>
-      <c r="AB36" s="109"/>
-      <c r="AC36" s="109"/>
-      <c r="AD36" s="109"/>
-      <c r="AE36" s="109"/>
-      <c r="AF36" s="109"/>
-      <c r="AG36" s="109"/>
-      <c r="AH36" s="109"/>
-      <c r="AI36" s="109"/>
-      <c r="AJ36" s="109"/>
-      <c r="AK36" s="109"/>
-      <c r="AL36" s="109"/>
-      <c r="AM36" s="109"/>
-      <c r="AN36" s="109"/>
-      <c r="AO36" s="109"/>
-      <c r="AP36" s="109" t="s">
+      <c r="S36" s="115"/>
+      <c r="T36" s="115"/>
+      <c r="U36" s="115"/>
+      <c r="V36" s="115"/>
+      <c r="W36" s="115"/>
+      <c r="X36" s="115"/>
+      <c r="Y36" s="115"/>
+      <c r="Z36" s="115"/>
+      <c r="AA36" s="115"/>
+      <c r="AB36" s="115"/>
+      <c r="AC36" s="115"/>
+      <c r="AD36" s="115"/>
+      <c r="AE36" s="115"/>
+      <c r="AF36" s="115"/>
+      <c r="AG36" s="115"/>
+      <c r="AH36" s="115"/>
+      <c r="AI36" s="115"/>
+      <c r="AJ36" s="115"/>
+      <c r="AK36" s="115"/>
+      <c r="AL36" s="115"/>
+      <c r="AM36" s="115"/>
+      <c r="AN36" s="115"/>
+      <c r="AO36" s="115"/>
+      <c r="AP36" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="AQ36" s="109"/>
-      <c r="AR36" s="109"/>
-      <c r="AS36" s="109"/>
-      <c r="AT36" s="109"/>
-      <c r="AU36" s="109"/>
-      <c r="AV36" s="109"/>
-      <c r="AW36" s="109"/>
-      <c r="AX36" s="109"/>
-      <c r="AY36" s="109"/>
-      <c r="AZ36" s="109"/>
-      <c r="BA36" s="109"/>
-      <c r="BB36" s="109"/>
-      <c r="BC36" s="109"/>
-      <c r="BD36" s="109"/>
-      <c r="BE36" s="109"/>
-      <c r="BF36" s="109"/>
-      <c r="BG36" s="109"/>
-      <c r="BH36" s="109"/>
-      <c r="BI36" s="109"/>
-      <c r="BJ36" s="109"/>
-      <c r="BK36" s="109"/>
-      <c r="BL36" s="109"/>
-      <c r="BM36" s="109"/>
-      <c r="BN36" s="109"/>
-      <c r="BO36" s="109"/>
-      <c r="BP36" s="114"/>
+      <c r="AQ36" s="115"/>
+      <c r="AR36" s="115"/>
+      <c r="AS36" s="115"/>
+      <c r="AT36" s="115"/>
+      <c r="AU36" s="115"/>
+      <c r="AV36" s="115"/>
+      <c r="AW36" s="115"/>
+      <c r="AX36" s="115"/>
+      <c r="AY36" s="115"/>
+      <c r="AZ36" s="115"/>
+      <c r="BA36" s="115"/>
+      <c r="BB36" s="115"/>
+      <c r="BC36" s="115"/>
+      <c r="BD36" s="115"/>
+      <c r="BE36" s="115"/>
+      <c r="BF36" s="115"/>
+      <c r="BG36" s="115"/>
+      <c r="BH36" s="115"/>
+      <c r="BI36" s="115"/>
+      <c r="BJ36" s="115"/>
+      <c r="BK36" s="115"/>
+      <c r="BL36" s="115"/>
+      <c r="BM36" s="115"/>
+      <c r="BN36" s="115"/>
+      <c r="BO36" s="115"/>
+      <c r="BP36" s="136"/>
     </row>
     <row r="37" spans="1:68" ht="15">
       <c r="E37" s="110" t="s">
@@ -5420,61 +8762,61 @@
       <c r="O37" s="111"/>
       <c r="P37" s="111"/>
       <c r="Q37" s="111"/>
-      <c r="R37" s="109" t="s">
+      <c r="R37" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="S37" s="109"/>
-      <c r="T37" s="109"/>
-      <c r="U37" s="109"/>
-      <c r="V37" s="109"/>
-      <c r="W37" s="109"/>
-      <c r="X37" s="109"/>
-      <c r="Y37" s="109"/>
-      <c r="Z37" s="109"/>
-      <c r="AA37" s="109"/>
-      <c r="AB37" s="109"/>
-      <c r="AC37" s="109"/>
-      <c r="AD37" s="109"/>
-      <c r="AE37" s="109"/>
-      <c r="AF37" s="109"/>
-      <c r="AG37" s="109"/>
-      <c r="AH37" s="109"/>
-      <c r="AI37" s="109"/>
-      <c r="AJ37" s="109"/>
-      <c r="AK37" s="109"/>
-      <c r="AL37" s="109"/>
-      <c r="AM37" s="109"/>
-      <c r="AN37" s="109"/>
-      <c r="AO37" s="109"/>
-      <c r="AP37" s="109" t="s">
+      <c r="S37" s="115"/>
+      <c r="T37" s="115"/>
+      <c r="U37" s="115"/>
+      <c r="V37" s="115"/>
+      <c r="W37" s="115"/>
+      <c r="X37" s="115"/>
+      <c r="Y37" s="115"/>
+      <c r="Z37" s="115"/>
+      <c r="AA37" s="115"/>
+      <c r="AB37" s="115"/>
+      <c r="AC37" s="115"/>
+      <c r="AD37" s="115"/>
+      <c r="AE37" s="115"/>
+      <c r="AF37" s="115"/>
+      <c r="AG37" s="115"/>
+      <c r="AH37" s="115"/>
+      <c r="AI37" s="115"/>
+      <c r="AJ37" s="115"/>
+      <c r="AK37" s="115"/>
+      <c r="AL37" s="115"/>
+      <c r="AM37" s="115"/>
+      <c r="AN37" s="115"/>
+      <c r="AO37" s="115"/>
+      <c r="AP37" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="AQ37" s="109"/>
-      <c r="AR37" s="109"/>
-      <c r="AS37" s="109"/>
-      <c r="AT37" s="109"/>
-      <c r="AU37" s="109"/>
-      <c r="AV37" s="109"/>
-      <c r="AW37" s="109"/>
-      <c r="AX37" s="109"/>
-      <c r="AY37" s="109"/>
-      <c r="AZ37" s="109"/>
-      <c r="BA37" s="109"/>
-      <c r="BB37" s="109"/>
-      <c r="BC37" s="109"/>
-      <c r="BD37" s="109"/>
-      <c r="BE37" s="109"/>
-      <c r="BF37" s="109"/>
-      <c r="BG37" s="109"/>
-      <c r="BH37" s="109"/>
-      <c r="BI37" s="109"/>
-      <c r="BJ37" s="109"/>
-      <c r="BK37" s="109"/>
-      <c r="BL37" s="109"/>
-      <c r="BM37" s="109"/>
-      <c r="BN37" s="109"/>
-      <c r="BO37" s="109"/>
-      <c r="BP37" s="114"/>
+      <c r="AQ37" s="115"/>
+      <c r="AR37" s="115"/>
+      <c r="AS37" s="115"/>
+      <c r="AT37" s="115"/>
+      <c r="AU37" s="115"/>
+      <c r="AV37" s="115"/>
+      <c r="AW37" s="115"/>
+      <c r="AX37" s="115"/>
+      <c r="AY37" s="115"/>
+      <c r="AZ37" s="115"/>
+      <c r="BA37" s="115"/>
+      <c r="BB37" s="115"/>
+      <c r="BC37" s="115"/>
+      <c r="BD37" s="115"/>
+      <c r="BE37" s="115"/>
+      <c r="BF37" s="115"/>
+      <c r="BG37" s="115"/>
+      <c r="BH37" s="115"/>
+      <c r="BI37" s="115"/>
+      <c r="BJ37" s="115"/>
+      <c r="BK37" s="115"/>
+      <c r="BL37" s="115"/>
+      <c r="BM37" s="115"/>
+      <c r="BN37" s="115"/>
+      <c r="BO37" s="115"/>
+      <c r="BP37" s="136"/>
     </row>
     <row r="38" spans="1:68" ht="15">
       <c r="E38" s="110" t="s">
@@ -5492,61 +8834,61 @@
       <c r="O38" s="111"/>
       <c r="P38" s="111"/>
       <c r="Q38" s="111"/>
-      <c r="R38" s="109" t="s">
+      <c r="R38" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="S38" s="109"/>
-      <c r="T38" s="109"/>
-      <c r="U38" s="109"/>
-      <c r="V38" s="109"/>
-      <c r="W38" s="109"/>
-      <c r="X38" s="109"/>
-      <c r="Y38" s="109"/>
-      <c r="Z38" s="109"/>
-      <c r="AA38" s="109"/>
-      <c r="AB38" s="109"/>
-      <c r="AC38" s="109"/>
-      <c r="AD38" s="109"/>
-      <c r="AE38" s="109"/>
-      <c r="AF38" s="109"/>
-      <c r="AG38" s="109"/>
-      <c r="AH38" s="109"/>
-      <c r="AI38" s="109"/>
-      <c r="AJ38" s="109"/>
-      <c r="AK38" s="109"/>
-      <c r="AL38" s="109"/>
-      <c r="AM38" s="109"/>
-      <c r="AN38" s="109"/>
-      <c r="AO38" s="109"/>
-      <c r="AP38" s="109" t="s">
+      <c r="S38" s="115"/>
+      <c r="T38" s="115"/>
+      <c r="U38" s="115"/>
+      <c r="V38" s="115"/>
+      <c r="W38" s="115"/>
+      <c r="X38" s="115"/>
+      <c r="Y38" s="115"/>
+      <c r="Z38" s="115"/>
+      <c r="AA38" s="115"/>
+      <c r="AB38" s="115"/>
+      <c r="AC38" s="115"/>
+      <c r="AD38" s="115"/>
+      <c r="AE38" s="115"/>
+      <c r="AF38" s="115"/>
+      <c r="AG38" s="115"/>
+      <c r="AH38" s="115"/>
+      <c r="AI38" s="115"/>
+      <c r="AJ38" s="115"/>
+      <c r="AK38" s="115"/>
+      <c r="AL38" s="115"/>
+      <c r="AM38" s="115"/>
+      <c r="AN38" s="115"/>
+      <c r="AO38" s="115"/>
+      <c r="AP38" s="115" t="s">
         <v>66</v>
       </c>
-      <c r="AQ38" s="109"/>
-      <c r="AR38" s="109"/>
-      <c r="AS38" s="109"/>
-      <c r="AT38" s="109"/>
-      <c r="AU38" s="109"/>
-      <c r="AV38" s="109"/>
-      <c r="AW38" s="109"/>
-      <c r="AX38" s="109"/>
-      <c r="AY38" s="109"/>
-      <c r="AZ38" s="109"/>
-      <c r="BA38" s="109"/>
-      <c r="BB38" s="109"/>
-      <c r="BC38" s="109"/>
-      <c r="BD38" s="109"/>
-      <c r="BE38" s="109"/>
-      <c r="BF38" s="109"/>
-      <c r="BG38" s="109"/>
-      <c r="BH38" s="109"/>
-      <c r="BI38" s="109"/>
-      <c r="BJ38" s="109"/>
-      <c r="BK38" s="109"/>
-      <c r="BL38" s="109"/>
-      <c r="BM38" s="109"/>
-      <c r="BN38" s="109"/>
-      <c r="BO38" s="109"/>
-      <c r="BP38" s="114"/>
+      <c r="AQ38" s="115"/>
+      <c r="AR38" s="115"/>
+      <c r="AS38" s="115"/>
+      <c r="AT38" s="115"/>
+      <c r="AU38" s="115"/>
+      <c r="AV38" s="115"/>
+      <c r="AW38" s="115"/>
+      <c r="AX38" s="115"/>
+      <c r="AY38" s="115"/>
+      <c r="AZ38" s="115"/>
+      <c r="BA38" s="115"/>
+      <c r="BB38" s="115"/>
+      <c r="BC38" s="115"/>
+      <c r="BD38" s="115"/>
+      <c r="BE38" s="115"/>
+      <c r="BF38" s="115"/>
+      <c r="BG38" s="115"/>
+      <c r="BH38" s="115"/>
+      <c r="BI38" s="115"/>
+      <c r="BJ38" s="115"/>
+      <c r="BK38" s="115"/>
+      <c r="BL38" s="115"/>
+      <c r="BM38" s="115"/>
+      <c r="BN38" s="115"/>
+      <c r="BO38" s="115"/>
+      <c r="BP38" s="136"/>
     </row>
     <row r="39" spans="1:68" ht="15">
       <c r="E39" s="110" t="s">
@@ -5564,61 +8906,61 @@
       <c r="O39" s="111"/>
       <c r="P39" s="111"/>
       <c r="Q39" s="111"/>
-      <c r="R39" s="109" t="s">
+      <c r="R39" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="S39" s="109"/>
-      <c r="T39" s="109"/>
-      <c r="U39" s="109"/>
-      <c r="V39" s="109"/>
-      <c r="W39" s="109"/>
-      <c r="X39" s="109"/>
-      <c r="Y39" s="109"/>
-      <c r="Z39" s="109"/>
-      <c r="AA39" s="109"/>
-      <c r="AB39" s="109"/>
-      <c r="AC39" s="109"/>
-      <c r="AD39" s="109"/>
-      <c r="AE39" s="109"/>
-      <c r="AF39" s="109"/>
-      <c r="AG39" s="109"/>
-      <c r="AH39" s="109"/>
-      <c r="AI39" s="109"/>
-      <c r="AJ39" s="109"/>
-      <c r="AK39" s="109"/>
-      <c r="AL39" s="109"/>
-      <c r="AM39" s="109"/>
-      <c r="AN39" s="109"/>
-      <c r="AO39" s="109"/>
-      <c r="AP39" s="109" t="s">
+      <c r="S39" s="115"/>
+      <c r="T39" s="115"/>
+      <c r="U39" s="115"/>
+      <c r="V39" s="115"/>
+      <c r="W39" s="115"/>
+      <c r="X39" s="115"/>
+      <c r="Y39" s="115"/>
+      <c r="Z39" s="115"/>
+      <c r="AA39" s="115"/>
+      <c r="AB39" s="115"/>
+      <c r="AC39" s="115"/>
+      <c r="AD39" s="115"/>
+      <c r="AE39" s="115"/>
+      <c r="AF39" s="115"/>
+      <c r="AG39" s="115"/>
+      <c r="AH39" s="115"/>
+      <c r="AI39" s="115"/>
+      <c r="AJ39" s="115"/>
+      <c r="AK39" s="115"/>
+      <c r="AL39" s="115"/>
+      <c r="AM39" s="115"/>
+      <c r="AN39" s="115"/>
+      <c r="AO39" s="115"/>
+      <c r="AP39" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="AQ39" s="109"/>
-      <c r="AR39" s="109"/>
-      <c r="AS39" s="109"/>
-      <c r="AT39" s="109"/>
-      <c r="AU39" s="109"/>
-      <c r="AV39" s="109"/>
-      <c r="AW39" s="109"/>
-      <c r="AX39" s="109"/>
-      <c r="AY39" s="109"/>
-      <c r="AZ39" s="109"/>
-      <c r="BA39" s="109"/>
-      <c r="BB39" s="109"/>
-      <c r="BC39" s="109"/>
-      <c r="BD39" s="109"/>
-      <c r="BE39" s="109"/>
-      <c r="BF39" s="109"/>
-      <c r="BG39" s="109"/>
-      <c r="BH39" s="109"/>
-      <c r="BI39" s="109"/>
-      <c r="BJ39" s="109"/>
-      <c r="BK39" s="109"/>
-      <c r="BL39" s="109"/>
-      <c r="BM39" s="109"/>
-      <c r="BN39" s="109"/>
-      <c r="BO39" s="109"/>
-      <c r="BP39" s="114"/>
+      <c r="AQ39" s="115"/>
+      <c r="AR39" s="115"/>
+      <c r="AS39" s="115"/>
+      <c r="AT39" s="115"/>
+      <c r="AU39" s="115"/>
+      <c r="AV39" s="115"/>
+      <c r="AW39" s="115"/>
+      <c r="AX39" s="115"/>
+      <c r="AY39" s="115"/>
+      <c r="AZ39" s="115"/>
+      <c r="BA39" s="115"/>
+      <c r="BB39" s="115"/>
+      <c r="BC39" s="115"/>
+      <c r="BD39" s="115"/>
+      <c r="BE39" s="115"/>
+      <c r="BF39" s="115"/>
+      <c r="BG39" s="115"/>
+      <c r="BH39" s="115"/>
+      <c r="BI39" s="115"/>
+      <c r="BJ39" s="115"/>
+      <c r="BK39" s="115"/>
+      <c r="BL39" s="115"/>
+      <c r="BM39" s="115"/>
+      <c r="BN39" s="115"/>
+      <c r="BO39" s="115"/>
+      <c r="BP39" s="136"/>
     </row>
     <row r="40" spans="1:68" ht="15">
       <c r="E40" s="110" t="s">
@@ -5636,61 +8978,61 @@
       <c r="O40" s="111"/>
       <c r="P40" s="111"/>
       <c r="Q40" s="111"/>
-      <c r="R40" s="109" t="s">
+      <c r="R40" s="115" t="s">
         <v>71</v>
       </c>
-      <c r="S40" s="109"/>
-      <c r="T40" s="109"/>
-      <c r="U40" s="109"/>
-      <c r="V40" s="109"/>
-      <c r="W40" s="109"/>
-      <c r="X40" s="109"/>
-      <c r="Y40" s="109"/>
-      <c r="Z40" s="109"/>
-      <c r="AA40" s="109"/>
-      <c r="AB40" s="109"/>
-      <c r="AC40" s="109"/>
-      <c r="AD40" s="109"/>
-      <c r="AE40" s="109"/>
-      <c r="AF40" s="109"/>
-      <c r="AG40" s="109"/>
-      <c r="AH40" s="109"/>
-      <c r="AI40" s="109"/>
-      <c r="AJ40" s="109"/>
-      <c r="AK40" s="109"/>
-      <c r="AL40" s="109"/>
-      <c r="AM40" s="109"/>
-      <c r="AN40" s="109"/>
-      <c r="AO40" s="109"/>
-      <c r="AP40" s="109" t="s">
+      <c r="S40" s="115"/>
+      <c r="T40" s="115"/>
+      <c r="U40" s="115"/>
+      <c r="V40" s="115"/>
+      <c r="W40" s="115"/>
+      <c r="X40" s="115"/>
+      <c r="Y40" s="115"/>
+      <c r="Z40" s="115"/>
+      <c r="AA40" s="115"/>
+      <c r="AB40" s="115"/>
+      <c r="AC40" s="115"/>
+      <c r="AD40" s="115"/>
+      <c r="AE40" s="115"/>
+      <c r="AF40" s="115"/>
+      <c r="AG40" s="115"/>
+      <c r="AH40" s="115"/>
+      <c r="AI40" s="115"/>
+      <c r="AJ40" s="115"/>
+      <c r="AK40" s="115"/>
+      <c r="AL40" s="115"/>
+      <c r="AM40" s="115"/>
+      <c r="AN40" s="115"/>
+      <c r="AO40" s="115"/>
+      <c r="AP40" s="115" t="s">
         <v>72</v>
       </c>
-      <c r="AQ40" s="109"/>
-      <c r="AR40" s="109"/>
-      <c r="AS40" s="109"/>
-      <c r="AT40" s="109"/>
-      <c r="AU40" s="109"/>
-      <c r="AV40" s="109"/>
-      <c r="AW40" s="109"/>
-      <c r="AX40" s="109"/>
-      <c r="AY40" s="109"/>
-      <c r="AZ40" s="109"/>
-      <c r="BA40" s="109"/>
-      <c r="BB40" s="109"/>
-      <c r="BC40" s="109"/>
-      <c r="BD40" s="109"/>
-      <c r="BE40" s="109"/>
-      <c r="BF40" s="109"/>
-      <c r="BG40" s="109"/>
-      <c r="BH40" s="109"/>
-      <c r="BI40" s="109"/>
-      <c r="BJ40" s="109"/>
-      <c r="BK40" s="109"/>
-      <c r="BL40" s="109"/>
-      <c r="BM40" s="109"/>
-      <c r="BN40" s="109"/>
-      <c r="BO40" s="109"/>
-      <c r="BP40" s="114"/>
+      <c r="AQ40" s="115"/>
+      <c r="AR40" s="115"/>
+      <c r="AS40" s="115"/>
+      <c r="AT40" s="115"/>
+      <c r="AU40" s="115"/>
+      <c r="AV40" s="115"/>
+      <c r="AW40" s="115"/>
+      <c r="AX40" s="115"/>
+      <c r="AY40" s="115"/>
+      <c r="AZ40" s="115"/>
+      <c r="BA40" s="115"/>
+      <c r="BB40" s="115"/>
+      <c r="BC40" s="115"/>
+      <c r="BD40" s="115"/>
+      <c r="BE40" s="115"/>
+      <c r="BF40" s="115"/>
+      <c r="BG40" s="115"/>
+      <c r="BH40" s="115"/>
+      <c r="BI40" s="115"/>
+      <c r="BJ40" s="115"/>
+      <c r="BK40" s="115"/>
+      <c r="BL40" s="115"/>
+      <c r="BM40" s="115"/>
+      <c r="BN40" s="115"/>
+      <c r="BO40" s="115"/>
+      <c r="BP40" s="136"/>
     </row>
     <row r="41" spans="1:68" ht="15">
       <c r="E41" s="110" t="s">
@@ -5708,61 +9050,61 @@
       <c r="O41" s="111"/>
       <c r="P41" s="111"/>
       <c r="Q41" s="111"/>
-      <c r="R41" s="109" t="s">
+      <c r="R41" s="115" t="s">
         <v>74</v>
       </c>
-      <c r="S41" s="109"/>
-      <c r="T41" s="109"/>
-      <c r="U41" s="109"/>
-      <c r="V41" s="109"/>
-      <c r="W41" s="109"/>
-      <c r="X41" s="109"/>
-      <c r="Y41" s="109"/>
-      <c r="Z41" s="109"/>
-      <c r="AA41" s="109"/>
-      <c r="AB41" s="109"/>
-      <c r="AC41" s="109"/>
-      <c r="AD41" s="109"/>
-      <c r="AE41" s="109"/>
-      <c r="AF41" s="109"/>
-      <c r="AG41" s="109"/>
-      <c r="AH41" s="109"/>
-      <c r="AI41" s="109"/>
-      <c r="AJ41" s="109"/>
-      <c r="AK41" s="109"/>
-      <c r="AL41" s="109"/>
-      <c r="AM41" s="109"/>
-      <c r="AN41" s="109"/>
-      <c r="AO41" s="109"/>
-      <c r="AP41" s="109" t="s">
+      <c r="S41" s="115"/>
+      <c r="T41" s="115"/>
+      <c r="U41" s="115"/>
+      <c r="V41" s="115"/>
+      <c r="W41" s="115"/>
+      <c r="X41" s="115"/>
+      <c r="Y41" s="115"/>
+      <c r="Z41" s="115"/>
+      <c r="AA41" s="115"/>
+      <c r="AB41" s="115"/>
+      <c r="AC41" s="115"/>
+      <c r="AD41" s="115"/>
+      <c r="AE41" s="115"/>
+      <c r="AF41" s="115"/>
+      <c r="AG41" s="115"/>
+      <c r="AH41" s="115"/>
+      <c r="AI41" s="115"/>
+      <c r="AJ41" s="115"/>
+      <c r="AK41" s="115"/>
+      <c r="AL41" s="115"/>
+      <c r="AM41" s="115"/>
+      <c r="AN41" s="115"/>
+      <c r="AO41" s="115"/>
+      <c r="AP41" s="115" t="s">
         <v>75</v>
       </c>
-      <c r="AQ41" s="109"/>
-      <c r="AR41" s="109"/>
-      <c r="AS41" s="109"/>
-      <c r="AT41" s="109"/>
-      <c r="AU41" s="109"/>
-      <c r="AV41" s="109"/>
-      <c r="AW41" s="109"/>
-      <c r="AX41" s="109"/>
-      <c r="AY41" s="109"/>
-      <c r="AZ41" s="109"/>
-      <c r="BA41" s="109"/>
-      <c r="BB41" s="109"/>
-      <c r="BC41" s="109"/>
-      <c r="BD41" s="109"/>
-      <c r="BE41" s="109"/>
-      <c r="BF41" s="109"/>
-      <c r="BG41" s="109"/>
-      <c r="BH41" s="109"/>
-      <c r="BI41" s="109"/>
-      <c r="BJ41" s="109"/>
-      <c r="BK41" s="109"/>
-      <c r="BL41" s="109"/>
-      <c r="BM41" s="109"/>
-      <c r="BN41" s="109"/>
-      <c r="BO41" s="109"/>
-      <c r="BP41" s="114"/>
+      <c r="AQ41" s="115"/>
+      <c r="AR41" s="115"/>
+      <c r="AS41" s="115"/>
+      <c r="AT41" s="115"/>
+      <c r="AU41" s="115"/>
+      <c r="AV41" s="115"/>
+      <c r="AW41" s="115"/>
+      <c r="AX41" s="115"/>
+      <c r="AY41" s="115"/>
+      <c r="AZ41" s="115"/>
+      <c r="BA41" s="115"/>
+      <c r="BB41" s="115"/>
+      <c r="BC41" s="115"/>
+      <c r="BD41" s="115"/>
+      <c r="BE41" s="115"/>
+      <c r="BF41" s="115"/>
+      <c r="BG41" s="115"/>
+      <c r="BH41" s="115"/>
+      <c r="BI41" s="115"/>
+      <c r="BJ41" s="115"/>
+      <c r="BK41" s="115"/>
+      <c r="BL41" s="115"/>
+      <c r="BM41" s="115"/>
+      <c r="BN41" s="115"/>
+      <c r="BO41" s="115"/>
+      <c r="BP41" s="136"/>
     </row>
     <row r="42" spans="1:68" ht="15">
       <c r="E42" s="110" t="s">
@@ -5780,61 +9122,61 @@
       <c r="O42" s="111"/>
       <c r="P42" s="111"/>
       <c r="Q42" s="111"/>
-      <c r="R42" s="109" t="s">
+      <c r="R42" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="S42" s="109"/>
-      <c r="T42" s="109"/>
-      <c r="U42" s="109"/>
-      <c r="V42" s="109"/>
-      <c r="W42" s="109"/>
-      <c r="X42" s="109"/>
-      <c r="Y42" s="109"/>
-      <c r="Z42" s="109"/>
-      <c r="AA42" s="109"/>
-      <c r="AB42" s="109"/>
-      <c r="AC42" s="109"/>
-      <c r="AD42" s="109"/>
-      <c r="AE42" s="109"/>
-      <c r="AF42" s="109"/>
-      <c r="AG42" s="109"/>
-      <c r="AH42" s="109"/>
-      <c r="AI42" s="109"/>
-      <c r="AJ42" s="109"/>
-      <c r="AK42" s="109"/>
-      <c r="AL42" s="109"/>
-      <c r="AM42" s="109"/>
-      <c r="AN42" s="109"/>
-      <c r="AO42" s="109"/>
-      <c r="AP42" s="109" t="s">
+      <c r="S42" s="115"/>
+      <c r="T42" s="115"/>
+      <c r="U42" s="115"/>
+      <c r="V42" s="115"/>
+      <c r="W42" s="115"/>
+      <c r="X42" s="115"/>
+      <c r="Y42" s="115"/>
+      <c r="Z42" s="115"/>
+      <c r="AA42" s="115"/>
+      <c r="AB42" s="115"/>
+      <c r="AC42" s="115"/>
+      <c r="AD42" s="115"/>
+      <c r="AE42" s="115"/>
+      <c r="AF42" s="115"/>
+      <c r="AG42" s="115"/>
+      <c r="AH42" s="115"/>
+      <c r="AI42" s="115"/>
+      <c r="AJ42" s="115"/>
+      <c r="AK42" s="115"/>
+      <c r="AL42" s="115"/>
+      <c r="AM42" s="115"/>
+      <c r="AN42" s="115"/>
+      <c r="AO42" s="115"/>
+      <c r="AP42" s="115" t="s">
         <v>78</v>
       </c>
-      <c r="AQ42" s="109"/>
-      <c r="AR42" s="109"/>
-      <c r="AS42" s="109"/>
-      <c r="AT42" s="109"/>
-      <c r="AU42" s="109"/>
-      <c r="AV42" s="109"/>
-      <c r="AW42" s="109"/>
-      <c r="AX42" s="109"/>
-      <c r="AY42" s="109"/>
-      <c r="AZ42" s="109"/>
-      <c r="BA42" s="109"/>
-      <c r="BB42" s="109"/>
-      <c r="BC42" s="109"/>
-      <c r="BD42" s="109"/>
-      <c r="BE42" s="109"/>
-      <c r="BF42" s="109"/>
-      <c r="BG42" s="109"/>
-      <c r="BH42" s="109"/>
-      <c r="BI42" s="109"/>
-      <c r="BJ42" s="109"/>
-      <c r="BK42" s="109"/>
-      <c r="BL42" s="109"/>
-      <c r="BM42" s="109"/>
-      <c r="BN42" s="109"/>
-      <c r="BO42" s="109"/>
-      <c r="BP42" s="114"/>
+      <c r="AQ42" s="115"/>
+      <c r="AR42" s="115"/>
+      <c r="AS42" s="115"/>
+      <c r="AT42" s="115"/>
+      <c r="AU42" s="115"/>
+      <c r="AV42" s="115"/>
+      <c r="AW42" s="115"/>
+      <c r="AX42" s="115"/>
+      <c r="AY42" s="115"/>
+      <c r="AZ42" s="115"/>
+      <c r="BA42" s="115"/>
+      <c r="BB42" s="115"/>
+      <c r="BC42" s="115"/>
+      <c r="BD42" s="115"/>
+      <c r="BE42" s="115"/>
+      <c r="BF42" s="115"/>
+      <c r="BG42" s="115"/>
+      <c r="BH42" s="115"/>
+      <c r="BI42" s="115"/>
+      <c r="BJ42" s="115"/>
+      <c r="BK42" s="115"/>
+      <c r="BL42" s="115"/>
+      <c r="BM42" s="115"/>
+      <c r="BN42" s="115"/>
+      <c r="BO42" s="115"/>
+      <c r="BP42" s="136"/>
     </row>
     <row r="43" spans="1:68" ht="15">
       <c r="E43" s="110" t="s">
@@ -5852,133 +9194,133 @@
       <c r="O43" s="111"/>
       <c r="P43" s="111"/>
       <c r="Q43" s="111"/>
-      <c r="R43" s="109" t="s">
+      <c r="R43" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="S43" s="109"/>
-      <c r="T43" s="109"/>
-      <c r="U43" s="109"/>
-      <c r="V43" s="109"/>
-      <c r="W43" s="109"/>
-      <c r="X43" s="109"/>
-      <c r="Y43" s="109"/>
-      <c r="Z43" s="109"/>
-      <c r="AA43" s="109"/>
-      <c r="AB43" s="109"/>
-      <c r="AC43" s="109"/>
-      <c r="AD43" s="109"/>
-      <c r="AE43" s="109"/>
-      <c r="AF43" s="109"/>
-      <c r="AG43" s="109"/>
-      <c r="AH43" s="109"/>
-      <c r="AI43" s="109"/>
-      <c r="AJ43" s="109"/>
-      <c r="AK43" s="109"/>
-      <c r="AL43" s="109"/>
-      <c r="AM43" s="109"/>
-      <c r="AN43" s="109"/>
-      <c r="AO43" s="109"/>
-      <c r="AP43" s="109" t="s">
+      <c r="S43" s="115"/>
+      <c r="T43" s="115"/>
+      <c r="U43" s="115"/>
+      <c r="V43" s="115"/>
+      <c r="W43" s="115"/>
+      <c r="X43" s="115"/>
+      <c r="Y43" s="115"/>
+      <c r="Z43" s="115"/>
+      <c r="AA43" s="115"/>
+      <c r="AB43" s="115"/>
+      <c r="AC43" s="115"/>
+      <c r="AD43" s="115"/>
+      <c r="AE43" s="115"/>
+      <c r="AF43" s="115"/>
+      <c r="AG43" s="115"/>
+      <c r="AH43" s="115"/>
+      <c r="AI43" s="115"/>
+      <c r="AJ43" s="115"/>
+      <c r="AK43" s="115"/>
+      <c r="AL43" s="115"/>
+      <c r="AM43" s="115"/>
+      <c r="AN43" s="115"/>
+      <c r="AO43" s="115"/>
+      <c r="AP43" s="115" t="s">
         <v>81</v>
       </c>
-      <c r="AQ43" s="109"/>
-      <c r="AR43" s="109"/>
-      <c r="AS43" s="109"/>
-      <c r="AT43" s="109"/>
-      <c r="AU43" s="109"/>
-      <c r="AV43" s="109"/>
-      <c r="AW43" s="109"/>
-      <c r="AX43" s="109"/>
-      <c r="AY43" s="109"/>
-      <c r="AZ43" s="109"/>
-      <c r="BA43" s="109"/>
-      <c r="BB43" s="109"/>
-      <c r="BC43" s="109"/>
-      <c r="BD43" s="109"/>
-      <c r="BE43" s="109"/>
-      <c r="BF43" s="109"/>
-      <c r="BG43" s="109"/>
-      <c r="BH43" s="109"/>
-      <c r="BI43" s="109"/>
-      <c r="BJ43" s="109"/>
-      <c r="BK43" s="109"/>
-      <c r="BL43" s="109"/>
-      <c r="BM43" s="109"/>
-      <c r="BN43" s="109"/>
-      <c r="BO43" s="109"/>
-      <c r="BP43" s="114"/>
+      <c r="AQ43" s="115"/>
+      <c r="AR43" s="115"/>
+      <c r="AS43" s="115"/>
+      <c r="AT43" s="115"/>
+      <c r="AU43" s="115"/>
+      <c r="AV43" s="115"/>
+      <c r="AW43" s="115"/>
+      <c r="AX43" s="115"/>
+      <c r="AY43" s="115"/>
+      <c r="AZ43" s="115"/>
+      <c r="BA43" s="115"/>
+      <c r="BB43" s="115"/>
+      <c r="BC43" s="115"/>
+      <c r="BD43" s="115"/>
+      <c r="BE43" s="115"/>
+      <c r="BF43" s="115"/>
+      <c r="BG43" s="115"/>
+      <c r="BH43" s="115"/>
+      <c r="BI43" s="115"/>
+      <c r="BJ43" s="115"/>
+      <c r="BK43" s="115"/>
+      <c r="BL43" s="115"/>
+      <c r="BM43" s="115"/>
+      <c r="BN43" s="115"/>
+      <c r="BO43" s="115"/>
+      <c r="BP43" s="136"/>
     </row>
     <row r="44" spans="1:68" ht="15.75" thickBot="1">
-      <c r="E44" s="106" t="s">
+      <c r="E44" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="F44" s="107"/>
-      <c r="G44" s="107"/>
-      <c r="H44" s="107"/>
-      <c r="I44" s="107"/>
-      <c r="J44" s="107"/>
-      <c r="K44" s="107"/>
-      <c r="L44" s="107"/>
-      <c r="M44" s="107"/>
-      <c r="N44" s="107"/>
-      <c r="O44" s="107"/>
-      <c r="P44" s="107"/>
-      <c r="Q44" s="107"/>
-      <c r="R44" s="112" t="s">
+      <c r="F44" s="109"/>
+      <c r="G44" s="109"/>
+      <c r="H44" s="109"/>
+      <c r="I44" s="109"/>
+      <c r="J44" s="109"/>
+      <c r="K44" s="109"/>
+      <c r="L44" s="109"/>
+      <c r="M44" s="109"/>
+      <c r="N44" s="109"/>
+      <c r="O44" s="109"/>
+      <c r="P44" s="109"/>
+      <c r="Q44" s="109"/>
+      <c r="R44" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="S44" s="112"/>
-      <c r="T44" s="112"/>
-      <c r="U44" s="112"/>
-      <c r="V44" s="112"/>
-      <c r="W44" s="112"/>
-      <c r="X44" s="112"/>
-      <c r="Y44" s="112"/>
-      <c r="Z44" s="112"/>
-      <c r="AA44" s="112"/>
-      <c r="AB44" s="112"/>
-      <c r="AC44" s="112"/>
-      <c r="AD44" s="112"/>
-      <c r="AE44" s="112"/>
-      <c r="AF44" s="112"/>
-      <c r="AG44" s="112"/>
-      <c r="AH44" s="112"/>
-      <c r="AI44" s="112"/>
-      <c r="AJ44" s="112"/>
-      <c r="AK44" s="112"/>
-      <c r="AL44" s="112"/>
-      <c r="AM44" s="112"/>
-      <c r="AN44" s="112"/>
-      <c r="AO44" s="112"/>
-      <c r="AP44" s="112" t="s">
+      <c r="S44" s="114"/>
+      <c r="T44" s="114"/>
+      <c r="U44" s="114"/>
+      <c r="V44" s="114"/>
+      <c r="W44" s="114"/>
+      <c r="X44" s="114"/>
+      <c r="Y44" s="114"/>
+      <c r="Z44" s="114"/>
+      <c r="AA44" s="114"/>
+      <c r="AB44" s="114"/>
+      <c r="AC44" s="114"/>
+      <c r="AD44" s="114"/>
+      <c r="AE44" s="114"/>
+      <c r="AF44" s="114"/>
+      <c r="AG44" s="114"/>
+      <c r="AH44" s="114"/>
+      <c r="AI44" s="114"/>
+      <c r="AJ44" s="114"/>
+      <c r="AK44" s="114"/>
+      <c r="AL44" s="114"/>
+      <c r="AM44" s="114"/>
+      <c r="AN44" s="114"/>
+      <c r="AO44" s="114"/>
+      <c r="AP44" s="114" t="s">
         <v>84</v>
       </c>
-      <c r="AQ44" s="112"/>
-      <c r="AR44" s="112"/>
-      <c r="AS44" s="112"/>
-      <c r="AT44" s="112"/>
-      <c r="AU44" s="112"/>
-      <c r="AV44" s="112"/>
-      <c r="AW44" s="112"/>
-      <c r="AX44" s="112"/>
-      <c r="AY44" s="112"/>
-      <c r="AZ44" s="112"/>
-      <c r="BA44" s="112"/>
-      <c r="BB44" s="112"/>
-      <c r="BC44" s="112"/>
-      <c r="BD44" s="112"/>
-      <c r="BE44" s="112"/>
-      <c r="BF44" s="112"/>
-      <c r="BG44" s="112"/>
-      <c r="BH44" s="112"/>
-      <c r="BI44" s="112"/>
-      <c r="BJ44" s="112"/>
-      <c r="BK44" s="112"/>
-      <c r="BL44" s="112"/>
-      <c r="BM44" s="112"/>
-      <c r="BN44" s="112"/>
-      <c r="BO44" s="112"/>
-      <c r="BP44" s="115"/>
+      <c r="AQ44" s="114"/>
+      <c r="AR44" s="114"/>
+      <c r="AS44" s="114"/>
+      <c r="AT44" s="114"/>
+      <c r="AU44" s="114"/>
+      <c r="AV44" s="114"/>
+      <c r="AW44" s="114"/>
+      <c r="AX44" s="114"/>
+      <c r="AY44" s="114"/>
+      <c r="AZ44" s="114"/>
+      <c r="BA44" s="114"/>
+      <c r="BB44" s="114"/>
+      <c r="BC44" s="114"/>
+      <c r="BD44" s="114"/>
+      <c r="BE44" s="114"/>
+      <c r="BF44" s="114"/>
+      <c r="BG44" s="114"/>
+      <c r="BH44" s="114"/>
+      <c r="BI44" s="114"/>
+      <c r="BJ44" s="114"/>
+      <c r="BK44" s="114"/>
+      <c r="BL44" s="114"/>
+      <c r="BM44" s="114"/>
+      <c r="BN44" s="114"/>
+      <c r="BO44" s="114"/>
+      <c r="BP44" s="135"/>
     </row>
     <row r="45" spans="1:68" ht="15" thickBot="1"/>
     <row r="46" spans="1:68" s="16" customFormat="1" ht="15.75" thickBot="1">
@@ -6787,42 +10129,23 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="L12:AG12"/>
-    <mergeCell ref="AH12:AY12"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="AH15:AY15"/>
-    <mergeCell ref="AH13:AY13"/>
-    <mergeCell ref="AH14:AY14"/>
-    <mergeCell ref="L15:AG15"/>
-    <mergeCell ref="L13:AG13"/>
-    <mergeCell ref="L14:AG14"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="I27:P27"/>
-    <mergeCell ref="I28:P28"/>
-    <mergeCell ref="I29:P29"/>
-    <mergeCell ref="I30:P30"/>
-    <mergeCell ref="AQ28:BB28"/>
-    <mergeCell ref="Q27:AC27"/>
-    <mergeCell ref="Q28:AC28"/>
-    <mergeCell ref="Q29:AC29"/>
-    <mergeCell ref="Q30:AC30"/>
-    <mergeCell ref="AD27:AP27"/>
-    <mergeCell ref="AD28:AP28"/>
-    <mergeCell ref="AD29:AP29"/>
-    <mergeCell ref="AD30:AP30"/>
-    <mergeCell ref="AZ12:BI12"/>
-    <mergeCell ref="AZ14:BI14"/>
-    <mergeCell ref="AZ13:BI13"/>
-    <mergeCell ref="AZ15:BI15"/>
-    <mergeCell ref="AQ27:BB27"/>
-    <mergeCell ref="AQ29:BB29"/>
-    <mergeCell ref="AQ30:BB30"/>
+    <mergeCell ref="E37:Q37"/>
+    <mergeCell ref="AP36:BP36"/>
+    <mergeCell ref="AP37:BP37"/>
+    <mergeCell ref="AP38:BP38"/>
+    <mergeCell ref="E44:Q44"/>
+    <mergeCell ref="R34:AO34"/>
+    <mergeCell ref="R35:AO35"/>
+    <mergeCell ref="R36:AO36"/>
+    <mergeCell ref="R37:AO37"/>
+    <mergeCell ref="E43:Q43"/>
+    <mergeCell ref="R43:AO43"/>
+    <mergeCell ref="R44:AO44"/>
+    <mergeCell ref="E38:Q38"/>
+    <mergeCell ref="E39:Q39"/>
+    <mergeCell ref="E40:Q40"/>
+    <mergeCell ref="E41:Q41"/>
+    <mergeCell ref="E42:Q42"/>
     <mergeCell ref="E34:Q34"/>
     <mergeCell ref="E35:Q35"/>
     <mergeCell ref="E36:Q36"/>
@@ -6839,23 +10162,42 @@
     <mergeCell ref="AP43:BP43"/>
     <mergeCell ref="AP34:BP34"/>
     <mergeCell ref="AP35:BP35"/>
-    <mergeCell ref="AP36:BP36"/>
-    <mergeCell ref="AP37:BP37"/>
-    <mergeCell ref="AP38:BP38"/>
-    <mergeCell ref="E44:Q44"/>
-    <mergeCell ref="R34:AO34"/>
-    <mergeCell ref="R35:AO35"/>
-    <mergeCell ref="R36:AO36"/>
-    <mergeCell ref="R37:AO37"/>
-    <mergeCell ref="E43:Q43"/>
-    <mergeCell ref="R43:AO43"/>
-    <mergeCell ref="R44:AO44"/>
-    <mergeCell ref="E38:Q38"/>
-    <mergeCell ref="E39:Q39"/>
-    <mergeCell ref="E40:Q40"/>
-    <mergeCell ref="E41:Q41"/>
-    <mergeCell ref="E42:Q42"/>
-    <mergeCell ref="E37:Q37"/>
+    <mergeCell ref="AZ12:BI12"/>
+    <mergeCell ref="AZ14:BI14"/>
+    <mergeCell ref="AZ13:BI13"/>
+    <mergeCell ref="AZ15:BI15"/>
+    <mergeCell ref="AQ27:BB27"/>
+    <mergeCell ref="AQ28:BB28"/>
+    <mergeCell ref="Q27:AC27"/>
+    <mergeCell ref="Q28:AC28"/>
+    <mergeCell ref="Q29:AC29"/>
+    <mergeCell ref="Q30:AC30"/>
+    <mergeCell ref="AD27:AP27"/>
+    <mergeCell ref="AD28:AP28"/>
+    <mergeCell ref="AD29:AP29"/>
+    <mergeCell ref="AD30:AP30"/>
+    <mergeCell ref="AQ29:BB29"/>
+    <mergeCell ref="AQ30:BB30"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="I27:P27"/>
+    <mergeCell ref="I28:P28"/>
+    <mergeCell ref="I29:P29"/>
+    <mergeCell ref="I30:P30"/>
+    <mergeCell ref="L12:AG12"/>
+    <mergeCell ref="AH12:AY12"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="D15:K15"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="AH15:AY15"/>
+    <mergeCell ref="AH13:AY13"/>
+    <mergeCell ref="AH14:AY14"/>
+    <mergeCell ref="L15:AG15"/>
+    <mergeCell ref="L13:AG13"/>
+    <mergeCell ref="L14:AG14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6875,77 +10217,77 @@
     </row>
     <row r="2" spans="2:43" ht="15" thickBot="1"/>
     <row r="3" spans="2:43" ht="15">
-      <c r="F3" s="132" t="s">
+      <c r="F3" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127" t="s">
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="117"/>
+      <c r="M3" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="N3" s="127"/>
-      <c r="O3" s="127"/>
-      <c r="P3" s="127"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="127"/>
-      <c r="T3" s="127"/>
-      <c r="U3" s="127"/>
-      <c r="V3" s="127"/>
-      <c r="W3" s="127"/>
-      <c r="X3" s="127" t="s">
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="117"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="117"/>
+      <c r="S3" s="117"/>
+      <c r="T3" s="117"/>
+      <c r="U3" s="117"/>
+      <c r="V3" s="117"/>
+      <c r="W3" s="117"/>
+      <c r="X3" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="Y3" s="127"/>
-      <c r="Z3" s="127"/>
-      <c r="AA3" s="127"/>
-      <c r="AB3" s="127"/>
-      <c r="AC3" s="127"/>
-      <c r="AD3" s="127"/>
-      <c r="AE3" s="127"/>
-      <c r="AF3" s="127"/>
-      <c r="AG3" s="127"/>
+      <c r="Y3" s="117"/>
+      <c r="Z3" s="117"/>
+      <c r="AA3" s="117"/>
+      <c r="AB3" s="117"/>
+      <c r="AC3" s="117"/>
+      <c r="AD3" s="117"/>
+      <c r="AE3" s="117"/>
+      <c r="AF3" s="117"/>
+      <c r="AG3" s="117"/>
       <c r="AH3" s="140"/>
     </row>
     <row r="4" spans="2:43">
-      <c r="F4" s="133" t="s">
+      <c r="F4" s="118" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="130" t="s">
+      <c r="G4" s="119"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="119"/>
+      <c r="M4" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="130"/>
-      <c r="S4" s="130"/>
-      <c r="T4" s="130"/>
-      <c r="U4" s="130"/>
-      <c r="V4" s="130"/>
-      <c r="W4" s="130"/>
-      <c r="X4" s="130" t="s">
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="123"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="123"/>
+      <c r="V4" s="123"/>
+      <c r="W4" s="123"/>
+      <c r="X4" s="123" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="130"/>
-      <c r="Z4" s="130"/>
-      <c r="AA4" s="130"/>
-      <c r="AB4" s="130"/>
-      <c r="AC4" s="130"/>
-      <c r="AD4" s="130"/>
-      <c r="AE4" s="130"/>
-      <c r="AF4" s="130"/>
-      <c r="AG4" s="130"/>
+      <c r="Y4" s="123"/>
+      <c r="Z4" s="123"/>
+      <c r="AA4" s="123"/>
+      <c r="AB4" s="123"/>
+      <c r="AC4" s="123"/>
+      <c r="AD4" s="123"/>
+      <c r="AE4" s="123"/>
+      <c r="AF4" s="123"/>
+      <c r="AG4" s="123"/>
       <c r="AH4" s="138"/>
       <c r="AI4" s="52" t="s">
         <v>201</v>
@@ -6960,40 +10302,40 @@
       <c r="AQ4" s="53"/>
     </row>
     <row r="5" spans="2:43">
-      <c r="F5" s="133" t="s">
+      <c r="F5" s="118" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="128"/>
-      <c r="K5" s="128"/>
-      <c r="L5" s="128"/>
-      <c r="M5" s="130" t="s">
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="123" t="s">
         <v>92</v>
       </c>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="130"/>
-      <c r="R5" s="130"/>
-      <c r="S5" s="130"/>
-      <c r="T5" s="130"/>
-      <c r="U5" s="130"/>
-      <c r="V5" s="130"/>
-      <c r="W5" s="130"/>
-      <c r="X5" s="130" t="s">
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="123"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
+      <c r="U5" s="123"/>
+      <c r="V5" s="123"/>
+      <c r="W5" s="123"/>
+      <c r="X5" s="123" t="s">
         <v>93</v>
       </c>
-      <c r="Y5" s="130"/>
-      <c r="Z5" s="130"/>
-      <c r="AA5" s="130"/>
-      <c r="AB5" s="130"/>
-      <c r="AC5" s="130"/>
-      <c r="AD5" s="130"/>
-      <c r="AE5" s="130"/>
-      <c r="AF5" s="130"/>
-      <c r="AG5" s="130"/>
+      <c r="Y5" s="123"/>
+      <c r="Z5" s="123"/>
+      <c r="AA5" s="123"/>
+      <c r="AB5" s="123"/>
+      <c r="AC5" s="123"/>
+      <c r="AD5" s="123"/>
+      <c r="AE5" s="123"/>
+      <c r="AF5" s="123"/>
+      <c r="AG5" s="123"/>
       <c r="AH5" s="138"/>
       <c r="AI5" s="52"/>
       <c r="AJ5" s="53"/>
@@ -7005,40 +10347,40 @@
       <c r="AQ5" s="53"/>
     </row>
     <row r="6" spans="2:43" ht="15">
-      <c r="F6" s="133" t="s">
+      <c r="F6" s="118" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="128"/>
-      <c r="H6" s="128"/>
-      <c r="I6" s="128"/>
-      <c r="J6" s="128"/>
-      <c r="K6" s="128"/>
-      <c r="L6" s="128"/>
-      <c r="M6" s="130" t="s">
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="119"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="119"/>
+      <c r="M6" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="130"/>
-      <c r="Q6" s="130"/>
-      <c r="R6" s="130"/>
-      <c r="S6" s="130"/>
-      <c r="T6" s="130"/>
-      <c r="U6" s="130"/>
-      <c r="V6" s="130"/>
-      <c r="W6" s="130"/>
-      <c r="X6" s="130" t="s">
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="123"/>
+      <c r="R6" s="123"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="123"/>
+      <c r="U6" s="123"/>
+      <c r="V6" s="123"/>
+      <c r="W6" s="123"/>
+      <c r="X6" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="Y6" s="130"/>
-      <c r="Z6" s="130"/>
-      <c r="AA6" s="130"/>
-      <c r="AB6" s="130"/>
-      <c r="AC6" s="130"/>
-      <c r="AD6" s="130"/>
-      <c r="AE6" s="130"/>
-      <c r="AF6" s="130"/>
-      <c r="AG6" s="130"/>
+      <c r="Y6" s="123"/>
+      <c r="Z6" s="123"/>
+      <c r="AA6" s="123"/>
+      <c r="AB6" s="123"/>
+      <c r="AC6" s="123"/>
+      <c r="AD6" s="123"/>
+      <c r="AE6" s="123"/>
+      <c r="AF6" s="123"/>
+      <c r="AG6" s="123"/>
       <c r="AH6" s="138"/>
       <c r="AI6" s="52"/>
       <c r="AJ6" s="53"/>
@@ -7053,40 +10395,40 @@
       <c r="AQ6" s="53"/>
     </row>
     <row r="7" spans="2:43">
-      <c r="F7" s="133" t="s">
+      <c r="F7" s="118" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="128"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="128"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="128"/>
-      <c r="L7" s="128"/>
-      <c r="M7" s="130" t="s">
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="119"/>
+      <c r="M7" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="130"/>
-      <c r="Q7" s="130"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="130"/>
-      <c r="T7" s="130"/>
-      <c r="U7" s="130"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130" t="s">
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="123"/>
+      <c r="U7" s="123"/>
+      <c r="V7" s="123"/>
+      <c r="W7" s="123"/>
+      <c r="X7" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="Y7" s="130"/>
-      <c r="Z7" s="130"/>
-      <c r="AA7" s="130"/>
-      <c r="AB7" s="130"/>
-      <c r="AC7" s="130"/>
-      <c r="AD7" s="130"/>
-      <c r="AE7" s="130"/>
-      <c r="AF7" s="130"/>
-      <c r="AG7" s="130"/>
+      <c r="Y7" s="123"/>
+      <c r="Z7" s="123"/>
+      <c r="AA7" s="123"/>
+      <c r="AB7" s="123"/>
+      <c r="AC7" s="123"/>
+      <c r="AD7" s="123"/>
+      <c r="AE7" s="123"/>
+      <c r="AF7" s="123"/>
+      <c r="AG7" s="123"/>
       <c r="AH7" s="138"/>
       <c r="AI7" s="52"/>
       <c r="AJ7" s="53"/>
@@ -7099,40 +10441,40 @@
       <c r="AQ7" s="53"/>
     </row>
     <row r="8" spans="2:43">
-      <c r="F8" s="133" t="s">
+      <c r="F8" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="128"/>
-      <c r="H8" s="128"/>
-      <c r="I8" s="128"/>
-      <c r="J8" s="128"/>
-      <c r="K8" s="128"/>
-      <c r="L8" s="128"/>
-      <c r="M8" s="130" t="s">
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="119"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="123" t="s">
         <v>101</v>
       </c>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="130"/>
-      <c r="Q8" s="130"/>
-      <c r="R8" s="130"/>
-      <c r="S8" s="130"/>
-      <c r="T8" s="130"/>
-      <c r="U8" s="130"/>
-      <c r="V8" s="130"/>
-      <c r="W8" s="130"/>
-      <c r="X8" s="130" t="s">
+      <c r="N8" s="123"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="123"/>
+      <c r="Q8" s="123"/>
+      <c r="R8" s="123"/>
+      <c r="S8" s="123"/>
+      <c r="T8" s="123"/>
+      <c r="U8" s="123"/>
+      <c r="V8" s="123"/>
+      <c r="W8" s="123"/>
+      <c r="X8" s="123" t="s">
         <v>102</v>
       </c>
-      <c r="Y8" s="130"/>
-      <c r="Z8" s="130"/>
-      <c r="AA8" s="130"/>
-      <c r="AB8" s="130"/>
-      <c r="AC8" s="130"/>
-      <c r="AD8" s="130"/>
-      <c r="AE8" s="130"/>
-      <c r="AF8" s="130"/>
-      <c r="AG8" s="130"/>
+      <c r="Y8" s="123"/>
+      <c r="Z8" s="123"/>
+      <c r="AA8" s="123"/>
+      <c r="AB8" s="123"/>
+      <c r="AC8" s="123"/>
+      <c r="AD8" s="123"/>
+      <c r="AE8" s="123"/>
+      <c r="AF8" s="123"/>
+      <c r="AG8" s="123"/>
       <c r="AH8" s="138"/>
       <c r="AI8" s="52"/>
       <c r="AJ8" s="53"/>
@@ -7145,157 +10487,157 @@
       <c r="AQ8" s="53"/>
     </row>
     <row r="9" spans="2:43">
-      <c r="F9" s="133" t="s">
+      <c r="F9" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="128"/>
-      <c r="L9" s="128"/>
-      <c r="M9" s="130" t="s">
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="123" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="130"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="130"/>
-      <c r="Q9" s="130"/>
-      <c r="R9" s="130"/>
-      <c r="S9" s="130"/>
-      <c r="T9" s="130"/>
-      <c r="U9" s="130"/>
-      <c r="V9" s="130"/>
-      <c r="W9" s="130"/>
-      <c r="X9" s="130" t="s">
+      <c r="N9" s="123"/>
+      <c r="O9" s="123"/>
+      <c r="P9" s="123"/>
+      <c r="Q9" s="123"/>
+      <c r="R9" s="123"/>
+      <c r="S9" s="123"/>
+      <c r="T9" s="123"/>
+      <c r="U9" s="123"/>
+      <c r="V9" s="123"/>
+      <c r="W9" s="123"/>
+      <c r="X9" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="Y9" s="130"/>
-      <c r="Z9" s="130"/>
-      <c r="AA9" s="130"/>
-      <c r="AB9" s="130"/>
-      <c r="AC9" s="130"/>
-      <c r="AD9" s="130"/>
-      <c r="AE9" s="130"/>
-      <c r="AF9" s="130"/>
-      <c r="AG9" s="130"/>
+      <c r="Y9" s="123"/>
+      <c r="Z9" s="123"/>
+      <c r="AA9" s="123"/>
+      <c r="AB9" s="123"/>
+      <c r="AC9" s="123"/>
+      <c r="AD9" s="123"/>
+      <c r="AE9" s="123"/>
+      <c r="AF9" s="123"/>
+      <c r="AG9" s="123"/>
       <c r="AH9" s="138"/>
     </row>
     <row r="10" spans="2:43" ht="26.25">
-      <c r="F10" s="133" t="s">
+      <c r="F10" s="118" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="128"/>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="130" t="s">
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="130"/>
-      <c r="Q10" s="130"/>
-      <c r="R10" s="130"/>
-      <c r="S10" s="130"/>
-      <c r="T10" s="130"/>
-      <c r="U10" s="130"/>
-      <c r="V10" s="130"/>
-      <c r="W10" s="130"/>
-      <c r="X10" s="130" t="s">
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="123"/>
+      <c r="Q10" s="123"/>
+      <c r="R10" s="123"/>
+      <c r="S10" s="123"/>
+      <c r="T10" s="123"/>
+      <c r="U10" s="123"/>
+      <c r="V10" s="123"/>
+      <c r="W10" s="123"/>
+      <c r="X10" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="Y10" s="130"/>
-      <c r="Z10" s="130"/>
-      <c r="AA10" s="130"/>
-      <c r="AB10" s="130"/>
-      <c r="AC10" s="130"/>
-      <c r="AD10" s="130"/>
-      <c r="AE10" s="130"/>
-      <c r="AF10" s="130"/>
-      <c r="AG10" s="130"/>
+      <c r="Y10" s="123"/>
+      <c r="Z10" s="123"/>
+      <c r="AA10" s="123"/>
+      <c r="AB10" s="123"/>
+      <c r="AC10" s="123"/>
+      <c r="AD10" s="123"/>
+      <c r="AE10" s="123"/>
+      <c r="AF10" s="123"/>
+      <c r="AG10" s="123"/>
       <c r="AH10" s="138"/>
       <c r="AK10" s="55" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="11" spans="2:43" ht="15">
-      <c r="F11" s="133" t="s">
+      <c r="F11" s="118" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="130" t="s">
+      <c r="G11" s="119"/>
+      <c r="H11" s="119"/>
+      <c r="I11" s="119"/>
+      <c r="J11" s="119"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="119"/>
+      <c r="M11" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="N11" s="130"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="130"/>
-      <c r="R11" s="130"/>
-      <c r="S11" s="130"/>
-      <c r="T11" s="130"/>
-      <c r="U11" s="130"/>
-      <c r="V11" s="130"/>
-      <c r="W11" s="130"/>
-      <c r="X11" s="130" t="s">
+      <c r="N11" s="123"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="123"/>
+      <c r="R11" s="123"/>
+      <c r="S11" s="123"/>
+      <c r="T11" s="123"/>
+      <c r="U11" s="123"/>
+      <c r="V11" s="123"/>
+      <c r="W11" s="123"/>
+      <c r="X11" s="123" t="s">
         <v>109</v>
       </c>
-      <c r="Y11" s="130"/>
-      <c r="Z11" s="130"/>
-      <c r="AA11" s="130"/>
-      <c r="AB11" s="130"/>
-      <c r="AC11" s="130"/>
-      <c r="AD11" s="130"/>
-      <c r="AE11" s="130"/>
-      <c r="AF11" s="130"/>
-      <c r="AG11" s="130"/>
+      <c r="Y11" s="123"/>
+      <c r="Z11" s="123"/>
+      <c r="AA11" s="123"/>
+      <c r="AB11" s="123"/>
+      <c r="AC11" s="123"/>
+      <c r="AD11" s="123"/>
+      <c r="AE11" s="123"/>
+      <c r="AF11" s="123"/>
+      <c r="AG11" s="123"/>
       <c r="AH11" s="138"/>
       <c r="AL11" s="56" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="12" spans="2:43" ht="15" thickBot="1">
-      <c r="F12" s="134" t="s">
+      <c r="F12" s="120" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-      <c r="M12" s="131" t="s">
+      <c r="G12" s="121"/>
+      <c r="H12" s="121"/>
+      <c r="I12" s="121"/>
+      <c r="J12" s="121"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="121"/>
+      <c r="M12" s="126" t="s">
         <v>111</v>
       </c>
-      <c r="N12" s="131"/>
-      <c r="O12" s="131"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="131"/>
-      <c r="S12" s="131"/>
-      <c r="T12" s="131"/>
-      <c r="U12" s="131"/>
-      <c r="V12" s="131"/>
-      <c r="W12" s="131"/>
-      <c r="X12" s="131" t="s">
+      <c r="N12" s="126"/>
+      <c r="O12" s="126"/>
+      <c r="P12" s="126"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="126"/>
+      <c r="T12" s="126"/>
+      <c r="U12" s="126"/>
+      <c r="V12" s="126"/>
+      <c r="W12" s="126"/>
+      <c r="X12" s="126" t="s">
         <v>112</v>
       </c>
-      <c r="Y12" s="131"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="131"/>
-      <c r="AB12" s="131"/>
-      <c r="AC12" s="131"/>
-      <c r="AD12" s="131"/>
-      <c r="AE12" s="131"/>
-      <c r="AF12" s="131"/>
-      <c r="AG12" s="131"/>
+      <c r="Y12" s="126"/>
+      <c r="Z12" s="126"/>
+      <c r="AA12" s="126"/>
+      <c r="AB12" s="126"/>
+      <c r="AC12" s="126"/>
+      <c r="AD12" s="126"/>
+      <c r="AE12" s="126"/>
+      <c r="AF12" s="126"/>
+      <c r="AG12" s="126"/>
       <c r="AH12" s="139"/>
     </row>
     <row r="13" spans="2:43" ht="15" thickBot="1"/>
@@ -7656,6 +10998,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="M5:W5"/>
+    <mergeCell ref="M6:W6"/>
+    <mergeCell ref="M7:W7"/>
+    <mergeCell ref="M8:W8"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="F5:L5"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="F6:L6"/>
+    <mergeCell ref="F7:L7"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="F10:L10"/>
     <mergeCell ref="X11:AH11"/>
     <mergeCell ref="X12:AH12"/>
     <mergeCell ref="M12:W12"/>
@@ -7672,20 +11028,6 @@
     <mergeCell ref="M11:W11"/>
     <mergeCell ref="M3:W3"/>
     <mergeCell ref="M4:W4"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="F12:L12"/>
-    <mergeCell ref="F6:L6"/>
-    <mergeCell ref="F7:L7"/>
-    <mergeCell ref="F8:L8"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="F10:L10"/>
-    <mergeCell ref="M5:W5"/>
-    <mergeCell ref="M6:W6"/>
-    <mergeCell ref="M7:W7"/>
-    <mergeCell ref="M8:W8"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7693,8 +11035,1116 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC47467-BEE9-4A44-8F61-D0BCCE72D6DF}">
+  <dimension ref="B1:BM22"/>
+  <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="2:65" ht="15" thickBot="1">
+      <c r="B1" s="74"/>
+    </row>
+    <row r="2" spans="2:65" ht="15">
+      <c r="B2" s="154" t="s">
+        <v>360</v>
+      </c>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155"/>
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155"/>
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="155"/>
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="155"/>
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="155"/>
+      <c r="AF2" s="155"/>
+      <c r="AG2" s="155"/>
+      <c r="AH2" s="155"/>
+      <c r="AI2" s="155"/>
+      <c r="AJ2" s="155"/>
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="155"/>
+      <c r="AO2" s="155"/>
+      <c r="AP2" s="155"/>
+      <c r="AQ2" s="155"/>
+      <c r="AR2" s="155"/>
+      <c r="AS2" s="155"/>
+      <c r="AT2" s="155"/>
+      <c r="AU2" s="155"/>
+      <c r="AV2" s="155"/>
+      <c r="AW2" s="155"/>
+      <c r="AX2" s="155"/>
+      <c r="AY2" s="155"/>
+      <c r="AZ2" s="155"/>
+      <c r="BA2" s="156"/>
+    </row>
+    <row r="3" spans="2:65" ht="15.75" thickBot="1">
+      <c r="B3" s="157" t="s">
+        <v>361</v>
+      </c>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="158"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="158"/>
+      <c r="O3" s="158"/>
+      <c r="P3" s="158"/>
+      <c r="Q3" s="158"/>
+      <c r="R3" s="158"/>
+      <c r="S3" s="158"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="158"/>
+      <c r="W3" s="158"/>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="158"/>
+      <c r="Z3" s="158"/>
+      <c r="AA3" s="158"/>
+      <c r="AB3" s="158"/>
+      <c r="AC3" s="158"/>
+      <c r="AD3" s="158"/>
+      <c r="AE3" s="158"/>
+      <c r="AF3" s="158"/>
+      <c r="AG3" s="158"/>
+      <c r="AH3" s="158"/>
+      <c r="AI3" s="158"/>
+      <c r="AJ3" s="158"/>
+      <c r="AK3" s="158"/>
+      <c r="AL3" s="158"/>
+      <c r="AM3" s="158"/>
+      <c r="AN3" s="158"/>
+      <c r="AO3" s="158"/>
+      <c r="AP3" s="158"/>
+      <c r="AQ3" s="158"/>
+      <c r="AR3" s="158"/>
+      <c r="AS3" s="158"/>
+      <c r="AT3" s="158"/>
+      <c r="AU3" s="158"/>
+      <c r="AV3" s="158"/>
+      <c r="AW3" s="158"/>
+      <c r="AX3" s="158"/>
+      <c r="AY3" s="158"/>
+      <c r="AZ3" s="158"/>
+      <c r="BA3" s="159"/>
+    </row>
+    <row r="4" spans="2:65" ht="15" thickBot="1"/>
+    <row r="5" spans="2:65" ht="15">
+      <c r="C5" s="144" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145" t="s">
+        <v>301</v>
+      </c>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="145"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="145"/>
+      <c r="T5" s="145" t="s">
+        <v>302</v>
+      </c>
+      <c r="U5" s="145"/>
+      <c r="V5" s="145"/>
+      <c r="W5" s="145"/>
+      <c r="X5" s="145"/>
+      <c r="Y5" s="145"/>
+      <c r="Z5" s="145"/>
+      <c r="AA5" s="145"/>
+      <c r="AB5" s="145"/>
+      <c r="AC5" s="145"/>
+      <c r="AD5" s="145"/>
+      <c r="AE5" s="145"/>
+      <c r="AF5" s="145"/>
+      <c r="AG5" s="145" t="s">
+        <v>303</v>
+      </c>
+      <c r="AH5" s="145"/>
+      <c r="AI5" s="145"/>
+      <c r="AJ5" s="145"/>
+      <c r="AK5" s="145"/>
+      <c r="AL5" s="145"/>
+      <c r="AM5" s="145"/>
+      <c r="AN5" s="145"/>
+      <c r="AO5" s="145"/>
+      <c r="AP5" s="145"/>
+      <c r="AQ5" s="145"/>
+      <c r="AR5" s="145"/>
+      <c r="AS5" s="145"/>
+      <c r="AT5" s="145"/>
+      <c r="AU5" s="145"/>
+      <c r="AV5" s="145" t="s">
+        <v>304</v>
+      </c>
+      <c r="AW5" s="145"/>
+      <c r="AX5" s="145"/>
+      <c r="AY5" s="145"/>
+      <c r="AZ5" s="145"/>
+      <c r="BA5" s="145"/>
+      <c r="BB5" s="145"/>
+      <c r="BC5" s="145"/>
+      <c r="BD5" s="145"/>
+      <c r="BE5" s="145"/>
+      <c r="BF5" s="145"/>
+      <c r="BG5" s="145"/>
+      <c r="BH5" s="145"/>
+      <c r="BI5" s="145"/>
+      <c r="BJ5" s="145"/>
+      <c r="BK5" s="145"/>
+      <c r="BL5" s="145"/>
+      <c r="BM5" s="146"/>
+    </row>
+    <row r="6" spans="2:65" ht="15">
+      <c r="C6" s="147" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="141"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="142" t="s">
+        <v>306</v>
+      </c>
+      <c r="H6" s="142"/>
+      <c r="I6" s="142"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="142"/>
+      <c r="M6" s="142"/>
+      <c r="N6" s="142"/>
+      <c r="O6" s="142"/>
+      <c r="P6" s="142"/>
+      <c r="Q6" s="142"/>
+      <c r="R6" s="142"/>
+      <c r="S6" s="142"/>
+      <c r="T6" s="143" t="s">
+        <v>307</v>
+      </c>
+      <c r="U6" s="143"/>
+      <c r="V6" s="143"/>
+      <c r="W6" s="143"/>
+      <c r="X6" s="143"/>
+      <c r="Y6" s="143"/>
+      <c r="Z6" s="143"/>
+      <c r="AA6" s="143"/>
+      <c r="AB6" s="143"/>
+      <c r="AC6" s="143"/>
+      <c r="AD6" s="143"/>
+      <c r="AE6" s="143"/>
+      <c r="AF6" s="143"/>
+      <c r="AG6" s="143" t="s">
+        <v>308</v>
+      </c>
+      <c r="AH6" s="143"/>
+      <c r="AI6" s="143"/>
+      <c r="AJ6" s="143"/>
+      <c r="AK6" s="143"/>
+      <c r="AL6" s="143"/>
+      <c r="AM6" s="143"/>
+      <c r="AN6" s="143"/>
+      <c r="AO6" s="143"/>
+      <c r="AP6" s="143"/>
+      <c r="AQ6" s="143"/>
+      <c r="AR6" s="143"/>
+      <c r="AS6" s="143"/>
+      <c r="AT6" s="143"/>
+      <c r="AU6" s="143"/>
+      <c r="AV6" s="143" t="s">
+        <v>309</v>
+      </c>
+      <c r="AW6" s="143"/>
+      <c r="AX6" s="143"/>
+      <c r="AY6" s="143"/>
+      <c r="AZ6" s="143"/>
+      <c r="BA6" s="143"/>
+      <c r="BB6" s="143"/>
+      <c r="BC6" s="143"/>
+      <c r="BD6" s="143"/>
+      <c r="BE6" s="143"/>
+      <c r="BF6" s="143"/>
+      <c r="BG6" s="143"/>
+      <c r="BH6" s="143"/>
+      <c r="BI6" s="143"/>
+      <c r="BJ6" s="143"/>
+      <c r="BK6" s="143"/>
+      <c r="BL6" s="143"/>
+      <c r="BM6" s="148"/>
+    </row>
+    <row r="7" spans="2:65" ht="15">
+      <c r="C7" s="147" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="141"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="142" t="s">
+        <v>310</v>
+      </c>
+      <c r="H7" s="142"/>
+      <c r="I7" s="142"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="142"/>
+      <c r="M7" s="142"/>
+      <c r="N7" s="142"/>
+      <c r="O7" s="142"/>
+      <c r="P7" s="142"/>
+      <c r="Q7" s="142"/>
+      <c r="R7" s="142"/>
+      <c r="S7" s="142"/>
+      <c r="T7" s="143" t="s">
+        <v>311</v>
+      </c>
+      <c r="U7" s="143"/>
+      <c r="V7" s="143"/>
+      <c r="W7" s="143"/>
+      <c r="X7" s="143"/>
+      <c r="Y7" s="143"/>
+      <c r="Z7" s="143"/>
+      <c r="AA7" s="143"/>
+      <c r="AB7" s="143"/>
+      <c r="AC7" s="143"/>
+      <c r="AD7" s="143"/>
+      <c r="AE7" s="143"/>
+      <c r="AF7" s="143"/>
+      <c r="AG7" s="142" t="s">
+        <v>312</v>
+      </c>
+      <c r="AH7" s="142"/>
+      <c r="AI7" s="142"/>
+      <c r="AJ7" s="142"/>
+      <c r="AK7" s="142"/>
+      <c r="AL7" s="142"/>
+      <c r="AM7" s="142"/>
+      <c r="AN7" s="142"/>
+      <c r="AO7" s="142"/>
+      <c r="AP7" s="142"/>
+      <c r="AQ7" s="142"/>
+      <c r="AR7" s="142"/>
+      <c r="AS7" s="142"/>
+      <c r="AT7" s="142"/>
+      <c r="AU7" s="142"/>
+      <c r="AV7" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="AW7" s="143"/>
+      <c r="AX7" s="143"/>
+      <c r="AY7" s="143"/>
+      <c r="AZ7" s="143"/>
+      <c r="BA7" s="143"/>
+      <c r="BB7" s="143"/>
+      <c r="BC7" s="143"/>
+      <c r="BD7" s="143"/>
+      <c r="BE7" s="143"/>
+      <c r="BF7" s="143"/>
+      <c r="BG7" s="143"/>
+      <c r="BH7" s="143"/>
+      <c r="BI7" s="143"/>
+      <c r="BJ7" s="143"/>
+      <c r="BK7" s="143"/>
+      <c r="BL7" s="143"/>
+      <c r="BM7" s="148"/>
+    </row>
+    <row r="8" spans="2:65" ht="15">
+      <c r="C8" s="147" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="142" t="s">
+        <v>314</v>
+      </c>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="142"/>
+      <c r="M8" s="142"/>
+      <c r="N8" s="142"/>
+      <c r="O8" s="142"/>
+      <c r="P8" s="142"/>
+      <c r="Q8" s="142"/>
+      <c r="R8" s="142"/>
+      <c r="S8" s="142"/>
+      <c r="T8" s="143" t="s">
+        <v>315</v>
+      </c>
+      <c r="U8" s="143"/>
+      <c r="V8" s="143"/>
+      <c r="W8" s="143"/>
+      <c r="X8" s="143"/>
+      <c r="Y8" s="143"/>
+      <c r="Z8" s="143"/>
+      <c r="AA8" s="143"/>
+      <c r="AB8" s="143"/>
+      <c r="AC8" s="143"/>
+      <c r="AD8" s="143"/>
+      <c r="AE8" s="143"/>
+      <c r="AF8" s="143"/>
+      <c r="AG8" s="142" t="s">
+        <v>316</v>
+      </c>
+      <c r="AH8" s="142"/>
+      <c r="AI8" s="142"/>
+      <c r="AJ8" s="142"/>
+      <c r="AK8" s="142"/>
+      <c r="AL8" s="142"/>
+      <c r="AM8" s="142"/>
+      <c r="AN8" s="142"/>
+      <c r="AO8" s="142"/>
+      <c r="AP8" s="142"/>
+      <c r="AQ8" s="142"/>
+      <c r="AR8" s="142"/>
+      <c r="AS8" s="142"/>
+      <c r="AT8" s="142"/>
+      <c r="AU8" s="142"/>
+      <c r="AV8" s="143" t="s">
+        <v>317</v>
+      </c>
+      <c r="AW8" s="143"/>
+      <c r="AX8" s="143"/>
+      <c r="AY8" s="143"/>
+      <c r="AZ8" s="143"/>
+      <c r="BA8" s="143"/>
+      <c r="BB8" s="143"/>
+      <c r="BC8" s="143"/>
+      <c r="BD8" s="143"/>
+      <c r="BE8" s="143"/>
+      <c r="BF8" s="143"/>
+      <c r="BG8" s="143"/>
+      <c r="BH8" s="143"/>
+      <c r="BI8" s="143"/>
+      <c r="BJ8" s="143"/>
+      <c r="BK8" s="143"/>
+      <c r="BL8" s="143"/>
+      <c r="BM8" s="148"/>
+    </row>
+    <row r="9" spans="2:65" ht="15">
+      <c r="C9" s="147" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="142" t="s">
+        <v>318</v>
+      </c>
+      <c r="H9" s="142"/>
+      <c r="I9" s="142"/>
+      <c r="J9" s="142"/>
+      <c r="K9" s="142"/>
+      <c r="L9" s="142"/>
+      <c r="M9" s="142"/>
+      <c r="N9" s="142"/>
+      <c r="O9" s="142"/>
+      <c r="P9" s="142"/>
+      <c r="Q9" s="142"/>
+      <c r="R9" s="142"/>
+      <c r="S9" s="142"/>
+      <c r="T9" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="U9" s="143"/>
+      <c r="V9" s="143"/>
+      <c r="W9" s="143"/>
+      <c r="X9" s="143"/>
+      <c r="Y9" s="143"/>
+      <c r="Z9" s="143"/>
+      <c r="AA9" s="143"/>
+      <c r="AB9" s="143"/>
+      <c r="AC9" s="143"/>
+      <c r="AD9" s="143"/>
+      <c r="AE9" s="143"/>
+      <c r="AF9" s="143"/>
+      <c r="AG9" s="142" t="s">
+        <v>320</v>
+      </c>
+      <c r="AH9" s="142"/>
+      <c r="AI9" s="142"/>
+      <c r="AJ9" s="142"/>
+      <c r="AK9" s="142"/>
+      <c r="AL9" s="142"/>
+      <c r="AM9" s="142"/>
+      <c r="AN9" s="142"/>
+      <c r="AO9" s="142"/>
+      <c r="AP9" s="142"/>
+      <c r="AQ9" s="142"/>
+      <c r="AR9" s="142"/>
+      <c r="AS9" s="142"/>
+      <c r="AT9" s="142"/>
+      <c r="AU9" s="142"/>
+      <c r="AV9" s="143" t="s">
+        <v>321</v>
+      </c>
+      <c r="AW9" s="143"/>
+      <c r="AX9" s="143"/>
+      <c r="AY9" s="143"/>
+      <c r="AZ9" s="143"/>
+      <c r="BA9" s="143"/>
+      <c r="BB9" s="143"/>
+      <c r="BC9" s="143"/>
+      <c r="BD9" s="143"/>
+      <c r="BE9" s="143"/>
+      <c r="BF9" s="143"/>
+      <c r="BG9" s="143"/>
+      <c r="BH9" s="143"/>
+      <c r="BI9" s="143"/>
+      <c r="BJ9" s="143"/>
+      <c r="BK9" s="143"/>
+      <c r="BL9" s="143"/>
+      <c r="BM9" s="148"/>
+    </row>
+    <row r="10" spans="2:65" ht="15">
+      <c r="C10" s="147" t="s">
+        <v>322</v>
+      </c>
+      <c r="D10" s="141"/>
+      <c r="E10" s="141"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="142" t="s">
+        <v>323</v>
+      </c>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
+      <c r="L10" s="142"/>
+      <c r="M10" s="142"/>
+      <c r="N10" s="142"/>
+      <c r="O10" s="142"/>
+      <c r="P10" s="142"/>
+      <c r="Q10" s="142"/>
+      <c r="R10" s="142"/>
+      <c r="S10" s="142"/>
+      <c r="T10" s="143" t="s">
+        <v>324</v>
+      </c>
+      <c r="U10" s="143"/>
+      <c r="V10" s="143"/>
+      <c r="W10" s="143"/>
+      <c r="X10" s="143"/>
+      <c r="Y10" s="143"/>
+      <c r="Z10" s="143"/>
+      <c r="AA10" s="143"/>
+      <c r="AB10" s="143"/>
+      <c r="AC10" s="143"/>
+      <c r="AD10" s="143"/>
+      <c r="AE10" s="143"/>
+      <c r="AF10" s="143"/>
+      <c r="AG10" s="142" t="s">
+        <v>325</v>
+      </c>
+      <c r="AH10" s="142"/>
+      <c r="AI10" s="142"/>
+      <c r="AJ10" s="142"/>
+      <c r="AK10" s="142"/>
+      <c r="AL10" s="142"/>
+      <c r="AM10" s="142"/>
+      <c r="AN10" s="142"/>
+      <c r="AO10" s="142"/>
+      <c r="AP10" s="142"/>
+      <c r="AQ10" s="142"/>
+      <c r="AR10" s="142"/>
+      <c r="AS10" s="142"/>
+      <c r="AT10" s="142"/>
+      <c r="AU10" s="142"/>
+      <c r="AV10" s="143" t="s">
+        <v>326</v>
+      </c>
+      <c r="AW10" s="143"/>
+      <c r="AX10" s="143"/>
+      <c r="AY10" s="143"/>
+      <c r="AZ10" s="143"/>
+      <c r="BA10" s="143"/>
+      <c r="BB10" s="143"/>
+      <c r="BC10" s="143"/>
+      <c r="BD10" s="143"/>
+      <c r="BE10" s="143"/>
+      <c r="BF10" s="143"/>
+      <c r="BG10" s="143"/>
+      <c r="BH10" s="143"/>
+      <c r="BI10" s="143"/>
+      <c r="BJ10" s="143"/>
+      <c r="BK10" s="143"/>
+      <c r="BL10" s="143"/>
+      <c r="BM10" s="148"/>
+    </row>
+    <row r="11" spans="2:65" ht="15">
+      <c r="C11" s="147" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="142" t="s">
+        <v>327</v>
+      </c>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
+      <c r="N11" s="142"/>
+      <c r="O11" s="142"/>
+      <c r="P11" s="142"/>
+      <c r="Q11" s="142"/>
+      <c r="R11" s="142"/>
+      <c r="S11" s="142"/>
+      <c r="T11" s="143" t="s">
+        <v>328</v>
+      </c>
+      <c r="U11" s="143"/>
+      <c r="V11" s="143"/>
+      <c r="W11" s="143"/>
+      <c r="X11" s="143"/>
+      <c r="Y11" s="143"/>
+      <c r="Z11" s="143"/>
+      <c r="AA11" s="143"/>
+      <c r="AB11" s="143"/>
+      <c r="AC11" s="143"/>
+      <c r="AD11" s="143"/>
+      <c r="AE11" s="143"/>
+      <c r="AF11" s="143"/>
+      <c r="AG11" s="142" t="s">
+        <v>329</v>
+      </c>
+      <c r="AH11" s="142"/>
+      <c r="AI11" s="142"/>
+      <c r="AJ11" s="142"/>
+      <c r="AK11" s="142"/>
+      <c r="AL11" s="142"/>
+      <c r="AM11" s="142"/>
+      <c r="AN11" s="142"/>
+      <c r="AO11" s="142"/>
+      <c r="AP11" s="142"/>
+      <c r="AQ11" s="142"/>
+      <c r="AR11" s="142"/>
+      <c r="AS11" s="142"/>
+      <c r="AT11" s="142"/>
+      <c r="AU11" s="142"/>
+      <c r="AV11" s="143" t="s">
+        <v>330</v>
+      </c>
+      <c r="AW11" s="143"/>
+      <c r="AX11" s="143"/>
+      <c r="AY11" s="143"/>
+      <c r="AZ11" s="143"/>
+      <c r="BA11" s="143"/>
+      <c r="BB11" s="143"/>
+      <c r="BC11" s="143"/>
+      <c r="BD11" s="143"/>
+      <c r="BE11" s="143"/>
+      <c r="BF11" s="143"/>
+      <c r="BG11" s="143"/>
+      <c r="BH11" s="143"/>
+      <c r="BI11" s="143"/>
+      <c r="BJ11" s="143"/>
+      <c r="BK11" s="143"/>
+      <c r="BL11" s="143"/>
+      <c r="BM11" s="148"/>
+    </row>
+    <row r="12" spans="2:65" ht="15">
+      <c r="C12" s="147" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" s="141"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="142" t="s">
+        <v>332</v>
+      </c>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="142"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="142"/>
+      <c r="Q12" s="142"/>
+      <c r="R12" s="142"/>
+      <c r="S12" s="142"/>
+      <c r="T12" s="143" t="s">
+        <v>333</v>
+      </c>
+      <c r="U12" s="143"/>
+      <c r="V12" s="143"/>
+      <c r="W12" s="143"/>
+      <c r="X12" s="143"/>
+      <c r="Y12" s="143"/>
+      <c r="Z12" s="143"/>
+      <c r="AA12" s="143"/>
+      <c r="AB12" s="143"/>
+      <c r="AC12" s="143"/>
+      <c r="AD12" s="143"/>
+      <c r="AE12" s="143"/>
+      <c r="AF12" s="143"/>
+      <c r="AG12" s="142" t="s">
+        <v>334</v>
+      </c>
+      <c r="AH12" s="142"/>
+      <c r="AI12" s="142"/>
+      <c r="AJ12" s="142"/>
+      <c r="AK12" s="142"/>
+      <c r="AL12" s="142"/>
+      <c r="AM12" s="142"/>
+      <c r="AN12" s="142"/>
+      <c r="AO12" s="142"/>
+      <c r="AP12" s="142"/>
+      <c r="AQ12" s="142"/>
+      <c r="AR12" s="142"/>
+      <c r="AS12" s="142"/>
+      <c r="AT12" s="142"/>
+      <c r="AU12" s="142"/>
+      <c r="AV12" s="143" t="s">
+        <v>335</v>
+      </c>
+      <c r="AW12" s="143"/>
+      <c r="AX12" s="143"/>
+      <c r="AY12" s="143"/>
+      <c r="AZ12" s="143"/>
+      <c r="BA12" s="143"/>
+      <c r="BB12" s="143"/>
+      <c r="BC12" s="143"/>
+      <c r="BD12" s="143"/>
+      <c r="BE12" s="143"/>
+      <c r="BF12" s="143"/>
+      <c r="BG12" s="143"/>
+      <c r="BH12" s="143"/>
+      <c r="BI12" s="143"/>
+      <c r="BJ12" s="143"/>
+      <c r="BK12" s="143"/>
+      <c r="BL12" s="143"/>
+      <c r="BM12" s="148"/>
+    </row>
+    <row r="13" spans="2:65" ht="15">
+      <c r="C13" s="147" t="s">
+        <v>336</v>
+      </c>
+      <c r="D13" s="141"/>
+      <c r="E13" s="141"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="142" t="s">
+        <v>337</v>
+      </c>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="142"/>
+      <c r="O13" s="142"/>
+      <c r="P13" s="142"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="142"/>
+      <c r="S13" s="142"/>
+      <c r="T13" s="143" t="s">
+        <v>338</v>
+      </c>
+      <c r="U13" s="143"/>
+      <c r="V13" s="143"/>
+      <c r="W13" s="143"/>
+      <c r="X13" s="143"/>
+      <c r="Y13" s="143"/>
+      <c r="Z13" s="143"/>
+      <c r="AA13" s="143"/>
+      <c r="AB13" s="143"/>
+      <c r="AC13" s="143"/>
+      <c r="AD13" s="143"/>
+      <c r="AE13" s="143"/>
+      <c r="AF13" s="143"/>
+      <c r="AG13" s="142" t="s">
+        <v>339</v>
+      </c>
+      <c r="AH13" s="142"/>
+      <c r="AI13" s="142"/>
+      <c r="AJ13" s="142"/>
+      <c r="AK13" s="142"/>
+      <c r="AL13" s="142"/>
+      <c r="AM13" s="142"/>
+      <c r="AN13" s="142"/>
+      <c r="AO13" s="142"/>
+      <c r="AP13" s="142"/>
+      <c r="AQ13" s="142"/>
+      <c r="AR13" s="142"/>
+      <c r="AS13" s="142"/>
+      <c r="AT13" s="142"/>
+      <c r="AU13" s="142"/>
+      <c r="AV13" s="143" t="s">
+        <v>340</v>
+      </c>
+      <c r="AW13" s="143"/>
+      <c r="AX13" s="143"/>
+      <c r="AY13" s="143"/>
+      <c r="AZ13" s="143"/>
+      <c r="BA13" s="143"/>
+      <c r="BB13" s="143"/>
+      <c r="BC13" s="143"/>
+      <c r="BD13" s="143"/>
+      <c r="BE13" s="143"/>
+      <c r="BF13" s="143"/>
+      <c r="BG13" s="143"/>
+      <c r="BH13" s="143"/>
+      <c r="BI13" s="143"/>
+      <c r="BJ13" s="143"/>
+      <c r="BK13" s="143"/>
+      <c r="BL13" s="143"/>
+      <c r="BM13" s="148"/>
+    </row>
+    <row r="14" spans="2:65" ht="15">
+      <c r="C14" s="147" t="s">
+        <v>341</v>
+      </c>
+      <c r="D14" s="141"/>
+      <c r="E14" s="141"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="142" t="s">
+        <v>342</v>
+      </c>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
+      <c r="M14" s="142"/>
+      <c r="N14" s="142"/>
+      <c r="O14" s="142"/>
+      <c r="P14" s="142"/>
+      <c r="Q14" s="142"/>
+      <c r="R14" s="142"/>
+      <c r="S14" s="142"/>
+      <c r="T14" s="143" t="s">
+        <v>343</v>
+      </c>
+      <c r="U14" s="143"/>
+      <c r="V14" s="143"/>
+      <c r="W14" s="143"/>
+      <c r="X14" s="143"/>
+      <c r="Y14" s="143"/>
+      <c r="Z14" s="143"/>
+      <c r="AA14" s="143"/>
+      <c r="AB14" s="143"/>
+      <c r="AC14" s="143"/>
+      <c r="AD14" s="143"/>
+      <c r="AE14" s="143"/>
+      <c r="AF14" s="143"/>
+      <c r="AG14" s="142" t="s">
+        <v>344</v>
+      </c>
+      <c r="AH14" s="142"/>
+      <c r="AI14" s="142"/>
+      <c r="AJ14" s="142"/>
+      <c r="AK14" s="142"/>
+      <c r="AL14" s="142"/>
+      <c r="AM14" s="142"/>
+      <c r="AN14" s="142"/>
+      <c r="AO14" s="142"/>
+      <c r="AP14" s="142"/>
+      <c r="AQ14" s="142"/>
+      <c r="AR14" s="142"/>
+      <c r="AS14" s="142"/>
+      <c r="AT14" s="142"/>
+      <c r="AU14" s="142"/>
+      <c r="AV14" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="AW14" s="143"/>
+      <c r="AX14" s="143"/>
+      <c r="AY14" s="143"/>
+      <c r="AZ14" s="143"/>
+      <c r="BA14" s="143"/>
+      <c r="BB14" s="143"/>
+      <c r="BC14" s="143"/>
+      <c r="BD14" s="143"/>
+      <c r="BE14" s="143"/>
+      <c r="BF14" s="143"/>
+      <c r="BG14" s="143"/>
+      <c r="BH14" s="143"/>
+      <c r="BI14" s="143"/>
+      <c r="BJ14" s="143"/>
+      <c r="BK14" s="143"/>
+      <c r="BL14" s="143"/>
+      <c r="BM14" s="148"/>
+    </row>
+    <row r="15" spans="2:65" ht="15">
+      <c r="C15" s="147" t="s">
+        <v>346</v>
+      </c>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="142" t="s">
+        <v>347</v>
+      </c>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
+      <c r="M15" s="142"/>
+      <c r="N15" s="142"/>
+      <c r="O15" s="142"/>
+      <c r="P15" s="142"/>
+      <c r="Q15" s="142"/>
+      <c r="R15" s="142"/>
+      <c r="S15" s="142"/>
+      <c r="T15" s="143" t="s">
+        <v>348</v>
+      </c>
+      <c r="U15" s="143"/>
+      <c r="V15" s="143"/>
+      <c r="W15" s="143"/>
+      <c r="X15" s="143"/>
+      <c r="Y15" s="143"/>
+      <c r="Z15" s="143"/>
+      <c r="AA15" s="143"/>
+      <c r="AB15" s="143"/>
+      <c r="AC15" s="143"/>
+      <c r="AD15" s="143"/>
+      <c r="AE15" s="143"/>
+      <c r="AF15" s="143"/>
+      <c r="AG15" s="142" t="s">
+        <v>349</v>
+      </c>
+      <c r="AH15" s="142"/>
+      <c r="AI15" s="142"/>
+      <c r="AJ15" s="142"/>
+      <c r="AK15" s="142"/>
+      <c r="AL15" s="142"/>
+      <c r="AM15" s="142"/>
+      <c r="AN15" s="142"/>
+      <c r="AO15" s="142"/>
+      <c r="AP15" s="142"/>
+      <c r="AQ15" s="142"/>
+      <c r="AR15" s="142"/>
+      <c r="AS15" s="142"/>
+      <c r="AT15" s="142"/>
+      <c r="AU15" s="142"/>
+      <c r="AV15" s="143" t="s">
+        <v>350</v>
+      </c>
+      <c r="AW15" s="143"/>
+      <c r="AX15" s="143"/>
+      <c r="AY15" s="143"/>
+      <c r="AZ15" s="143"/>
+      <c r="BA15" s="143"/>
+      <c r="BB15" s="143"/>
+      <c r="BC15" s="143"/>
+      <c r="BD15" s="143"/>
+      <c r="BE15" s="143"/>
+      <c r="BF15" s="143"/>
+      <c r="BG15" s="143"/>
+      <c r="BH15" s="143"/>
+      <c r="BI15" s="143"/>
+      <c r="BJ15" s="143"/>
+      <c r="BK15" s="143"/>
+      <c r="BL15" s="143"/>
+      <c r="BM15" s="148"/>
+    </row>
+    <row r="16" spans="2:65" ht="15.75" thickBot="1">
+      <c r="C16" s="149" t="s">
+        <v>351</v>
+      </c>
+      <c r="D16" s="150"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="151" t="s">
+        <v>352</v>
+      </c>
+      <c r="H16" s="151"/>
+      <c r="I16" s="151"/>
+      <c r="J16" s="151"/>
+      <c r="K16" s="151"/>
+      <c r="L16" s="151"/>
+      <c r="M16" s="151"/>
+      <c r="N16" s="151"/>
+      <c r="O16" s="151"/>
+      <c r="P16" s="151"/>
+      <c r="Q16" s="151"/>
+      <c r="R16" s="151"/>
+      <c r="S16" s="151"/>
+      <c r="T16" s="152" t="s">
+        <v>353</v>
+      </c>
+      <c r="U16" s="152"/>
+      <c r="V16" s="152"/>
+      <c r="W16" s="152"/>
+      <c r="X16" s="152"/>
+      <c r="Y16" s="152"/>
+      <c r="Z16" s="152"/>
+      <c r="AA16" s="152"/>
+      <c r="AB16" s="152"/>
+      <c r="AC16" s="152"/>
+      <c r="AD16" s="152"/>
+      <c r="AE16" s="152"/>
+      <c r="AF16" s="152"/>
+      <c r="AG16" s="151" t="s">
+        <v>354</v>
+      </c>
+      <c r="AH16" s="151"/>
+      <c r="AI16" s="151"/>
+      <c r="AJ16" s="151"/>
+      <c r="AK16" s="151"/>
+      <c r="AL16" s="151"/>
+      <c r="AM16" s="151"/>
+      <c r="AN16" s="151"/>
+      <c r="AO16" s="151"/>
+      <c r="AP16" s="151"/>
+      <c r="AQ16" s="151"/>
+      <c r="AR16" s="151"/>
+      <c r="AS16" s="151"/>
+      <c r="AT16" s="151"/>
+      <c r="AU16" s="151"/>
+      <c r="AV16" s="152" t="s">
+        <v>355</v>
+      </c>
+      <c r="AW16" s="152"/>
+      <c r="AX16" s="152"/>
+      <c r="AY16" s="152"/>
+      <c r="AZ16" s="152"/>
+      <c r="BA16" s="152"/>
+      <c r="BB16" s="152"/>
+      <c r="BC16" s="152"/>
+      <c r="BD16" s="152"/>
+      <c r="BE16" s="152"/>
+      <c r="BF16" s="152"/>
+      <c r="BG16" s="152"/>
+      <c r="BH16" s="152"/>
+      <c r="BI16" s="152"/>
+      <c r="BJ16" s="152"/>
+      <c r="BK16" s="152"/>
+      <c r="BL16" s="152"/>
+      <c r="BM16" s="153"/>
+    </row>
+    <row r="19" spans="2:2" ht="17.25">
+      <c r="B19" s="76" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="15">
+      <c r="B20" s="74" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="15">
+      <c r="B21" s="74" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" ht="15">
+      <c r="B22" s="74" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="60">
+    <mergeCell ref="AV11:BM11"/>
+    <mergeCell ref="AV12:BM12"/>
+    <mergeCell ref="AV13:BM13"/>
+    <mergeCell ref="AV14:BM14"/>
+    <mergeCell ref="AV15:BM15"/>
+    <mergeCell ref="AV16:BM16"/>
+    <mergeCell ref="AV5:BM5"/>
+    <mergeCell ref="AV6:BM6"/>
+    <mergeCell ref="AV7:BM7"/>
+    <mergeCell ref="AV8:BM8"/>
+    <mergeCell ref="AV9:BM9"/>
+    <mergeCell ref="AV10:BM10"/>
+    <mergeCell ref="AG9:AU9"/>
+    <mergeCell ref="AG10:AU10"/>
+    <mergeCell ref="AG11:AU11"/>
+    <mergeCell ref="AG12:AU12"/>
+    <mergeCell ref="AG13:AU13"/>
+    <mergeCell ref="AG14:AU14"/>
+    <mergeCell ref="AG15:AU15"/>
+    <mergeCell ref="AG16:AU16"/>
+    <mergeCell ref="AG5:AU5"/>
+    <mergeCell ref="AG6:AU6"/>
+    <mergeCell ref="AG7:AU7"/>
+    <mergeCell ref="AG8:AU8"/>
+    <mergeCell ref="T11:AF11"/>
+    <mergeCell ref="T12:AF12"/>
+    <mergeCell ref="T13:AF13"/>
+    <mergeCell ref="T14:AF14"/>
+    <mergeCell ref="T15:AF15"/>
+    <mergeCell ref="T16:AF16"/>
+    <mergeCell ref="T5:AF5"/>
+    <mergeCell ref="T6:AF6"/>
+    <mergeCell ref="T7:AF7"/>
+    <mergeCell ref="T8:AF8"/>
+    <mergeCell ref="T9:AF9"/>
+    <mergeCell ref="T10:AF10"/>
+    <mergeCell ref="G15:S15"/>
+    <mergeCell ref="G16:S16"/>
+    <mergeCell ref="G9:S9"/>
+    <mergeCell ref="G10:S10"/>
+    <mergeCell ref="G11:S11"/>
+    <mergeCell ref="G12:S12"/>
+    <mergeCell ref="G13:S13"/>
+    <mergeCell ref="G14:S14"/>
+    <mergeCell ref="G5:S5"/>
+    <mergeCell ref="G6:S6"/>
+    <mergeCell ref="G7:S7"/>
+    <mergeCell ref="G8:S8"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5C6D57-9A86-4D22-90DF-F0D5383CEF40}">
-  <dimension ref="A1:BK47"/>
+  <dimension ref="A1:BL172"/>
   <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="13.9" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:63" ht="13.9" customHeight="1" thickBot="1">
@@ -8364,7 +12814,7 @@
       <c r="P32" s="88"/>
       <c r="Q32" s="89"/>
     </row>
-    <row r="33" spans="3:17" ht="13.9" customHeight="1">
+    <row r="33" spans="2:64" ht="13.9" customHeight="1">
       <c r="C33" s="96"/>
       <c r="D33" s="88"/>
       <c r="E33" s="88"/>
@@ -8381,7 +12831,7 @@
       <c r="P33" s="88"/>
       <c r="Q33" s="89"/>
     </row>
-    <row r="34" spans="3:17" ht="13.9" customHeight="1">
+    <row r="34" spans="2:64" ht="13.9" customHeight="1">
       <c r="C34" s="96" t="s">
         <v>291</v>
       </c>
@@ -8400,7 +12850,7 @@
       <c r="P34" s="88"/>
       <c r="Q34" s="89"/>
     </row>
-    <row r="35" spans="3:17" ht="13.9" customHeight="1">
+    <row r="35" spans="2:64" ht="13.9" customHeight="1">
       <c r="C35" s="97" t="s">
         <v>292</v>
       </c>
@@ -8419,7 +12869,7 @@
       <c r="P35" s="88"/>
       <c r="Q35" s="89"/>
     </row>
-    <row r="36" spans="3:17" ht="13.9" customHeight="1">
+    <row r="36" spans="2:64" ht="13.9" customHeight="1">
       <c r="C36" s="87" t="s">
         <v>293</v>
       </c>
@@ -8438,7 +12888,7 @@
       <c r="P36" s="88"/>
       <c r="Q36" s="89"/>
     </row>
-    <row r="37" spans="3:17" ht="13.9" customHeight="1">
+    <row r="37" spans="2:64" ht="13.9" customHeight="1">
       <c r="C37" s="96" t="s">
         <v>294</v>
       </c>
@@ -8457,7 +12907,7 @@
       <c r="P37" s="88"/>
       <c r="Q37" s="89"/>
     </row>
-    <row r="38" spans="3:17" ht="13.9" customHeight="1">
+    <row r="38" spans="2:64" ht="13.9" customHeight="1">
       <c r="C38" s="98" t="s">
         <v>239</v>
       </c>
@@ -8476,39 +12926,618 @@
       <c r="P38" s="92"/>
       <c r="Q38" s="93"/>
     </row>
-    <row r="40" spans="3:17" ht="13.9" customHeight="1">
+    <row r="39" spans="2:64" ht="13.9" customHeight="1">
+      <c r="BL39" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="40" spans="2:64" ht="13.9" customHeight="1">
       <c r="C40" s="73"/>
     </row>
-    <row r="42" spans="3:17" ht="13.9" customHeight="1">
+    <row r="41" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B41" t="s">
+        <v>362</v>
+      </c>
+      <c r="BL41" s="76" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="42" spans="2:64" ht="13.9" customHeight="1">
       <c r="C42" s="78"/>
       <c r="D42" s="78"/>
-    </row>
-    <row r="43" spans="3:17" ht="13.9" customHeight="1">
+      <c r="BL42" s="74"/>
+    </row>
+    <row r="43" spans="2:64" ht="13.9" customHeight="1">
       <c r="C43" s="79"/>
       <c r="D43" s="79"/>
-    </row>
-    <row r="44" spans="3:17" ht="13.9" customHeight="1">
+      <c r="BL43" s="74" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="44" spans="2:64" ht="13.9" customHeight="1">
       <c r="C44" s="79"/>
       <c r="D44" s="79"/>
-    </row>
-    <row r="45" spans="3:17" ht="13.9" customHeight="1">
+      <c r="BL44" s="74"/>
+    </row>
+    <row r="45" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B45" s="73" t="s">
+        <v>363</v>
+      </c>
       <c r="C45" s="79"/>
       <c r="D45" s="79"/>
-    </row>
-    <row r="46" spans="3:17" ht="13.9" customHeight="1">
+      <c r="BL45" s="74" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="46" spans="2:64" ht="13.9" customHeight="1">
       <c r="C46" s="79"/>
       <c r="D46" s="79"/>
-    </row>
-    <row r="47" spans="3:17" ht="13.9" customHeight="1">
+      <c r="BL46" s="74"/>
+    </row>
+    <row r="47" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B47" t="s">
+        <v>364</v>
+      </c>
       <c r="C47" s="79"/>
       <c r="D47" s="79"/>
+      <c r="BL47" s="74" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="51" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B51" s="76" t="s">
+        <v>365</v>
+      </c>
+      <c r="BL51" s="73" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="52" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B52" s="74"/>
+    </row>
+    <row r="53" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B53" s="74" t="s">
+        <v>366</v>
+      </c>
+      <c r="BL53" s="76" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="54" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B54" s="74"/>
+      <c r="BL54" s="74"/>
+    </row>
+    <row r="55" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B55" s="74" t="s">
+        <v>367</v>
+      </c>
+      <c r="BL55" s="163" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="56" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B56" s="74"/>
+      <c r="BL56" s="74"/>
+    </row>
+    <row r="57" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B57" s="74"/>
+      <c r="BL57" s="163" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="58" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B58" s="160"/>
+      <c r="BL58" s="74"/>
+    </row>
+    <row r="59" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B59" s="160" t="s">
+        <v>368</v>
+      </c>
+      <c r="BL59" s="163" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="60" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B60" s="160"/>
+      <c r="BL60" s="74" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="61" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B61" s="160" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="62" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B62" s="160"/>
+    </row>
+    <row r="63" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B63" s="160" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="64" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B64" s="74"/>
+      <c r="BL64" s="76" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="65" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B65" s="74" t="s">
+        <v>371</v>
+      </c>
+      <c r="BL65" s="74"/>
+    </row>
+    <row r="66" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B66" s="74"/>
+      <c r="BL66" s="163" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="67" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B67" s="82" t="s">
+        <v>372</v>
+      </c>
+      <c r="BL67" s="74"/>
+    </row>
+    <row r="68" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B68" s="74"/>
+      <c r="BL68" s="163" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="69" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B69" s="74"/>
+      <c r="BL69" s="74" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="70" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B70" s="160"/>
+    </row>
+    <row r="71" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B71" s="160" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="72" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B72" s="160"/>
+    </row>
+    <row r="73" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B73" s="160" t="s">
+        <v>374</v>
+      </c>
+      <c r="BL73" s="76" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="74" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B74" s="160"/>
+      <c r="BL74" s="74"/>
+    </row>
+    <row r="75" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B75" s="160" t="s">
+        <v>375</v>
+      </c>
+      <c r="BL75" s="163" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="76" spans="2:64" ht="13.9" customHeight="1">
+      <c r="BL76" s="74" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="77" spans="2:64" ht="13.9" customHeight="1">
+      <c r="BL77" s="74"/>
+    </row>
+    <row r="78" spans="2:64" ht="13.9" customHeight="1">
+      <c r="BL78" s="163" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="79" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B79" s="76" t="s">
+        <v>376</v>
+      </c>
+      <c r="BL79" s="74" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="80" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B80" s="74"/>
+    </row>
+    <row r="81" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B81" s="74" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="82" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B82" s="74"/>
+    </row>
+    <row r="83" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B83" s="74" t="s">
+        <v>378</v>
+      </c>
+      <c r="BL83" s="76" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="84" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B84" s="74"/>
+      <c r="BL84" s="74"/>
+    </row>
+    <row r="85" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B85" s="74"/>
+      <c r="BL85" s="163" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="86" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B86" s="160"/>
+      <c r="BL86" s="74"/>
+    </row>
+    <row r="87" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B87" s="160" t="s">
+        <v>379</v>
+      </c>
+      <c r="BL87" s="163" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="88" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B88" s="160"/>
+    </row>
+    <row r="89" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B89" s="160" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="90" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B90" s="160"/>
+    </row>
+    <row r="91" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B91" s="160" t="s">
+        <v>381</v>
+      </c>
+      <c r="BL91" s="76" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="92" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B92" s="160"/>
+      <c r="BL92" s="74"/>
+    </row>
+    <row r="93" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B93" s="161" t="s">
+        <v>382</v>
+      </c>
+      <c r="BL93" s="163" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="94" spans="2:64" ht="13.9" customHeight="1">
+      <c r="BL94" s="74" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="95" spans="2:64" ht="13.9" customHeight="1">
+      <c r="BL95" s="74" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="97" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B97" s="76" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="98" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B98" s="74"/>
+    </row>
+    <row r="99" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B99" s="74" t="s">
+        <v>384</v>
+      </c>
+      <c r="BL99" s="76" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="100" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B100" s="74"/>
+      <c r="BL100" s="74"/>
+    </row>
+    <row r="101" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B101" s="74" t="s">
+        <v>385</v>
+      </c>
+      <c r="BL101" s="163" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="102" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B102" s="74"/>
+      <c r="BL102" s="74" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="103" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B103" s="74"/>
+      <c r="BL103" s="74" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="104" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B104" s="160"/>
+    </row>
+    <row r="105" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B105" s="160" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="106" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B106" s="160"/>
+    </row>
+    <row r="107" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B107" s="160" t="s">
+        <v>387</v>
+      </c>
+      <c r="BL107" s="76" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="108" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B108" s="160"/>
+      <c r="BL108" s="74"/>
+    </row>
+    <row r="109" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B109" s="160"/>
+      <c r="BL109" s="163" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="110" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B110" s="162"/>
+      <c r="BL110" s="74"/>
+    </row>
+    <row r="111" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B111" s="162" t="s">
+        <v>388</v>
+      </c>
+      <c r="BL111" s="74" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="112" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B112" s="162"/>
+    </row>
+    <row r="113" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B113" s="162" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="114" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B114" s="74"/>
+    </row>
+    <row r="115" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B115" s="82" t="s">
+        <v>372</v>
+      </c>
+      <c r="BL115" s="76" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="116" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B116" s="74"/>
+    </row>
+    <row r="117" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B117" s="74"/>
+      <c r="BL117" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="118" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B118" s="160"/>
+      <c r="BL118" s="74"/>
+    </row>
+    <row r="119" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B119" s="160" t="s">
+        <v>390</v>
+      </c>
+      <c r="BL119" s="163" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="120" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B120" s="160"/>
+      <c r="BL120" s="74"/>
+    </row>
+    <row r="121" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B121" s="160" t="s">
+        <v>391</v>
+      </c>
+      <c r="BL121" s="163" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="122" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B122" s="160"/>
+      <c r="BL122" s="74"/>
+    </row>
+    <row r="123" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B123" s="160" t="s">
+        <v>392</v>
+      </c>
+      <c r="BL123" s="163" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="124" spans="2:64" ht="13.9" customHeight="1">
+      <c r="BL124" s="74" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="127" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B127" s="76" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="128" spans="2:64" ht="13.9" customHeight="1">
+      <c r="B128" s="74"/>
+      <c r="BL128" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B129" s="74" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B130" s="74"/>
+    </row>
+    <row r="131" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B131" s="74" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B132" s="74"/>
+    </row>
+    <row r="133" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B133" s="74"/>
+    </row>
+    <row r="134" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B134" s="160"/>
+    </row>
+    <row r="135" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B135" s="161" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B136" s="160"/>
+    </row>
+    <row r="137" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B137" s="161" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B138" s="74"/>
+    </row>
+    <row r="139" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B139" s="74" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B143" s="73" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B145" s="75" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B146" s="75" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B147" s="75" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B148" s="75" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B149" s="75" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B150" s="75" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B151" s="75" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B152" s="75" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B153" s="75" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B154" s="75" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B158" s="73" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B159" s="74"/>
+    </row>
+    <row r="160" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B160" s="74" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B164" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B165" s="74"/>
+    </row>
+    <row r="166" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B166" s="74" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B167" s="74"/>
+    </row>
+    <row r="168" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B168" s="74" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B169" s="74"/>
+    </row>
+    <row r="170" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B170" s="74" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" ht="13.9" customHeight="1">
+      <c r="B172" t="s">
+        <v>416</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:E63"/>
   <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="14.25"/>
@@ -8781,13 +13810,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC47467-BEE9-4A44-8F61-D0BCCE72D6DF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="14.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/BaseTraining/unit13_protocall.bus.controller_driver/unit13_protocall.bus.controller_driver.xlsx
+++ b/BaseTraining/unit13_protocall.bus.controller_driver/unit13_protocall.bus.controller_driver.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14283197-0FEF-4E1F-ABA6-9A1752FFBB05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5694A1-D5A0-4888-9062-8C3D75633145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Các loại driver" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="362">
   <si>
     <t>1. Đọc document trong linux kernel</t>
   </si>
@@ -3849,1923 +3849,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> sử dụng giao tiếp qua loại bus đó.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dưới đây là phiên bản mô tả lại ý hiểu của bạn một cách </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>chính xác, rõ ràng và sát với kiến trúc thật của Linux kernel driver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <t>🧠 Ý Hiểu Chính Xác Về Kiến Trúc Driver Trong Linux Kernel</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kiến trúc driver trong Linux được chia thành </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nhiều tầng</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, mỗi tầng đảm nhận một vai trò cụ thể nhằm đảm bảo tính </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>modular</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>portable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>reusable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Cụ thể:</t>
-    </r>
-  </si>
-  <si>
-    <t>🧩 Tầng 1: Bus Controller Drivers</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Đây là các </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>driver điều khiển phần cứng controller/host</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quản lý các loại bus như UART, I2C, SPI.</t>
-    </r>
-  </si>
-  <si>
-    <t>Chúng chịu trách nhiệm:</t>
-  </si>
-  <si>
-    <t>Khởi tạo controller</t>
-  </si>
-  <si>
-    <t>Điều khiển truyền nhận dữ liệu</t>
-  </si>
-  <si>
-    <t>Cung cấp các callback/hook cho core sử dụng</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Thường được viết dưới dạng </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>platform driver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> nếu controller tích hợp trên SoC (on-chip).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ví dụ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">UART: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>8250</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>pl011</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I2C: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>designware-i2c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>imx-i2c</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SPI: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dw-spi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>pl022</t>
-    </r>
-  </si>
-  <si>
-    <t>🧠 Tầng 2: Subsystem Core Layer</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Là </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>phần cốt lõi</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> của từng subsystem (UART/I2C/SPI) – chứa logic chung.</t>
-    </r>
-  </si>
-  <si>
-    <t>Nhiệm vụ:</t>
-  </si>
-  <si>
-    <t>Quản lý danh sách controller drivers và device drivers</t>
-  </si>
-  <si>
-    <t>Quét và match device ↔ driver</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cung cấp </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>APIs chuẩn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho device drivers sử dụng để giao tiếp với controller</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>(Tùy subsystem)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Có thể tạo các node </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/dev/...</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hoặc đăng ký vào các subsystem khác như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>input</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>rtc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>hwmon</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>...</t>
-    </r>
-  </si>
-  <si>
-    <t>🔌 Tầng 3: Device Drivers</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tương ứng với </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>các thiết bị ngoại vi cụ thể</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> kết nối qua bus (I2C/SPI/UART).</t>
-    </r>
-  </si>
-  <si>
-    <t>Mỗi device driver sử dụng APIs do core cung cấp để:</t>
-  </si>
-  <si>
-    <t>Gửi/nhận dữ liệu thông qua controller</t>
-  </si>
-  <si>
-    <t>Tùy subsystem, có thể:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tạo node </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/dev/...</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để giao tiếp với userspace</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Hoặc đăng ký vào subsystem như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>input</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>rtc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>hwmon</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>net</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>block</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>…</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I2C: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>rtc-ds1307</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>tmp102</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>eeprom</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">SPI: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>spidev</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>oled display</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>adc</t>
-    </r>
-  </si>
-  <si>
-    <t>UART: ít device driver riêng, chủ yếu dùng qua TTY layer</t>
-  </si>
-  <si>
-    <t>👤 Tầng 4: Giao diện Userspace</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Giao diện mà </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>user application</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> có thể truy cập bằng các lệnh như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>open()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>read()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>write()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ioctl()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Ứng dụng giao tiếp qua:</t>
-  </si>
-  <si>
-    <r>
-      <t>/dev/...</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: khi device tạo character/block device</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>/sys/...</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: khi thiết bị chỉ xuất hiện dưới dạng attribute</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nhờ tầng core và driver, ứng dụng có thể hoạt động </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>mà không cần biết controller cụ thể là gì</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>🔁 Luồng hoạt động tổng quát:</t>
-  </si>
-  <si>
-    <t>[User App]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ↓ system calls (open, read...)</t>
-  </si>
-  <si>
-    <t>[/dev/ttyS0 or /dev/i2c-1 or /sys/...]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ↓</t>
-  </si>
-  <si>
-    <t>[Core Layer (i2c-core.c, uart-core.c...)]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ↓       ↓</t>
-  </si>
-  <si>
-    <t>[Controller Driver]   [Device Driver]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   (pl011)               (ds1307)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ↓                       ↓</t>
-  </si>
-  <si>
-    <t>[Hardware controller]    [Peripheral Device]</t>
-  </si>
-  <si>
-    <t>✅ Tóm tắt lại ý hiểu của bạn:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bạn đã hiểu rất đúng cách mà </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linux kernel tách biệt phần điều khiển controller (host)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>phần điều khiển thiết bị (device)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, qua một tầng </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>core trung gian</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Việc tạo ra </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/dev</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, xử lý </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>system calls</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, match driver/device và cung cấp APIs là nhiệm vụ của tầng core. Nhờ vậy, các device driver có thể hoạt động được với nhiều loại controller khác nhau, và người dùng không cần quan tâm đến phần cứng cụ thể phía dưới.</t>
-    </r>
-  </si>
-  <si>
-    <t>Nếu bạn cần, mình có thể tiếp tục:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Giải thích rõ cách hoạt động của </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>platform bus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>device tree</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, hay </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ACPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> khi binding driver ↔ device</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Phân tích cụ thể hơn các ví dụ như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>rtc-ds1307</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>spidev</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, hay </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>8250</t>
-    </r>
-  </si>
-  <si>
-    <t>Hoặc hướng dẫn bạn tự viết một driver đơn giản</t>
-  </si>
-  <si>
-    <t>Bạn muốn đi tiếp hướng nào?</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Core layer trong Linux driver architecture là nơi chứa </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>logic trung gian</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> giữa controller drivers và device drivers — nó </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>không tương tác trực tiếp với phần cứng</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, nhưng cung cấp </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>API chuẩn, cơ chế đăng ký/match, quản lý device, tạo sysfs/dev entries</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, v.v.</t>
-    </r>
-  </si>
-  <si>
-    <t>📂 Các file trong Core Layer thường có các đặc điểm:</t>
-  </si>
-  <si>
-    <r>
-      <t>Nằm trong thư mục subsystem tương ứng (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>drivers/i2c/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>drivers/spi/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>drivers/tty/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, ...)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tên file thường chứa chữ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>core</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, hoặc là một file trung tâm điều phối.</t>
-    </r>
-  </si>
-  <si>
-    <t>Không gắn với phần cứng cụ thể (hardware-agnostic).</t>
-  </si>
-  <si>
-    <t>📚 Danh sách Core Layer file phổ biến theo subsystem</t>
-  </si>
-  <si>
-    <t>🔹 I2C:</t>
-  </si>
-  <si>
-    <t>drivers/i2c/i2c-core-base.c</t>
-  </si>
-  <si>
-    <t>drivers/i2c/i2c-core-of.c</t>
-  </si>
-  <si>
-    <t>drivers/i2c/i2c-core-smbus.c</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">⤷ Chứa API như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>i2c_add_adapter()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>i2c_add_driver()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>i2c_transfer()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>of_i2c_register_devices()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>...</t>
-    </r>
-  </si>
-  <si>
-    <t>🔹 SPI:</t>
-  </si>
-  <si>
-    <t>drivers/spi/spi.c</t>
-  </si>
-  <si>
-    <t>drivers/spi/spi-master.c</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">⤷ Chứa các API như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>spi_register_driver()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>spi_sync()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>spi_new_device()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>...</t>
-    </r>
-  </si>
-  <si>
-    <t>🔹 UART / Serial:</t>
-  </si>
-  <si>
-    <t>drivers/tty/serial/serial_core.c</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">⤷ Cung cấp API chuẩn như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>uart_register_driver()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>uart_write()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>uart_tx()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>drivers/tty/tty_io.c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>tty_core.c</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">⤷ Cốt lõi của TTY subsystem, quản lý </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/dev/tty*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, xử lý input/output</t>
-    </r>
-  </si>
-  <si>
-    <t>🔹 Input subsystem (cho các driver bàn phím, touch, button...):</t>
-  </si>
-  <si>
-    <t>drivers/input/input.c</t>
-  </si>
-  <si>
-    <r>
-      <t>drivers/input/evdev.c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (tạo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/dev/input/eventX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>🔹 RTC:</t>
-  </si>
-  <si>
-    <t>drivers/rtc/rtc-core.c</t>
-  </si>
-  <si>
-    <t>⤷ Đăng ký thiết bị RTC, quản lý callbacks từ các rtc driver</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">⤷ API: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>rtc_register_device()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>rtc_read_time()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>rtc_set_time()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>...</t>
-    </r>
-  </si>
-  <si>
-    <t>🔹 HWMon (sensor nhiệt độ, điện áp...):</t>
-  </si>
-  <si>
-    <t>drivers/hwmon/hwmon.c</t>
-  </si>
-  <si>
-    <t>⤷ API cho driver sensor đăng ký</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">⤷ Tạo file trong </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>/sys/class/hwmon/...</t>
-    </r>
-  </si>
-  <si>
-    <t>🔹 Block (cho MMC, SD, USB mass storage...):</t>
-  </si>
-  <si>
-    <r>
-      <t>drivers/block/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (nhiều file core như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>genhd.c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>partitions/core.c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Các subsystem như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>drivers/mmc/core/mmc_core.c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cũng là core layer</t>
-    </r>
-  </si>
-  <si>
-    <t>✅ Nhận diện Core Layer:</t>
-  </si>
-  <si>
-    <t>Bạn có thể xem code và nếu thấy các hàm như:</t>
-  </si>
-  <si>
-    <r>
-      <t>*_register_driver()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>*_add_driver()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>device_register()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>bus_register()</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>sysfs_create_*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dev_set_drvdata()</t>
-    </r>
-  </si>
-  <si>
-    <t>Thì nhiều khả năng bạn đang nhìn vào phần Core Layer.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Nếu bạn cần danh sách file core tương ứng cho một </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>subsystem cụ thể</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, ví dụ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>USB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>PCI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Sound</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>Media</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, mình có thể liệt kê chi tiết hơn. Bạn muốn subsystem nào?</t>
     </r>
   </si>
 </sst>
@@ -5773,7 +3856,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5861,6 +3944,19 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -6316,7 +4412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -6479,138 +4575,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -6632,6 +4596,147 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7065,50 +5170,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>56</xdr:col>
-      <xdr:colOff>161924</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>20480</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>71</xdr:col>
-      <xdr:colOff>143617</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>96128</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11896724" y="13545980"/>
-          <a:ext cx="3124943" cy="3695148"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>60</xdr:col>
       <xdr:colOff>1891</xdr:colOff>
       <xdr:row>113</xdr:row>
@@ -7118,7 +5179,7 @@
       <xdr:col>84</xdr:col>
       <xdr:colOff>168937</xdr:colOff>
       <xdr:row>130</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:rowOff>161923</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7134,7 +5195,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7178,7 +5239,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7222,7 +5283,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7757,60 +5818,60 @@
     </row>
     <row r="11" spans="1:82" ht="15" thickBot="1"/>
     <row r="12" spans="1:82" ht="15">
-      <c r="D12" s="107" t="s">
+      <c r="D12" s="124" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106" t="s">
+      <c r="E12" s="122"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="122"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="122"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="106"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="106"/>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="106"/>
-      <c r="T12" s="106"/>
-      <c r="U12" s="106"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="106"/>
-      <c r="X12" s="106"/>
-      <c r="Y12" s="106"/>
-      <c r="Z12" s="106"/>
-      <c r="AA12" s="106"/>
-      <c r="AB12" s="106"/>
-      <c r="AC12" s="106"/>
-      <c r="AD12" s="106"/>
-      <c r="AE12" s="106"/>
-      <c r="AF12" s="106"/>
-      <c r="AG12" s="106"/>
-      <c r="AH12" s="106" t="s">
+      <c r="M12" s="122"/>
+      <c r="N12" s="122"/>
+      <c r="O12" s="122"/>
+      <c r="P12" s="122"/>
+      <c r="Q12" s="122"/>
+      <c r="R12" s="122"/>
+      <c r="S12" s="122"/>
+      <c r="T12" s="122"/>
+      <c r="U12" s="122"/>
+      <c r="V12" s="122"/>
+      <c r="W12" s="122"/>
+      <c r="X12" s="122"/>
+      <c r="Y12" s="122"/>
+      <c r="Z12" s="122"/>
+      <c r="AA12" s="122"/>
+      <c r="AB12" s="122"/>
+      <c r="AC12" s="122"/>
+      <c r="AD12" s="122"/>
+      <c r="AE12" s="122"/>
+      <c r="AF12" s="122"/>
+      <c r="AG12" s="122"/>
+      <c r="AH12" s="122" t="s">
         <v>208</v>
       </c>
-      <c r="AI12" s="106"/>
-      <c r="AJ12" s="106"/>
-      <c r="AK12" s="106"/>
-      <c r="AL12" s="106"/>
-      <c r="AM12" s="106"/>
-      <c r="AN12" s="106"/>
-      <c r="AO12" s="106"/>
-      <c r="AP12" s="106"/>
-      <c r="AQ12" s="106"/>
-      <c r="AR12" s="106"/>
-      <c r="AS12" s="106"/>
-      <c r="AT12" s="106"/>
-      <c r="AU12" s="106"/>
-      <c r="AV12" s="106"/>
-      <c r="AW12" s="106"/>
-      <c r="AX12" s="106"/>
-      <c r="AY12" s="106"/>
+      <c r="AI12" s="122"/>
+      <c r="AJ12" s="122"/>
+      <c r="AK12" s="122"/>
+      <c r="AL12" s="122"/>
+      <c r="AM12" s="122"/>
+      <c r="AN12" s="122"/>
+      <c r="AO12" s="122"/>
+      <c r="AP12" s="122"/>
+      <c r="AQ12" s="122"/>
+      <c r="AR12" s="122"/>
+      <c r="AS12" s="122"/>
+      <c r="AT12" s="122"/>
+      <c r="AU12" s="122"/>
+      <c r="AV12" s="122"/>
+      <c r="AW12" s="122"/>
+      <c r="AX12" s="122"/>
+      <c r="AY12" s="122"/>
       <c r="AZ12" s="127" t="s">
         <v>40</v>
       </c>
@@ -7825,60 +5886,60 @@
       <c r="BI12" s="128"/>
     </row>
     <row r="13" spans="1:82" ht="29.45" customHeight="1">
-      <c r="D13" s="110" t="s">
+      <c r="D13" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="115" t="s">
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="118" t="s">
         <v>205</v>
       </c>
-      <c r="M13" s="115"/>
-      <c r="N13" s="115"/>
-      <c r="O13" s="115"/>
-      <c r="P13" s="115"/>
-      <c r="Q13" s="115"/>
-      <c r="R13" s="115"/>
-      <c r="S13" s="115"/>
-      <c r="T13" s="115"/>
-      <c r="U13" s="115"/>
-      <c r="V13" s="115"/>
-      <c r="W13" s="115"/>
-      <c r="X13" s="115"/>
-      <c r="Y13" s="115"/>
-      <c r="Z13" s="115"/>
-      <c r="AA13" s="115"/>
-      <c r="AB13" s="115"/>
-      <c r="AC13" s="115"/>
-      <c r="AD13" s="115"/>
-      <c r="AE13" s="115"/>
-      <c r="AF13" s="115"/>
-      <c r="AG13" s="115"/>
-      <c r="AH13" s="113" t="s">
+      <c r="M13" s="118"/>
+      <c r="N13" s="118"/>
+      <c r="O13" s="118"/>
+      <c r="P13" s="118"/>
+      <c r="Q13" s="118"/>
+      <c r="R13" s="118"/>
+      <c r="S13" s="118"/>
+      <c r="T13" s="118"/>
+      <c r="U13" s="118"/>
+      <c r="V13" s="118"/>
+      <c r="W13" s="118"/>
+      <c r="X13" s="118"/>
+      <c r="Y13" s="118"/>
+      <c r="Z13" s="118"/>
+      <c r="AA13" s="118"/>
+      <c r="AB13" s="118"/>
+      <c r="AC13" s="118"/>
+      <c r="AD13" s="118"/>
+      <c r="AE13" s="118"/>
+      <c r="AF13" s="118"/>
+      <c r="AG13" s="118"/>
+      <c r="AH13" s="147" t="s">
         <v>210</v>
       </c>
-      <c r="AI13" s="113"/>
-      <c r="AJ13" s="113"/>
-      <c r="AK13" s="113"/>
-      <c r="AL13" s="113"/>
-      <c r="AM13" s="113"/>
-      <c r="AN13" s="113"/>
-      <c r="AO13" s="113"/>
-      <c r="AP13" s="113"/>
-      <c r="AQ13" s="113"/>
-      <c r="AR13" s="113"/>
-      <c r="AS13" s="113"/>
-      <c r="AT13" s="113"/>
-      <c r="AU13" s="113"/>
-      <c r="AV13" s="113"/>
-      <c r="AW13" s="113"/>
-      <c r="AX13" s="113"/>
-      <c r="AY13" s="113"/>
+      <c r="AI13" s="147"/>
+      <c r="AJ13" s="147"/>
+      <c r="AK13" s="147"/>
+      <c r="AL13" s="147"/>
+      <c r="AM13" s="147"/>
+      <c r="AN13" s="147"/>
+      <c r="AO13" s="147"/>
+      <c r="AP13" s="147"/>
+      <c r="AQ13" s="147"/>
+      <c r="AR13" s="147"/>
+      <c r="AS13" s="147"/>
+      <c r="AT13" s="147"/>
+      <c r="AU13" s="147"/>
+      <c r="AV13" s="147"/>
+      <c r="AW13" s="147"/>
+      <c r="AX13" s="147"/>
+      <c r="AY13" s="147"/>
       <c r="AZ13" s="129" t="s">
         <v>43</v>
       </c>
@@ -7916,60 +5977,60 @@
       <c r="CD13" s="57"/>
     </row>
     <row r="14" spans="1:82" ht="30" customHeight="1">
-      <c r="D14" s="110" t="s">
+      <c r="D14" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="115" t="s">
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="118" t="s">
         <v>219</v>
       </c>
-      <c r="M14" s="115"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="115"/>
-      <c r="P14" s="115"/>
-      <c r="Q14" s="115"/>
-      <c r="R14" s="115"/>
-      <c r="S14" s="115"/>
-      <c r="T14" s="115"/>
-      <c r="U14" s="115"/>
-      <c r="V14" s="115"/>
-      <c r="W14" s="115"/>
-      <c r="X14" s="115"/>
-      <c r="Y14" s="115"/>
-      <c r="Z14" s="115"/>
-      <c r="AA14" s="115"/>
-      <c r="AB14" s="115"/>
-      <c r="AC14" s="115"/>
-      <c r="AD14" s="115"/>
-      <c r="AE14" s="115"/>
-      <c r="AF14" s="115"/>
-      <c r="AG14" s="115"/>
-      <c r="AH14" s="113" t="s">
+      <c r="M14" s="118"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="118"/>
+      <c r="T14" s="118"/>
+      <c r="U14" s="118"/>
+      <c r="V14" s="118"/>
+      <c r="W14" s="118"/>
+      <c r="X14" s="118"/>
+      <c r="Y14" s="118"/>
+      <c r="Z14" s="118"/>
+      <c r="AA14" s="118"/>
+      <c r="AB14" s="118"/>
+      <c r="AC14" s="118"/>
+      <c r="AD14" s="118"/>
+      <c r="AE14" s="118"/>
+      <c r="AF14" s="118"/>
+      <c r="AG14" s="118"/>
+      <c r="AH14" s="147" t="s">
         <v>209</v>
       </c>
-      <c r="AI14" s="113"/>
-      <c r="AJ14" s="113"/>
-      <c r="AK14" s="113"/>
-      <c r="AL14" s="113"/>
-      <c r="AM14" s="113"/>
-      <c r="AN14" s="113"/>
-      <c r="AO14" s="113"/>
-      <c r="AP14" s="113"/>
-      <c r="AQ14" s="113"/>
-      <c r="AR14" s="113"/>
-      <c r="AS14" s="113"/>
-      <c r="AT14" s="113"/>
-      <c r="AU14" s="113"/>
-      <c r="AV14" s="113"/>
-      <c r="AW14" s="113"/>
-      <c r="AX14" s="113"/>
-      <c r="AY14" s="113"/>
+      <c r="AI14" s="147"/>
+      <c r="AJ14" s="147"/>
+      <c r="AK14" s="147"/>
+      <c r="AL14" s="147"/>
+      <c r="AM14" s="147"/>
+      <c r="AN14" s="147"/>
+      <c r="AO14" s="147"/>
+      <c r="AP14" s="147"/>
+      <c r="AQ14" s="147"/>
+      <c r="AR14" s="147"/>
+      <c r="AS14" s="147"/>
+      <c r="AT14" s="147"/>
+      <c r="AU14" s="147"/>
+      <c r="AV14" s="147"/>
+      <c r="AW14" s="147"/>
+      <c r="AX14" s="147"/>
+      <c r="AY14" s="147"/>
       <c r="AZ14" s="129" t="s">
         <v>41</v>
       </c>
@@ -8007,60 +6068,60 @@
       <c r="CD14" s="57"/>
     </row>
     <row r="15" spans="1:82" ht="28.9" customHeight="1" thickBot="1">
-      <c r="D15" s="108" t="s">
+      <c r="D15" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="114" t="s">
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="121"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="123" t="s">
         <v>206</v>
       </c>
-      <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="114"/>
-      <c r="S15" s="114"/>
-      <c r="T15" s="114"/>
-      <c r="U15" s="114"/>
-      <c r="V15" s="114"/>
-      <c r="W15" s="114"/>
-      <c r="X15" s="114"/>
-      <c r="Y15" s="114"/>
-      <c r="Z15" s="114"/>
-      <c r="AA15" s="114"/>
-      <c r="AB15" s="114"/>
-      <c r="AC15" s="114"/>
-      <c r="AD15" s="114"/>
-      <c r="AE15" s="114"/>
-      <c r="AF15" s="114"/>
-      <c r="AG15" s="114"/>
-      <c r="AH15" s="112" t="s">
+      <c r="M15" s="123"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="123"/>
+      <c r="S15" s="123"/>
+      <c r="T15" s="123"/>
+      <c r="U15" s="123"/>
+      <c r="V15" s="123"/>
+      <c r="W15" s="123"/>
+      <c r="X15" s="123"/>
+      <c r="Y15" s="123"/>
+      <c r="Z15" s="123"/>
+      <c r="AA15" s="123"/>
+      <c r="AB15" s="123"/>
+      <c r="AC15" s="123"/>
+      <c r="AD15" s="123"/>
+      <c r="AE15" s="123"/>
+      <c r="AF15" s="123"/>
+      <c r="AG15" s="123"/>
+      <c r="AH15" s="146" t="s">
         <v>211</v>
       </c>
-      <c r="AI15" s="112"/>
-      <c r="AJ15" s="112"/>
-      <c r="AK15" s="112"/>
-      <c r="AL15" s="112"/>
-      <c r="AM15" s="112"/>
-      <c r="AN15" s="112"/>
-      <c r="AO15" s="112"/>
-      <c r="AP15" s="112"/>
-      <c r="AQ15" s="112"/>
-      <c r="AR15" s="112"/>
-      <c r="AS15" s="112"/>
-      <c r="AT15" s="112"/>
-      <c r="AU15" s="112"/>
-      <c r="AV15" s="112"/>
-      <c r="AW15" s="112"/>
-      <c r="AX15" s="112"/>
-      <c r="AY15" s="112"/>
+      <c r="AI15" s="146"/>
+      <c r="AJ15" s="146"/>
+      <c r="AK15" s="146"/>
+      <c r="AL15" s="146"/>
+      <c r="AM15" s="146"/>
+      <c r="AN15" s="146"/>
+      <c r="AO15" s="146"/>
+      <c r="AP15" s="146"/>
+      <c r="AQ15" s="146"/>
+      <c r="AR15" s="146"/>
+      <c r="AS15" s="146"/>
+      <c r="AT15" s="146"/>
+      <c r="AU15" s="146"/>
+      <c r="AV15" s="146"/>
+      <c r="AW15" s="146"/>
+      <c r="AX15" s="146"/>
+      <c r="AY15" s="146"/>
       <c r="AZ15" s="131" t="s">
         <v>42</v>
       </c>
@@ -8217,53 +6278,53 @@
     </row>
     <row r="26" spans="1:70" ht="15" thickBot="1"/>
     <row r="27" spans="1:70" ht="15">
-      <c r="D27" s="116" t="s">
+      <c r="D27" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="122" t="s">
+      <c r="E27" s="135"/>
+      <c r="F27" s="135"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="122"/>
-      <c r="K27" s="122"/>
-      <c r="L27" s="122"/>
-      <c r="M27" s="122"/>
-      <c r="N27" s="122"/>
-      <c r="O27" s="122"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="117" t="s">
+      <c r="J27" s="145"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="145"/>
+      <c r="M27" s="145"/>
+      <c r="N27" s="145"/>
+      <c r="O27" s="145"/>
+      <c r="P27" s="145"/>
+      <c r="Q27" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="R27" s="117"/>
-      <c r="S27" s="117"/>
-      <c r="T27" s="117"/>
-      <c r="U27" s="117"/>
-      <c r="V27" s="117"/>
-      <c r="W27" s="117"/>
-      <c r="X27" s="117"/>
-      <c r="Y27" s="117"/>
-      <c r="Z27" s="117"/>
-      <c r="AA27" s="117"/>
-      <c r="AB27" s="117"/>
-      <c r="AC27" s="117"/>
-      <c r="AD27" s="117" t="s">
+      <c r="R27" s="135"/>
+      <c r="S27" s="135"/>
+      <c r="T27" s="135"/>
+      <c r="U27" s="135"/>
+      <c r="V27" s="135"/>
+      <c r="W27" s="135"/>
+      <c r="X27" s="135"/>
+      <c r="Y27" s="135"/>
+      <c r="Z27" s="135"/>
+      <c r="AA27" s="135"/>
+      <c r="AB27" s="135"/>
+      <c r="AC27" s="135"/>
+      <c r="AD27" s="135" t="s">
         <v>27</v>
       </c>
-      <c r="AE27" s="117"/>
-      <c r="AF27" s="117"/>
-      <c r="AG27" s="117"/>
-      <c r="AH27" s="117"/>
-      <c r="AI27" s="117"/>
-      <c r="AJ27" s="117"/>
-      <c r="AK27" s="117"/>
-      <c r="AL27" s="117"/>
-      <c r="AM27" s="117"/>
-      <c r="AN27" s="117"/>
-      <c r="AO27" s="117"/>
-      <c r="AP27" s="117"/>
+      <c r="AE27" s="135"/>
+      <c r="AF27" s="135"/>
+      <c r="AG27" s="135"/>
+      <c r="AH27" s="135"/>
+      <c r="AI27" s="135"/>
+      <c r="AJ27" s="135"/>
+      <c r="AK27" s="135"/>
+      <c r="AL27" s="135"/>
+      <c r="AM27" s="135"/>
+      <c r="AN27" s="135"/>
+      <c r="AO27" s="135"/>
+      <c r="AP27" s="135"/>
       <c r="AQ27" s="127" t="s">
         <v>40</v>
       </c>
@@ -8280,67 +6341,67 @@
       <c r="BB27" s="128"/>
     </row>
     <row r="28" spans="1:70">
-      <c r="D28" s="118" t="s">
+      <c r="D28" s="143" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="119"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="123" t="s">
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="138" t="s">
         <v>29</v>
       </c>
-      <c r="J28" s="123"/>
-      <c r="K28" s="123"/>
-      <c r="L28" s="123"/>
-      <c r="M28" s="123"/>
-      <c r="N28" s="123"/>
-      <c r="O28" s="123"/>
-      <c r="P28" s="123"/>
-      <c r="Q28" s="119" t="s">
+      <c r="J28" s="138"/>
+      <c r="K28" s="138"/>
+      <c r="L28" s="138"/>
+      <c r="M28" s="138"/>
+      <c r="N28" s="138"/>
+      <c r="O28" s="138"/>
+      <c r="P28" s="138"/>
+      <c r="Q28" s="136" t="s">
         <v>30</v>
       </c>
-      <c r="R28" s="119"/>
-      <c r="S28" s="119"/>
-      <c r="T28" s="119"/>
-      <c r="U28" s="119"/>
-      <c r="V28" s="119"/>
-      <c r="W28" s="119"/>
-      <c r="X28" s="119"/>
-      <c r="Y28" s="119"/>
-      <c r="Z28" s="119"/>
-      <c r="AA28" s="119"/>
-      <c r="AB28" s="119"/>
-      <c r="AC28" s="119"/>
-      <c r="AD28" s="123" t="s">
+      <c r="R28" s="136"/>
+      <c r="S28" s="136"/>
+      <c r="T28" s="136"/>
+      <c r="U28" s="136"/>
+      <c r="V28" s="136"/>
+      <c r="W28" s="136"/>
+      <c r="X28" s="136"/>
+      <c r="Y28" s="136"/>
+      <c r="Z28" s="136"/>
+      <c r="AA28" s="136"/>
+      <c r="AB28" s="136"/>
+      <c r="AC28" s="136"/>
+      <c r="AD28" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="AE28" s="123"/>
-      <c r="AF28" s="123"/>
-      <c r="AG28" s="123"/>
-      <c r="AH28" s="123"/>
-      <c r="AI28" s="123"/>
-      <c r="AJ28" s="123"/>
-      <c r="AK28" s="123"/>
-      <c r="AL28" s="123"/>
-      <c r="AM28" s="123"/>
-      <c r="AN28" s="123"/>
-      <c r="AO28" s="123"/>
-      <c r="AP28" s="123"/>
-      <c r="AQ28" s="124" t="s">
+      <c r="AE28" s="138"/>
+      <c r="AF28" s="138"/>
+      <c r="AG28" s="138"/>
+      <c r="AH28" s="138"/>
+      <c r="AI28" s="138"/>
+      <c r="AJ28" s="138"/>
+      <c r="AK28" s="138"/>
+      <c r="AL28" s="138"/>
+      <c r="AM28" s="138"/>
+      <c r="AN28" s="138"/>
+      <c r="AO28" s="138"/>
+      <c r="AP28" s="138"/>
+      <c r="AQ28" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="AR28" s="124"/>
-      <c r="AS28" s="124"/>
-      <c r="AT28" s="124"/>
-      <c r="AU28" s="124"/>
-      <c r="AV28" s="124"/>
-      <c r="AW28" s="124"/>
-      <c r="AX28" s="124"/>
-      <c r="AY28" s="124"/>
-      <c r="AZ28" s="124"/>
-      <c r="BA28" s="124"/>
-      <c r="BB28" s="125"/>
+      <c r="AR28" s="133"/>
+      <c r="AS28" s="133"/>
+      <c r="AT28" s="133"/>
+      <c r="AU28" s="133"/>
+      <c r="AV28" s="133"/>
+      <c r="AW28" s="133"/>
+      <c r="AX28" s="133"/>
+      <c r="AY28" s="133"/>
+      <c r="AZ28" s="133"/>
+      <c r="BA28" s="133"/>
+      <c r="BB28" s="134"/>
       <c r="BC28" s="13" t="s">
         <v>48</v>
       </c>
@@ -8361,67 +6422,67 @@
       <c r="BR28" s="13"/>
     </row>
     <row r="29" spans="1:70">
-      <c r="D29" s="118" t="s">
+      <c r="D29" s="143" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="123" t="s">
+      <c r="E29" s="136"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="136"/>
+      <c r="I29" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="J29" s="123"/>
-      <c r="K29" s="123"/>
-      <c r="L29" s="123"/>
-      <c r="M29" s="123"/>
-      <c r="N29" s="123"/>
-      <c r="O29" s="123"/>
-      <c r="P29" s="123"/>
-      <c r="Q29" s="119" t="s">
+      <c r="J29" s="138"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="138"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="138"/>
+      <c r="Q29" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="R29" s="119"/>
-      <c r="S29" s="119"/>
-      <c r="T29" s="119"/>
-      <c r="U29" s="119"/>
-      <c r="V29" s="119"/>
-      <c r="W29" s="119"/>
-      <c r="X29" s="119"/>
-      <c r="Y29" s="119"/>
-      <c r="Z29" s="119"/>
-      <c r="AA29" s="119"/>
-      <c r="AB29" s="119"/>
-      <c r="AC29" s="119"/>
-      <c r="AD29" s="123" t="s">
+      <c r="R29" s="136"/>
+      <c r="S29" s="136"/>
+      <c r="T29" s="136"/>
+      <c r="U29" s="136"/>
+      <c r="V29" s="136"/>
+      <c r="W29" s="136"/>
+      <c r="X29" s="136"/>
+      <c r="Y29" s="136"/>
+      <c r="Z29" s="136"/>
+      <c r="AA29" s="136"/>
+      <c r="AB29" s="136"/>
+      <c r="AC29" s="136"/>
+      <c r="AD29" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="AE29" s="123"/>
-      <c r="AF29" s="123"/>
-      <c r="AG29" s="123"/>
-      <c r="AH29" s="123"/>
-      <c r="AI29" s="123"/>
-      <c r="AJ29" s="123"/>
-      <c r="AK29" s="123"/>
-      <c r="AL29" s="123"/>
-      <c r="AM29" s="123"/>
-      <c r="AN29" s="123"/>
-      <c r="AO29" s="123"/>
-      <c r="AP29" s="123"/>
-      <c r="AQ29" s="124" t="s">
+      <c r="AE29" s="138"/>
+      <c r="AF29" s="138"/>
+      <c r="AG29" s="138"/>
+      <c r="AH29" s="138"/>
+      <c r="AI29" s="138"/>
+      <c r="AJ29" s="138"/>
+      <c r="AK29" s="138"/>
+      <c r="AL29" s="138"/>
+      <c r="AM29" s="138"/>
+      <c r="AN29" s="138"/>
+      <c r="AO29" s="138"/>
+      <c r="AP29" s="138"/>
+      <c r="AQ29" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="AR29" s="124"/>
-      <c r="AS29" s="124"/>
-      <c r="AT29" s="124"/>
-      <c r="AU29" s="124"/>
-      <c r="AV29" s="124"/>
-      <c r="AW29" s="124"/>
-      <c r="AX29" s="124"/>
-      <c r="AY29" s="124"/>
-      <c r="AZ29" s="124"/>
-      <c r="BA29" s="124"/>
-      <c r="BB29" s="125"/>
+      <c r="AR29" s="133"/>
+      <c r="AS29" s="133"/>
+      <c r="AT29" s="133"/>
+      <c r="AU29" s="133"/>
+      <c r="AV29" s="133"/>
+      <c r="AW29" s="133"/>
+      <c r="AX29" s="133"/>
+      <c r="AY29" s="133"/>
+      <c r="AZ29" s="133"/>
+      <c r="BA29" s="133"/>
+      <c r="BB29" s="134"/>
       <c r="BC29" s="13" t="s">
         <v>49</v>
       </c>
@@ -8442,67 +6503,67 @@
       <c r="BR29" s="13"/>
     </row>
     <row r="30" spans="1:70" ht="15" thickBot="1">
-      <c r="D30" s="120" t="s">
+      <c r="D30" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="121"/>
-      <c r="F30" s="121"/>
-      <c r="G30" s="121"/>
-      <c r="H30" s="121"/>
-      <c r="I30" s="121" t="s">
+      <c r="E30" s="137"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="137"/>
+      <c r="I30" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="J30" s="121"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="121"/>
-      <c r="Q30" s="121" t="s">
+      <c r="J30" s="137"/>
+      <c r="K30" s="137"/>
+      <c r="L30" s="137"/>
+      <c r="M30" s="137"/>
+      <c r="N30" s="137"/>
+      <c r="O30" s="137"/>
+      <c r="P30" s="137"/>
+      <c r="Q30" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="R30" s="121"/>
-      <c r="S30" s="121"/>
-      <c r="T30" s="121"/>
-      <c r="U30" s="121"/>
-      <c r="V30" s="121"/>
-      <c r="W30" s="121"/>
-      <c r="X30" s="121"/>
-      <c r="Y30" s="121"/>
-      <c r="Z30" s="121"/>
-      <c r="AA30" s="121"/>
-      <c r="AB30" s="121"/>
-      <c r="AC30" s="121"/>
-      <c r="AD30" s="126" t="s">
+      <c r="R30" s="137"/>
+      <c r="S30" s="137"/>
+      <c r="T30" s="137"/>
+      <c r="U30" s="137"/>
+      <c r="V30" s="137"/>
+      <c r="W30" s="137"/>
+      <c r="X30" s="137"/>
+      <c r="Y30" s="137"/>
+      <c r="Z30" s="137"/>
+      <c r="AA30" s="137"/>
+      <c r="AB30" s="137"/>
+      <c r="AC30" s="137"/>
+      <c r="AD30" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="AE30" s="126"/>
-      <c r="AF30" s="126"/>
-      <c r="AG30" s="126"/>
-      <c r="AH30" s="126"/>
-      <c r="AI30" s="126"/>
-      <c r="AJ30" s="126"/>
-      <c r="AK30" s="126"/>
-      <c r="AL30" s="126"/>
-      <c r="AM30" s="126"/>
-      <c r="AN30" s="126"/>
-      <c r="AO30" s="126"/>
-      <c r="AP30" s="126"/>
-      <c r="AQ30" s="133" t="s">
+      <c r="AE30" s="139"/>
+      <c r="AF30" s="139"/>
+      <c r="AG30" s="139"/>
+      <c r="AH30" s="139"/>
+      <c r="AI30" s="139"/>
+      <c r="AJ30" s="139"/>
+      <c r="AK30" s="139"/>
+      <c r="AL30" s="139"/>
+      <c r="AM30" s="139"/>
+      <c r="AN30" s="139"/>
+      <c r="AO30" s="139"/>
+      <c r="AP30" s="139"/>
+      <c r="AQ30" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="AR30" s="133"/>
-      <c r="AS30" s="133"/>
-      <c r="AT30" s="133"/>
-      <c r="AU30" s="133"/>
-      <c r="AV30" s="133"/>
-      <c r="AW30" s="133"/>
-      <c r="AX30" s="133"/>
-      <c r="AY30" s="133"/>
-      <c r="AZ30" s="133"/>
-      <c r="BA30" s="133"/>
-      <c r="BB30" s="134"/>
+      <c r="AR30" s="140"/>
+      <c r="AS30" s="140"/>
+      <c r="AT30" s="140"/>
+      <c r="AU30" s="140"/>
+      <c r="AV30" s="140"/>
+      <c r="AW30" s="140"/>
+      <c r="AX30" s="140"/>
+      <c r="AY30" s="140"/>
+      <c r="AZ30" s="140"/>
+      <c r="BA30" s="140"/>
+      <c r="BB30" s="141"/>
       <c r="BC30" s="13" t="s">
         <v>50</v>
       </c>
@@ -8531,796 +6592,796 @@
     </row>
     <row r="33" spans="1:68" ht="15" thickBot="1"/>
     <row r="34" spans="1:68" ht="15">
-      <c r="E34" s="107" t="s">
+      <c r="E34" s="124" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
-      <c r="I34" s="106"/>
-      <c r="J34" s="106"/>
-      <c r="K34" s="106"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="106"/>
-      <c r="N34" s="106"/>
-      <c r="O34" s="106"/>
-      <c r="P34" s="106"/>
-      <c r="Q34" s="106"/>
-      <c r="R34" s="106" t="s">
+      <c r="F34" s="122"/>
+      <c r="G34" s="122"/>
+      <c r="H34" s="122"/>
+      <c r="I34" s="122"/>
+      <c r="J34" s="122"/>
+      <c r="K34" s="122"/>
+      <c r="L34" s="122"/>
+      <c r="M34" s="122"/>
+      <c r="N34" s="122"/>
+      <c r="O34" s="122"/>
+      <c r="P34" s="122"/>
+      <c r="Q34" s="122"/>
+      <c r="R34" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="S34" s="106"/>
-      <c r="T34" s="106"/>
-      <c r="U34" s="106"/>
-      <c r="V34" s="106"/>
-      <c r="W34" s="106"/>
-      <c r="X34" s="106"/>
-      <c r="Y34" s="106"/>
-      <c r="Z34" s="106"/>
-      <c r="AA34" s="106"/>
-      <c r="AB34" s="106"/>
-      <c r="AC34" s="106"/>
-      <c r="AD34" s="106"/>
-      <c r="AE34" s="106"/>
-      <c r="AF34" s="106"/>
-      <c r="AG34" s="106"/>
-      <c r="AH34" s="106"/>
-      <c r="AI34" s="106"/>
-      <c r="AJ34" s="106"/>
-      <c r="AK34" s="106"/>
-      <c r="AL34" s="106"/>
-      <c r="AM34" s="106"/>
-      <c r="AN34" s="106"/>
-      <c r="AO34" s="106"/>
-      <c r="AP34" s="106" t="s">
+      <c r="S34" s="122"/>
+      <c r="T34" s="122"/>
+      <c r="U34" s="122"/>
+      <c r="V34" s="122"/>
+      <c r="W34" s="122"/>
+      <c r="X34" s="122"/>
+      <c r="Y34" s="122"/>
+      <c r="Z34" s="122"/>
+      <c r="AA34" s="122"/>
+      <c r="AB34" s="122"/>
+      <c r="AC34" s="122"/>
+      <c r="AD34" s="122"/>
+      <c r="AE34" s="122"/>
+      <c r="AF34" s="122"/>
+      <c r="AG34" s="122"/>
+      <c r="AH34" s="122"/>
+      <c r="AI34" s="122"/>
+      <c r="AJ34" s="122"/>
+      <c r="AK34" s="122"/>
+      <c r="AL34" s="122"/>
+      <c r="AM34" s="122"/>
+      <c r="AN34" s="122"/>
+      <c r="AO34" s="122"/>
+      <c r="AP34" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="AQ34" s="106"/>
-      <c r="AR34" s="106"/>
-      <c r="AS34" s="106"/>
-      <c r="AT34" s="106"/>
-      <c r="AU34" s="106"/>
-      <c r="AV34" s="106"/>
-      <c r="AW34" s="106"/>
-      <c r="AX34" s="106"/>
-      <c r="AY34" s="106"/>
-      <c r="AZ34" s="106"/>
-      <c r="BA34" s="106"/>
-      <c r="BB34" s="106"/>
-      <c r="BC34" s="106"/>
-      <c r="BD34" s="106"/>
-      <c r="BE34" s="106"/>
-      <c r="BF34" s="106"/>
-      <c r="BG34" s="106"/>
-      <c r="BH34" s="106"/>
-      <c r="BI34" s="106"/>
-      <c r="BJ34" s="106"/>
-      <c r="BK34" s="106"/>
-      <c r="BL34" s="106"/>
-      <c r="BM34" s="106"/>
-      <c r="BN34" s="106"/>
-      <c r="BO34" s="106"/>
-      <c r="BP34" s="137"/>
+      <c r="AQ34" s="122"/>
+      <c r="AR34" s="122"/>
+      <c r="AS34" s="122"/>
+      <c r="AT34" s="122"/>
+      <c r="AU34" s="122"/>
+      <c r="AV34" s="122"/>
+      <c r="AW34" s="122"/>
+      <c r="AX34" s="122"/>
+      <c r="AY34" s="122"/>
+      <c r="AZ34" s="122"/>
+      <c r="BA34" s="122"/>
+      <c r="BB34" s="122"/>
+      <c r="BC34" s="122"/>
+      <c r="BD34" s="122"/>
+      <c r="BE34" s="122"/>
+      <c r="BF34" s="122"/>
+      <c r="BG34" s="122"/>
+      <c r="BH34" s="122"/>
+      <c r="BI34" s="122"/>
+      <c r="BJ34" s="122"/>
+      <c r="BK34" s="122"/>
+      <c r="BL34" s="122"/>
+      <c r="BM34" s="122"/>
+      <c r="BN34" s="122"/>
+      <c r="BO34" s="122"/>
+      <c r="BP34" s="126"/>
     </row>
     <row r="35" spans="1:68" ht="15">
-      <c r="E35" s="110" t="s">
+      <c r="E35" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="111"/>
-      <c r="G35" s="111"/>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="115" t="s">
+      <c r="F35" s="117"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="117"/>
+      <c r="I35" s="117"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="117"/>
+      <c r="L35" s="117"/>
+      <c r="M35" s="117"/>
+      <c r="N35" s="117"/>
+      <c r="O35" s="117"/>
+      <c r="P35" s="117"/>
+      <c r="Q35" s="117"/>
+      <c r="R35" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="S35" s="115"/>
-      <c r="T35" s="115"/>
-      <c r="U35" s="115"/>
-      <c r="V35" s="115"/>
-      <c r="W35" s="115"/>
-      <c r="X35" s="115"/>
-      <c r="Y35" s="115"/>
-      <c r="Z35" s="115"/>
-      <c r="AA35" s="115"/>
-      <c r="AB35" s="115"/>
-      <c r="AC35" s="115"/>
-      <c r="AD35" s="115"/>
-      <c r="AE35" s="115"/>
-      <c r="AF35" s="115"/>
-      <c r="AG35" s="115"/>
-      <c r="AH35" s="115"/>
-      <c r="AI35" s="115"/>
-      <c r="AJ35" s="115"/>
-      <c r="AK35" s="115"/>
-      <c r="AL35" s="115"/>
-      <c r="AM35" s="115"/>
-      <c r="AN35" s="115"/>
-      <c r="AO35" s="115"/>
-      <c r="AP35" s="115" t="s">
+      <c r="S35" s="118"/>
+      <c r="T35" s="118"/>
+      <c r="U35" s="118"/>
+      <c r="V35" s="118"/>
+      <c r="W35" s="118"/>
+      <c r="X35" s="118"/>
+      <c r="Y35" s="118"/>
+      <c r="Z35" s="118"/>
+      <c r="AA35" s="118"/>
+      <c r="AB35" s="118"/>
+      <c r="AC35" s="118"/>
+      <c r="AD35" s="118"/>
+      <c r="AE35" s="118"/>
+      <c r="AF35" s="118"/>
+      <c r="AG35" s="118"/>
+      <c r="AH35" s="118"/>
+      <c r="AI35" s="118"/>
+      <c r="AJ35" s="118"/>
+      <c r="AK35" s="118"/>
+      <c r="AL35" s="118"/>
+      <c r="AM35" s="118"/>
+      <c r="AN35" s="118"/>
+      <c r="AO35" s="118"/>
+      <c r="AP35" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="AQ35" s="115"/>
-      <c r="AR35" s="115"/>
-      <c r="AS35" s="115"/>
-      <c r="AT35" s="115"/>
-      <c r="AU35" s="115"/>
-      <c r="AV35" s="115"/>
-      <c r="AW35" s="115"/>
-      <c r="AX35" s="115"/>
-      <c r="AY35" s="115"/>
-      <c r="AZ35" s="115"/>
-      <c r="BA35" s="115"/>
-      <c r="BB35" s="115"/>
-      <c r="BC35" s="115"/>
-      <c r="BD35" s="115"/>
-      <c r="BE35" s="115"/>
-      <c r="BF35" s="115"/>
-      <c r="BG35" s="115"/>
-      <c r="BH35" s="115"/>
-      <c r="BI35" s="115"/>
-      <c r="BJ35" s="115"/>
-      <c r="BK35" s="115"/>
-      <c r="BL35" s="115"/>
-      <c r="BM35" s="115"/>
-      <c r="BN35" s="115"/>
-      <c r="BO35" s="115"/>
-      <c r="BP35" s="136"/>
+      <c r="AQ35" s="118"/>
+      <c r="AR35" s="118"/>
+      <c r="AS35" s="118"/>
+      <c r="AT35" s="118"/>
+      <c r="AU35" s="118"/>
+      <c r="AV35" s="118"/>
+      <c r="AW35" s="118"/>
+      <c r="AX35" s="118"/>
+      <c r="AY35" s="118"/>
+      <c r="AZ35" s="118"/>
+      <c r="BA35" s="118"/>
+      <c r="BB35" s="118"/>
+      <c r="BC35" s="118"/>
+      <c r="BD35" s="118"/>
+      <c r="BE35" s="118"/>
+      <c r="BF35" s="118"/>
+      <c r="BG35" s="118"/>
+      <c r="BH35" s="118"/>
+      <c r="BI35" s="118"/>
+      <c r="BJ35" s="118"/>
+      <c r="BK35" s="118"/>
+      <c r="BL35" s="118"/>
+      <c r="BM35" s="118"/>
+      <c r="BN35" s="118"/>
+      <c r="BO35" s="118"/>
+      <c r="BP35" s="119"/>
     </row>
     <row r="36" spans="1:68" ht="15">
-      <c r="E36" s="110" t="s">
+      <c r="E36" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="115" t="s">
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="117"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="117"/>
+      <c r="N36" s="117"/>
+      <c r="O36" s="117"/>
+      <c r="P36" s="117"/>
+      <c r="Q36" s="117"/>
+      <c r="R36" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="S36" s="115"/>
-      <c r="T36" s="115"/>
-      <c r="U36" s="115"/>
-      <c r="V36" s="115"/>
-      <c r="W36" s="115"/>
-      <c r="X36" s="115"/>
-      <c r="Y36" s="115"/>
-      <c r="Z36" s="115"/>
-      <c r="AA36" s="115"/>
-      <c r="AB36" s="115"/>
-      <c r="AC36" s="115"/>
-      <c r="AD36" s="115"/>
-      <c r="AE36" s="115"/>
-      <c r="AF36" s="115"/>
-      <c r="AG36" s="115"/>
-      <c r="AH36" s="115"/>
-      <c r="AI36" s="115"/>
-      <c r="AJ36" s="115"/>
-      <c r="AK36" s="115"/>
-      <c r="AL36" s="115"/>
-      <c r="AM36" s="115"/>
-      <c r="AN36" s="115"/>
-      <c r="AO36" s="115"/>
-      <c r="AP36" s="115" t="s">
+      <c r="S36" s="118"/>
+      <c r="T36" s="118"/>
+      <c r="U36" s="118"/>
+      <c r="V36" s="118"/>
+      <c r="W36" s="118"/>
+      <c r="X36" s="118"/>
+      <c r="Y36" s="118"/>
+      <c r="Z36" s="118"/>
+      <c r="AA36" s="118"/>
+      <c r="AB36" s="118"/>
+      <c r="AC36" s="118"/>
+      <c r="AD36" s="118"/>
+      <c r="AE36" s="118"/>
+      <c r="AF36" s="118"/>
+      <c r="AG36" s="118"/>
+      <c r="AH36" s="118"/>
+      <c r="AI36" s="118"/>
+      <c r="AJ36" s="118"/>
+      <c r="AK36" s="118"/>
+      <c r="AL36" s="118"/>
+      <c r="AM36" s="118"/>
+      <c r="AN36" s="118"/>
+      <c r="AO36" s="118"/>
+      <c r="AP36" s="118" t="s">
         <v>60</v>
       </c>
-      <c r="AQ36" s="115"/>
-      <c r="AR36" s="115"/>
-      <c r="AS36" s="115"/>
-      <c r="AT36" s="115"/>
-      <c r="AU36" s="115"/>
-      <c r="AV36" s="115"/>
-      <c r="AW36" s="115"/>
-      <c r="AX36" s="115"/>
-      <c r="AY36" s="115"/>
-      <c r="AZ36" s="115"/>
-      <c r="BA36" s="115"/>
-      <c r="BB36" s="115"/>
-      <c r="BC36" s="115"/>
-      <c r="BD36" s="115"/>
-      <c r="BE36" s="115"/>
-      <c r="BF36" s="115"/>
-      <c r="BG36" s="115"/>
-      <c r="BH36" s="115"/>
-      <c r="BI36" s="115"/>
-      <c r="BJ36" s="115"/>
-      <c r="BK36" s="115"/>
-      <c r="BL36" s="115"/>
-      <c r="BM36" s="115"/>
-      <c r="BN36" s="115"/>
-      <c r="BO36" s="115"/>
-      <c r="BP36" s="136"/>
+      <c r="AQ36" s="118"/>
+      <c r="AR36" s="118"/>
+      <c r="AS36" s="118"/>
+      <c r="AT36" s="118"/>
+      <c r="AU36" s="118"/>
+      <c r="AV36" s="118"/>
+      <c r="AW36" s="118"/>
+      <c r="AX36" s="118"/>
+      <c r="AY36" s="118"/>
+      <c r="AZ36" s="118"/>
+      <c r="BA36" s="118"/>
+      <c r="BB36" s="118"/>
+      <c r="BC36" s="118"/>
+      <c r="BD36" s="118"/>
+      <c r="BE36" s="118"/>
+      <c r="BF36" s="118"/>
+      <c r="BG36" s="118"/>
+      <c r="BH36" s="118"/>
+      <c r="BI36" s="118"/>
+      <c r="BJ36" s="118"/>
+      <c r="BK36" s="118"/>
+      <c r="BL36" s="118"/>
+      <c r="BM36" s="118"/>
+      <c r="BN36" s="118"/>
+      <c r="BO36" s="118"/>
+      <c r="BP36" s="119"/>
     </row>
     <row r="37" spans="1:68" ht="15">
-      <c r="E37" s="110" t="s">
+      <c r="E37" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="F37" s="111"/>
-      <c r="G37" s="111"/>
-      <c r="H37" s="111"/>
-      <c r="I37" s="111"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="111"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="111"/>
-      <c r="N37" s="111"/>
-      <c r="O37" s="111"/>
-      <c r="P37" s="111"/>
-      <c r="Q37" s="111"/>
-      <c r="R37" s="115" t="s">
+      <c r="F37" s="117"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+      <c r="I37" s="117"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="117"/>
+      <c r="L37" s="117"/>
+      <c r="M37" s="117"/>
+      <c r="N37" s="117"/>
+      <c r="O37" s="117"/>
+      <c r="P37" s="117"/>
+      <c r="Q37" s="117"/>
+      <c r="R37" s="118" t="s">
         <v>62</v>
       </c>
-      <c r="S37" s="115"/>
-      <c r="T37" s="115"/>
-      <c r="U37" s="115"/>
-      <c r="V37" s="115"/>
-      <c r="W37" s="115"/>
-      <c r="X37" s="115"/>
-      <c r="Y37" s="115"/>
-      <c r="Z37" s="115"/>
-      <c r="AA37" s="115"/>
-      <c r="AB37" s="115"/>
-      <c r="AC37" s="115"/>
-      <c r="AD37" s="115"/>
-      <c r="AE37" s="115"/>
-      <c r="AF37" s="115"/>
-      <c r="AG37" s="115"/>
-      <c r="AH37" s="115"/>
-      <c r="AI37" s="115"/>
-      <c r="AJ37" s="115"/>
-      <c r="AK37" s="115"/>
-      <c r="AL37" s="115"/>
-      <c r="AM37" s="115"/>
-      <c r="AN37" s="115"/>
-      <c r="AO37" s="115"/>
-      <c r="AP37" s="115" t="s">
+      <c r="S37" s="118"/>
+      <c r="T37" s="118"/>
+      <c r="U37" s="118"/>
+      <c r="V37" s="118"/>
+      <c r="W37" s="118"/>
+      <c r="X37" s="118"/>
+      <c r="Y37" s="118"/>
+      <c r="Z37" s="118"/>
+      <c r="AA37" s="118"/>
+      <c r="AB37" s="118"/>
+      <c r="AC37" s="118"/>
+      <c r="AD37" s="118"/>
+      <c r="AE37" s="118"/>
+      <c r="AF37" s="118"/>
+      <c r="AG37" s="118"/>
+      <c r="AH37" s="118"/>
+      <c r="AI37" s="118"/>
+      <c r="AJ37" s="118"/>
+      <c r="AK37" s="118"/>
+      <c r="AL37" s="118"/>
+      <c r="AM37" s="118"/>
+      <c r="AN37" s="118"/>
+      <c r="AO37" s="118"/>
+      <c r="AP37" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="AQ37" s="115"/>
-      <c r="AR37" s="115"/>
-      <c r="AS37" s="115"/>
-      <c r="AT37" s="115"/>
-      <c r="AU37" s="115"/>
-      <c r="AV37" s="115"/>
-      <c r="AW37" s="115"/>
-      <c r="AX37" s="115"/>
-      <c r="AY37" s="115"/>
-      <c r="AZ37" s="115"/>
-      <c r="BA37" s="115"/>
-      <c r="BB37" s="115"/>
-      <c r="BC37" s="115"/>
-      <c r="BD37" s="115"/>
-      <c r="BE37" s="115"/>
-      <c r="BF37" s="115"/>
-      <c r="BG37" s="115"/>
-      <c r="BH37" s="115"/>
-      <c r="BI37" s="115"/>
-      <c r="BJ37" s="115"/>
-      <c r="BK37" s="115"/>
-      <c r="BL37" s="115"/>
-      <c r="BM37" s="115"/>
-      <c r="BN37" s="115"/>
-      <c r="BO37" s="115"/>
-      <c r="BP37" s="136"/>
+      <c r="AQ37" s="118"/>
+      <c r="AR37" s="118"/>
+      <c r="AS37" s="118"/>
+      <c r="AT37" s="118"/>
+      <c r="AU37" s="118"/>
+      <c r="AV37" s="118"/>
+      <c r="AW37" s="118"/>
+      <c r="AX37" s="118"/>
+      <c r="AY37" s="118"/>
+      <c r="AZ37" s="118"/>
+      <c r="BA37" s="118"/>
+      <c r="BB37" s="118"/>
+      <c r="BC37" s="118"/>
+      <c r="BD37" s="118"/>
+      <c r="BE37" s="118"/>
+      <c r="BF37" s="118"/>
+      <c r="BG37" s="118"/>
+      <c r="BH37" s="118"/>
+      <c r="BI37" s="118"/>
+      <c r="BJ37" s="118"/>
+      <c r="BK37" s="118"/>
+      <c r="BL37" s="118"/>
+      <c r="BM37" s="118"/>
+      <c r="BN37" s="118"/>
+      <c r="BO37" s="118"/>
+      <c r="BP37" s="119"/>
     </row>
     <row r="38" spans="1:68" ht="15">
-      <c r="E38" s="110" t="s">
+      <c r="E38" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="F38" s="111"/>
-      <c r="G38" s="111"/>
-      <c r="H38" s="111"/>
-      <c r="I38" s="111"/>
-      <c r="J38" s="111"/>
-      <c r="K38" s="111"/>
-      <c r="L38" s="111"/>
-      <c r="M38" s="111"/>
-      <c r="N38" s="111"/>
-      <c r="O38" s="111"/>
-      <c r="P38" s="111"/>
-      <c r="Q38" s="111"/>
-      <c r="R38" s="115" t="s">
+      <c r="F38" s="117"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="117"/>
+      <c r="I38" s="117"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="117"/>
+      <c r="L38" s="117"/>
+      <c r="M38" s="117"/>
+      <c r="N38" s="117"/>
+      <c r="O38" s="117"/>
+      <c r="P38" s="117"/>
+      <c r="Q38" s="117"/>
+      <c r="R38" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="S38" s="115"/>
-      <c r="T38" s="115"/>
-      <c r="U38" s="115"/>
-      <c r="V38" s="115"/>
-      <c r="W38" s="115"/>
-      <c r="X38" s="115"/>
-      <c r="Y38" s="115"/>
-      <c r="Z38" s="115"/>
-      <c r="AA38" s="115"/>
-      <c r="AB38" s="115"/>
-      <c r="AC38" s="115"/>
-      <c r="AD38" s="115"/>
-      <c r="AE38" s="115"/>
-      <c r="AF38" s="115"/>
-      <c r="AG38" s="115"/>
-      <c r="AH38" s="115"/>
-      <c r="AI38" s="115"/>
-      <c r="AJ38" s="115"/>
-      <c r="AK38" s="115"/>
-      <c r="AL38" s="115"/>
-      <c r="AM38" s="115"/>
-      <c r="AN38" s="115"/>
-      <c r="AO38" s="115"/>
-      <c r="AP38" s="115" t="s">
+      <c r="S38" s="118"/>
+      <c r="T38" s="118"/>
+      <c r="U38" s="118"/>
+      <c r="V38" s="118"/>
+      <c r="W38" s="118"/>
+      <c r="X38" s="118"/>
+      <c r="Y38" s="118"/>
+      <c r="Z38" s="118"/>
+      <c r="AA38" s="118"/>
+      <c r="AB38" s="118"/>
+      <c r="AC38" s="118"/>
+      <c r="AD38" s="118"/>
+      <c r="AE38" s="118"/>
+      <c r="AF38" s="118"/>
+      <c r="AG38" s="118"/>
+      <c r="AH38" s="118"/>
+      <c r="AI38" s="118"/>
+      <c r="AJ38" s="118"/>
+      <c r="AK38" s="118"/>
+      <c r="AL38" s="118"/>
+      <c r="AM38" s="118"/>
+      <c r="AN38" s="118"/>
+      <c r="AO38" s="118"/>
+      <c r="AP38" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="AQ38" s="115"/>
-      <c r="AR38" s="115"/>
-      <c r="AS38" s="115"/>
-      <c r="AT38" s="115"/>
-      <c r="AU38" s="115"/>
-      <c r="AV38" s="115"/>
-      <c r="AW38" s="115"/>
-      <c r="AX38" s="115"/>
-      <c r="AY38" s="115"/>
-      <c r="AZ38" s="115"/>
-      <c r="BA38" s="115"/>
-      <c r="BB38" s="115"/>
-      <c r="BC38" s="115"/>
-      <c r="BD38" s="115"/>
-      <c r="BE38" s="115"/>
-      <c r="BF38" s="115"/>
-      <c r="BG38" s="115"/>
-      <c r="BH38" s="115"/>
-      <c r="BI38" s="115"/>
-      <c r="BJ38" s="115"/>
-      <c r="BK38" s="115"/>
-      <c r="BL38" s="115"/>
-      <c r="BM38" s="115"/>
-      <c r="BN38" s="115"/>
-      <c r="BO38" s="115"/>
-      <c r="BP38" s="136"/>
+      <c r="AQ38" s="118"/>
+      <c r="AR38" s="118"/>
+      <c r="AS38" s="118"/>
+      <c r="AT38" s="118"/>
+      <c r="AU38" s="118"/>
+      <c r="AV38" s="118"/>
+      <c r="AW38" s="118"/>
+      <c r="AX38" s="118"/>
+      <c r="AY38" s="118"/>
+      <c r="AZ38" s="118"/>
+      <c r="BA38" s="118"/>
+      <c r="BB38" s="118"/>
+      <c r="BC38" s="118"/>
+      <c r="BD38" s="118"/>
+      <c r="BE38" s="118"/>
+      <c r="BF38" s="118"/>
+      <c r="BG38" s="118"/>
+      <c r="BH38" s="118"/>
+      <c r="BI38" s="118"/>
+      <c r="BJ38" s="118"/>
+      <c r="BK38" s="118"/>
+      <c r="BL38" s="118"/>
+      <c r="BM38" s="118"/>
+      <c r="BN38" s="118"/>
+      <c r="BO38" s="118"/>
+      <c r="BP38" s="119"/>
     </row>
     <row r="39" spans="1:68" ht="15">
-      <c r="E39" s="110" t="s">
+      <c r="E39" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="111"/>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
-      <c r="I39" s="111"/>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
-      <c r="L39" s="111"/>
-      <c r="M39" s="111"/>
-      <c r="N39" s="111"/>
-      <c r="O39" s="111"/>
-      <c r="P39" s="111"/>
-      <c r="Q39" s="111"/>
-      <c r="R39" s="115" t="s">
+      <c r="F39" s="117"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="117"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="117"/>
+      <c r="L39" s="117"/>
+      <c r="M39" s="117"/>
+      <c r="N39" s="117"/>
+      <c r="O39" s="117"/>
+      <c r="P39" s="117"/>
+      <c r="Q39" s="117"/>
+      <c r="R39" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="S39" s="115"/>
-      <c r="T39" s="115"/>
-      <c r="U39" s="115"/>
-      <c r="V39" s="115"/>
-      <c r="W39" s="115"/>
-      <c r="X39" s="115"/>
-      <c r="Y39" s="115"/>
-      <c r="Z39" s="115"/>
-      <c r="AA39" s="115"/>
-      <c r="AB39" s="115"/>
-      <c r="AC39" s="115"/>
-      <c r="AD39" s="115"/>
-      <c r="AE39" s="115"/>
-      <c r="AF39" s="115"/>
-      <c r="AG39" s="115"/>
-      <c r="AH39" s="115"/>
-      <c r="AI39" s="115"/>
-      <c r="AJ39" s="115"/>
-      <c r="AK39" s="115"/>
-      <c r="AL39" s="115"/>
-      <c r="AM39" s="115"/>
-      <c r="AN39" s="115"/>
-      <c r="AO39" s="115"/>
-      <c r="AP39" s="115" t="s">
+      <c r="S39" s="118"/>
+      <c r="T39" s="118"/>
+      <c r="U39" s="118"/>
+      <c r="V39" s="118"/>
+      <c r="W39" s="118"/>
+      <c r="X39" s="118"/>
+      <c r="Y39" s="118"/>
+      <c r="Z39" s="118"/>
+      <c r="AA39" s="118"/>
+      <c r="AB39" s="118"/>
+      <c r="AC39" s="118"/>
+      <c r="AD39" s="118"/>
+      <c r="AE39" s="118"/>
+      <c r="AF39" s="118"/>
+      <c r="AG39" s="118"/>
+      <c r="AH39" s="118"/>
+      <c r="AI39" s="118"/>
+      <c r="AJ39" s="118"/>
+      <c r="AK39" s="118"/>
+      <c r="AL39" s="118"/>
+      <c r="AM39" s="118"/>
+      <c r="AN39" s="118"/>
+      <c r="AO39" s="118"/>
+      <c r="AP39" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="AQ39" s="115"/>
-      <c r="AR39" s="115"/>
-      <c r="AS39" s="115"/>
-      <c r="AT39" s="115"/>
-      <c r="AU39" s="115"/>
-      <c r="AV39" s="115"/>
-      <c r="AW39" s="115"/>
-      <c r="AX39" s="115"/>
-      <c r="AY39" s="115"/>
-      <c r="AZ39" s="115"/>
-      <c r="BA39" s="115"/>
-      <c r="BB39" s="115"/>
-      <c r="BC39" s="115"/>
-      <c r="BD39" s="115"/>
-      <c r="BE39" s="115"/>
-      <c r="BF39" s="115"/>
-      <c r="BG39" s="115"/>
-      <c r="BH39" s="115"/>
-      <c r="BI39" s="115"/>
-      <c r="BJ39" s="115"/>
-      <c r="BK39" s="115"/>
-      <c r="BL39" s="115"/>
-      <c r="BM39" s="115"/>
-      <c r="BN39" s="115"/>
-      <c r="BO39" s="115"/>
-      <c r="BP39" s="136"/>
+      <c r="AQ39" s="118"/>
+      <c r="AR39" s="118"/>
+      <c r="AS39" s="118"/>
+      <c r="AT39" s="118"/>
+      <c r="AU39" s="118"/>
+      <c r="AV39" s="118"/>
+      <c r="AW39" s="118"/>
+      <c r="AX39" s="118"/>
+      <c r="AY39" s="118"/>
+      <c r="AZ39" s="118"/>
+      <c r="BA39" s="118"/>
+      <c r="BB39" s="118"/>
+      <c r="BC39" s="118"/>
+      <c r="BD39" s="118"/>
+      <c r="BE39" s="118"/>
+      <c r="BF39" s="118"/>
+      <c r="BG39" s="118"/>
+      <c r="BH39" s="118"/>
+      <c r="BI39" s="118"/>
+      <c r="BJ39" s="118"/>
+      <c r="BK39" s="118"/>
+      <c r="BL39" s="118"/>
+      <c r="BM39" s="118"/>
+      <c r="BN39" s="118"/>
+      <c r="BO39" s="118"/>
+      <c r="BP39" s="119"/>
     </row>
     <row r="40" spans="1:68" ht="15">
-      <c r="E40" s="110" t="s">
+      <c r="E40" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="111"/>
-      <c r="G40" s="111"/>
-      <c r="H40" s="111"/>
-      <c r="I40" s="111"/>
-      <c r="J40" s="111"/>
-      <c r="K40" s="111"/>
-      <c r="L40" s="111"/>
-      <c r="M40" s="111"/>
-      <c r="N40" s="111"/>
-      <c r="O40" s="111"/>
-      <c r="P40" s="111"/>
-      <c r="Q40" s="111"/>
-      <c r="R40" s="115" t="s">
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="117"/>
+      <c r="J40" s="117"/>
+      <c r="K40" s="117"/>
+      <c r="L40" s="117"/>
+      <c r="M40" s="117"/>
+      <c r="N40" s="117"/>
+      <c r="O40" s="117"/>
+      <c r="P40" s="117"/>
+      <c r="Q40" s="117"/>
+      <c r="R40" s="118" t="s">
         <v>71</v>
       </c>
-      <c r="S40" s="115"/>
-      <c r="T40" s="115"/>
-      <c r="U40" s="115"/>
-      <c r="V40" s="115"/>
-      <c r="W40" s="115"/>
-      <c r="X40" s="115"/>
-      <c r="Y40" s="115"/>
-      <c r="Z40" s="115"/>
-      <c r="AA40" s="115"/>
-      <c r="AB40" s="115"/>
-      <c r="AC40" s="115"/>
-      <c r="AD40" s="115"/>
-      <c r="AE40" s="115"/>
-      <c r="AF40" s="115"/>
-      <c r="AG40" s="115"/>
-      <c r="AH40" s="115"/>
-      <c r="AI40" s="115"/>
-      <c r="AJ40" s="115"/>
-      <c r="AK40" s="115"/>
-      <c r="AL40" s="115"/>
-      <c r="AM40" s="115"/>
-      <c r="AN40" s="115"/>
-      <c r="AO40" s="115"/>
-      <c r="AP40" s="115" t="s">
+      <c r="S40" s="118"/>
+      <c r="T40" s="118"/>
+      <c r="U40" s="118"/>
+      <c r="V40" s="118"/>
+      <c r="W40" s="118"/>
+      <c r="X40" s="118"/>
+      <c r="Y40" s="118"/>
+      <c r="Z40" s="118"/>
+      <c r="AA40" s="118"/>
+      <c r="AB40" s="118"/>
+      <c r="AC40" s="118"/>
+      <c r="AD40" s="118"/>
+      <c r="AE40" s="118"/>
+      <c r="AF40" s="118"/>
+      <c r="AG40" s="118"/>
+      <c r="AH40" s="118"/>
+      <c r="AI40" s="118"/>
+      <c r="AJ40" s="118"/>
+      <c r="AK40" s="118"/>
+      <c r="AL40" s="118"/>
+      <c r="AM40" s="118"/>
+      <c r="AN40" s="118"/>
+      <c r="AO40" s="118"/>
+      <c r="AP40" s="118" t="s">
         <v>72</v>
       </c>
-      <c r="AQ40" s="115"/>
-      <c r="AR40" s="115"/>
-      <c r="AS40" s="115"/>
-      <c r="AT40" s="115"/>
-      <c r="AU40" s="115"/>
-      <c r="AV40" s="115"/>
-      <c r="AW40" s="115"/>
-      <c r="AX40" s="115"/>
-      <c r="AY40" s="115"/>
-      <c r="AZ40" s="115"/>
-      <c r="BA40" s="115"/>
-      <c r="BB40" s="115"/>
-      <c r="BC40" s="115"/>
-      <c r="BD40" s="115"/>
-      <c r="BE40" s="115"/>
-      <c r="BF40" s="115"/>
-      <c r="BG40" s="115"/>
-      <c r="BH40" s="115"/>
-      <c r="BI40" s="115"/>
-      <c r="BJ40" s="115"/>
-      <c r="BK40" s="115"/>
-      <c r="BL40" s="115"/>
-      <c r="BM40" s="115"/>
-      <c r="BN40" s="115"/>
-      <c r="BO40" s="115"/>
-      <c r="BP40" s="136"/>
+      <c r="AQ40" s="118"/>
+      <c r="AR40" s="118"/>
+      <c r="AS40" s="118"/>
+      <c r="AT40" s="118"/>
+      <c r="AU40" s="118"/>
+      <c r="AV40" s="118"/>
+      <c r="AW40" s="118"/>
+      <c r="AX40" s="118"/>
+      <c r="AY40" s="118"/>
+      <c r="AZ40" s="118"/>
+      <c r="BA40" s="118"/>
+      <c r="BB40" s="118"/>
+      <c r="BC40" s="118"/>
+      <c r="BD40" s="118"/>
+      <c r="BE40" s="118"/>
+      <c r="BF40" s="118"/>
+      <c r="BG40" s="118"/>
+      <c r="BH40" s="118"/>
+      <c r="BI40" s="118"/>
+      <c r="BJ40" s="118"/>
+      <c r="BK40" s="118"/>
+      <c r="BL40" s="118"/>
+      <c r="BM40" s="118"/>
+      <c r="BN40" s="118"/>
+      <c r="BO40" s="118"/>
+      <c r="BP40" s="119"/>
     </row>
     <row r="41" spans="1:68" ht="15">
-      <c r="E41" s="110" t="s">
+      <c r="E41" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="111"/>
-      <c r="G41" s="111"/>
-      <c r="H41" s="111"/>
-      <c r="I41" s="111"/>
-      <c r="J41" s="111"/>
-      <c r="K41" s="111"/>
-      <c r="L41" s="111"/>
-      <c r="M41" s="111"/>
-      <c r="N41" s="111"/>
-      <c r="O41" s="111"/>
-      <c r="P41" s="111"/>
-      <c r="Q41" s="111"/>
-      <c r="R41" s="115" t="s">
+      <c r="F41" s="117"/>
+      <c r="G41" s="117"/>
+      <c r="H41" s="117"/>
+      <c r="I41" s="117"/>
+      <c r="J41" s="117"/>
+      <c r="K41" s="117"/>
+      <c r="L41" s="117"/>
+      <c r="M41" s="117"/>
+      <c r="N41" s="117"/>
+      <c r="O41" s="117"/>
+      <c r="P41" s="117"/>
+      <c r="Q41" s="117"/>
+      <c r="R41" s="118" t="s">
         <v>74</v>
       </c>
-      <c r="S41" s="115"/>
-      <c r="T41" s="115"/>
-      <c r="U41" s="115"/>
-      <c r="V41" s="115"/>
-      <c r="W41" s="115"/>
-      <c r="X41" s="115"/>
-      <c r="Y41" s="115"/>
-      <c r="Z41" s="115"/>
-      <c r="AA41" s="115"/>
-      <c r="AB41" s="115"/>
-      <c r="AC41" s="115"/>
-      <c r="AD41" s="115"/>
-      <c r="AE41" s="115"/>
-      <c r="AF41" s="115"/>
-      <c r="AG41" s="115"/>
-      <c r="AH41" s="115"/>
-      <c r="AI41" s="115"/>
-      <c r="AJ41" s="115"/>
-      <c r="AK41" s="115"/>
-      <c r="AL41" s="115"/>
-      <c r="AM41" s="115"/>
-      <c r="AN41" s="115"/>
-      <c r="AO41" s="115"/>
-      <c r="AP41" s="115" t="s">
+      <c r="S41" s="118"/>
+      <c r="T41" s="118"/>
+      <c r="U41" s="118"/>
+      <c r="V41" s="118"/>
+      <c r="W41" s="118"/>
+      <c r="X41" s="118"/>
+      <c r="Y41" s="118"/>
+      <c r="Z41" s="118"/>
+      <c r="AA41" s="118"/>
+      <c r="AB41" s="118"/>
+      <c r="AC41" s="118"/>
+      <c r="AD41" s="118"/>
+      <c r="AE41" s="118"/>
+      <c r="AF41" s="118"/>
+      <c r="AG41" s="118"/>
+      <c r="AH41" s="118"/>
+      <c r="AI41" s="118"/>
+      <c r="AJ41" s="118"/>
+      <c r="AK41" s="118"/>
+      <c r="AL41" s="118"/>
+      <c r="AM41" s="118"/>
+      <c r="AN41" s="118"/>
+      <c r="AO41" s="118"/>
+      <c r="AP41" s="118" t="s">
         <v>75</v>
       </c>
-      <c r="AQ41" s="115"/>
-      <c r="AR41" s="115"/>
-      <c r="AS41" s="115"/>
-      <c r="AT41" s="115"/>
-      <c r="AU41" s="115"/>
-      <c r="AV41" s="115"/>
-      <c r="AW41" s="115"/>
-      <c r="AX41" s="115"/>
-      <c r="AY41" s="115"/>
-      <c r="AZ41" s="115"/>
-      <c r="BA41" s="115"/>
-      <c r="BB41" s="115"/>
-      <c r="BC41" s="115"/>
-      <c r="BD41" s="115"/>
-      <c r="BE41" s="115"/>
-      <c r="BF41" s="115"/>
-      <c r="BG41" s="115"/>
-      <c r="BH41" s="115"/>
-      <c r="BI41" s="115"/>
-      <c r="BJ41" s="115"/>
-      <c r="BK41" s="115"/>
-      <c r="BL41" s="115"/>
-      <c r="BM41" s="115"/>
-      <c r="BN41" s="115"/>
-      <c r="BO41" s="115"/>
-      <c r="BP41" s="136"/>
+      <c r="AQ41" s="118"/>
+      <c r="AR41" s="118"/>
+      <c r="AS41" s="118"/>
+      <c r="AT41" s="118"/>
+      <c r="AU41" s="118"/>
+      <c r="AV41" s="118"/>
+      <c r="AW41" s="118"/>
+      <c r="AX41" s="118"/>
+      <c r="AY41" s="118"/>
+      <c r="AZ41" s="118"/>
+      <c r="BA41" s="118"/>
+      <c r="BB41" s="118"/>
+      <c r="BC41" s="118"/>
+      <c r="BD41" s="118"/>
+      <c r="BE41" s="118"/>
+      <c r="BF41" s="118"/>
+      <c r="BG41" s="118"/>
+      <c r="BH41" s="118"/>
+      <c r="BI41" s="118"/>
+      <c r="BJ41" s="118"/>
+      <c r="BK41" s="118"/>
+      <c r="BL41" s="118"/>
+      <c r="BM41" s="118"/>
+      <c r="BN41" s="118"/>
+      <c r="BO41" s="118"/>
+      <c r="BP41" s="119"/>
     </row>
     <row r="42" spans="1:68" ht="15">
-      <c r="E42" s="110" t="s">
+      <c r="E42" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="111"/>
-      <c r="G42" s="111"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="111"/>
-      <c r="J42" s="111"/>
-      <c r="K42" s="111"/>
-      <c r="L42" s="111"/>
-      <c r="M42" s="111"/>
-      <c r="N42" s="111"/>
-      <c r="O42" s="111"/>
-      <c r="P42" s="111"/>
-      <c r="Q42" s="111"/>
-      <c r="R42" s="115" t="s">
+      <c r="F42" s="117"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="117"/>
+      <c r="I42" s="117"/>
+      <c r="J42" s="117"/>
+      <c r="K42" s="117"/>
+      <c r="L42" s="117"/>
+      <c r="M42" s="117"/>
+      <c r="N42" s="117"/>
+      <c r="O42" s="117"/>
+      <c r="P42" s="117"/>
+      <c r="Q42" s="117"/>
+      <c r="R42" s="118" t="s">
         <v>77</v>
       </c>
-      <c r="S42" s="115"/>
-      <c r="T42" s="115"/>
-      <c r="U42" s="115"/>
-      <c r="V42" s="115"/>
-      <c r="W42" s="115"/>
-      <c r="X42" s="115"/>
-      <c r="Y42" s="115"/>
-      <c r="Z42" s="115"/>
-      <c r="AA42" s="115"/>
-      <c r="AB42" s="115"/>
-      <c r="AC42" s="115"/>
-      <c r="AD42" s="115"/>
-      <c r="AE42" s="115"/>
-      <c r="AF42" s="115"/>
-      <c r="AG42" s="115"/>
-      <c r="AH42" s="115"/>
-      <c r="AI42" s="115"/>
-      <c r="AJ42" s="115"/>
-      <c r="AK42" s="115"/>
-      <c r="AL42" s="115"/>
-      <c r="AM42" s="115"/>
-      <c r="AN42" s="115"/>
-      <c r="AO42" s="115"/>
-      <c r="AP42" s="115" t="s">
+      <c r="S42" s="118"/>
+      <c r="T42" s="118"/>
+      <c r="U42" s="118"/>
+      <c r="V42" s="118"/>
+      <c r="W42" s="118"/>
+      <c r="X42" s="118"/>
+      <c r="Y42" s="118"/>
+      <c r="Z42" s="118"/>
+      <c r="AA42" s="118"/>
+      <c r="AB42" s="118"/>
+      <c r="AC42" s="118"/>
+      <c r="AD42" s="118"/>
+      <c r="AE42" s="118"/>
+      <c r="AF42" s="118"/>
+      <c r="AG42" s="118"/>
+      <c r="AH42" s="118"/>
+      <c r="AI42" s="118"/>
+      <c r="AJ42" s="118"/>
+      <c r="AK42" s="118"/>
+      <c r="AL42" s="118"/>
+      <c r="AM42" s="118"/>
+      <c r="AN42" s="118"/>
+      <c r="AO42" s="118"/>
+      <c r="AP42" s="118" t="s">
         <v>78</v>
       </c>
-      <c r="AQ42" s="115"/>
-      <c r="AR42" s="115"/>
-      <c r="AS42" s="115"/>
-      <c r="AT42" s="115"/>
-      <c r="AU42" s="115"/>
-      <c r="AV42" s="115"/>
-      <c r="AW42" s="115"/>
-      <c r="AX42" s="115"/>
-      <c r="AY42" s="115"/>
-      <c r="AZ42" s="115"/>
-      <c r="BA42" s="115"/>
-      <c r="BB42" s="115"/>
-      <c r="BC42" s="115"/>
-      <c r="BD42" s="115"/>
-      <c r="BE42" s="115"/>
-      <c r="BF42" s="115"/>
-      <c r="BG42" s="115"/>
-      <c r="BH42" s="115"/>
-      <c r="BI42" s="115"/>
-      <c r="BJ42" s="115"/>
-      <c r="BK42" s="115"/>
-      <c r="BL42" s="115"/>
-      <c r="BM42" s="115"/>
-      <c r="BN42" s="115"/>
-      <c r="BO42" s="115"/>
-      <c r="BP42" s="136"/>
+      <c r="AQ42" s="118"/>
+      <c r="AR42" s="118"/>
+      <c r="AS42" s="118"/>
+      <c r="AT42" s="118"/>
+      <c r="AU42" s="118"/>
+      <c r="AV42" s="118"/>
+      <c r="AW42" s="118"/>
+      <c r="AX42" s="118"/>
+      <c r="AY42" s="118"/>
+      <c r="AZ42" s="118"/>
+      <c r="BA42" s="118"/>
+      <c r="BB42" s="118"/>
+      <c r="BC42" s="118"/>
+      <c r="BD42" s="118"/>
+      <c r="BE42" s="118"/>
+      <c r="BF42" s="118"/>
+      <c r="BG42" s="118"/>
+      <c r="BH42" s="118"/>
+      <c r="BI42" s="118"/>
+      <c r="BJ42" s="118"/>
+      <c r="BK42" s="118"/>
+      <c r="BL42" s="118"/>
+      <c r="BM42" s="118"/>
+      <c r="BN42" s="118"/>
+      <c r="BO42" s="118"/>
+      <c r="BP42" s="119"/>
     </row>
     <row r="43" spans="1:68" ht="15">
-      <c r="E43" s="110" t="s">
+      <c r="E43" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="F43" s="111"/>
-      <c r="G43" s="111"/>
-      <c r="H43" s="111"/>
-      <c r="I43" s="111"/>
-      <c r="J43" s="111"/>
-      <c r="K43" s="111"/>
-      <c r="L43" s="111"/>
-      <c r="M43" s="111"/>
-      <c r="N43" s="111"/>
-      <c r="O43" s="111"/>
-      <c r="P43" s="111"/>
-      <c r="Q43" s="111"/>
-      <c r="R43" s="115" t="s">
+      <c r="F43" s="117"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="117"/>
+      <c r="I43" s="117"/>
+      <c r="J43" s="117"/>
+      <c r="K43" s="117"/>
+      <c r="L43" s="117"/>
+      <c r="M43" s="117"/>
+      <c r="N43" s="117"/>
+      <c r="O43" s="117"/>
+      <c r="P43" s="117"/>
+      <c r="Q43" s="117"/>
+      <c r="R43" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="S43" s="115"/>
-      <c r="T43" s="115"/>
-      <c r="U43" s="115"/>
-      <c r="V43" s="115"/>
-      <c r="W43" s="115"/>
-      <c r="X43" s="115"/>
-      <c r="Y43" s="115"/>
-      <c r="Z43" s="115"/>
-      <c r="AA43" s="115"/>
-      <c r="AB43" s="115"/>
-      <c r="AC43" s="115"/>
-      <c r="AD43" s="115"/>
-      <c r="AE43" s="115"/>
-      <c r="AF43" s="115"/>
-      <c r="AG43" s="115"/>
-      <c r="AH43" s="115"/>
-      <c r="AI43" s="115"/>
-      <c r="AJ43" s="115"/>
-      <c r="AK43" s="115"/>
-      <c r="AL43" s="115"/>
-      <c r="AM43" s="115"/>
-      <c r="AN43" s="115"/>
-      <c r="AO43" s="115"/>
-      <c r="AP43" s="115" t="s">
+      <c r="S43" s="118"/>
+      <c r="T43" s="118"/>
+      <c r="U43" s="118"/>
+      <c r="V43" s="118"/>
+      <c r="W43" s="118"/>
+      <c r="X43" s="118"/>
+      <c r="Y43" s="118"/>
+      <c r="Z43" s="118"/>
+      <c r="AA43" s="118"/>
+      <c r="AB43" s="118"/>
+      <c r="AC43" s="118"/>
+      <c r="AD43" s="118"/>
+      <c r="AE43" s="118"/>
+      <c r="AF43" s="118"/>
+      <c r="AG43" s="118"/>
+      <c r="AH43" s="118"/>
+      <c r="AI43" s="118"/>
+      <c r="AJ43" s="118"/>
+      <c r="AK43" s="118"/>
+      <c r="AL43" s="118"/>
+      <c r="AM43" s="118"/>
+      <c r="AN43" s="118"/>
+      <c r="AO43" s="118"/>
+      <c r="AP43" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="AQ43" s="115"/>
-      <c r="AR43" s="115"/>
-      <c r="AS43" s="115"/>
-      <c r="AT43" s="115"/>
-      <c r="AU43" s="115"/>
-      <c r="AV43" s="115"/>
-      <c r="AW43" s="115"/>
-      <c r="AX43" s="115"/>
-      <c r="AY43" s="115"/>
-      <c r="AZ43" s="115"/>
-      <c r="BA43" s="115"/>
-      <c r="BB43" s="115"/>
-      <c r="BC43" s="115"/>
-      <c r="BD43" s="115"/>
-      <c r="BE43" s="115"/>
-      <c r="BF43" s="115"/>
-      <c r="BG43" s="115"/>
-      <c r="BH43" s="115"/>
-      <c r="BI43" s="115"/>
-      <c r="BJ43" s="115"/>
-      <c r="BK43" s="115"/>
-      <c r="BL43" s="115"/>
-      <c r="BM43" s="115"/>
-      <c r="BN43" s="115"/>
-      <c r="BO43" s="115"/>
-      <c r="BP43" s="136"/>
+      <c r="AQ43" s="118"/>
+      <c r="AR43" s="118"/>
+      <c r="AS43" s="118"/>
+      <c r="AT43" s="118"/>
+      <c r="AU43" s="118"/>
+      <c r="AV43" s="118"/>
+      <c r="AW43" s="118"/>
+      <c r="AX43" s="118"/>
+      <c r="AY43" s="118"/>
+      <c r="AZ43" s="118"/>
+      <c r="BA43" s="118"/>
+      <c r="BB43" s="118"/>
+      <c r="BC43" s="118"/>
+      <c r="BD43" s="118"/>
+      <c r="BE43" s="118"/>
+      <c r="BF43" s="118"/>
+      <c r="BG43" s="118"/>
+      <c r="BH43" s="118"/>
+      <c r="BI43" s="118"/>
+      <c r="BJ43" s="118"/>
+      <c r="BK43" s="118"/>
+      <c r="BL43" s="118"/>
+      <c r="BM43" s="118"/>
+      <c r="BN43" s="118"/>
+      <c r="BO43" s="118"/>
+      <c r="BP43" s="119"/>
     </row>
     <row r="44" spans="1:68" ht="15.75" thickBot="1">
-      <c r="E44" s="108" t="s">
+      <c r="E44" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="F44" s="109"/>
-      <c r="G44" s="109"/>
-      <c r="H44" s="109"/>
-      <c r="I44" s="109"/>
-      <c r="J44" s="109"/>
-      <c r="K44" s="109"/>
-      <c r="L44" s="109"/>
-      <c r="M44" s="109"/>
-      <c r="N44" s="109"/>
-      <c r="O44" s="109"/>
-      <c r="P44" s="109"/>
-      <c r="Q44" s="109"/>
-      <c r="R44" s="114" t="s">
+      <c r="F44" s="121"/>
+      <c r="G44" s="121"/>
+      <c r="H44" s="121"/>
+      <c r="I44" s="121"/>
+      <c r="J44" s="121"/>
+      <c r="K44" s="121"/>
+      <c r="L44" s="121"/>
+      <c r="M44" s="121"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="121"/>
+      <c r="P44" s="121"/>
+      <c r="Q44" s="121"/>
+      <c r="R44" s="123" t="s">
         <v>83</v>
       </c>
-      <c r="S44" s="114"/>
-      <c r="T44" s="114"/>
-      <c r="U44" s="114"/>
-      <c r="V44" s="114"/>
-      <c r="W44" s="114"/>
-      <c r="X44" s="114"/>
-      <c r="Y44" s="114"/>
-      <c r="Z44" s="114"/>
-      <c r="AA44" s="114"/>
-      <c r="AB44" s="114"/>
-      <c r="AC44" s="114"/>
-      <c r="AD44" s="114"/>
-      <c r="AE44" s="114"/>
-      <c r="AF44" s="114"/>
-      <c r="AG44" s="114"/>
-      <c r="AH44" s="114"/>
-      <c r="AI44" s="114"/>
-      <c r="AJ44" s="114"/>
-      <c r="AK44" s="114"/>
-      <c r="AL44" s="114"/>
-      <c r="AM44" s="114"/>
-      <c r="AN44" s="114"/>
-      <c r="AO44" s="114"/>
-      <c r="AP44" s="114" t="s">
+      <c r="S44" s="123"/>
+      <c r="T44" s="123"/>
+      <c r="U44" s="123"/>
+      <c r="V44" s="123"/>
+      <c r="W44" s="123"/>
+      <c r="X44" s="123"/>
+      <c r="Y44" s="123"/>
+      <c r="Z44" s="123"/>
+      <c r="AA44" s="123"/>
+      <c r="AB44" s="123"/>
+      <c r="AC44" s="123"/>
+      <c r="AD44" s="123"/>
+      <c r="AE44" s="123"/>
+      <c r="AF44" s="123"/>
+      <c r="AG44" s="123"/>
+      <c r="AH44" s="123"/>
+      <c r="AI44" s="123"/>
+      <c r="AJ44" s="123"/>
+      <c r="AK44" s="123"/>
+      <c r="AL44" s="123"/>
+      <c r="AM44" s="123"/>
+      <c r="AN44" s="123"/>
+      <c r="AO44" s="123"/>
+      <c r="AP44" s="123" t="s">
         <v>84</v>
       </c>
-      <c r="AQ44" s="114"/>
-      <c r="AR44" s="114"/>
-      <c r="AS44" s="114"/>
-      <c r="AT44" s="114"/>
-      <c r="AU44" s="114"/>
-      <c r="AV44" s="114"/>
-      <c r="AW44" s="114"/>
-      <c r="AX44" s="114"/>
-      <c r="AY44" s="114"/>
-      <c r="AZ44" s="114"/>
-      <c r="BA44" s="114"/>
-      <c r="BB44" s="114"/>
-      <c r="BC44" s="114"/>
-      <c r="BD44" s="114"/>
-      <c r="BE44" s="114"/>
-      <c r="BF44" s="114"/>
-      <c r="BG44" s="114"/>
-      <c r="BH44" s="114"/>
-      <c r="BI44" s="114"/>
-      <c r="BJ44" s="114"/>
-      <c r="BK44" s="114"/>
-      <c r="BL44" s="114"/>
-      <c r="BM44" s="114"/>
-      <c r="BN44" s="114"/>
-      <c r="BO44" s="114"/>
-      <c r="BP44" s="135"/>
+      <c r="AQ44" s="123"/>
+      <c r="AR44" s="123"/>
+      <c r="AS44" s="123"/>
+      <c r="AT44" s="123"/>
+      <c r="AU44" s="123"/>
+      <c r="AV44" s="123"/>
+      <c r="AW44" s="123"/>
+      <c r="AX44" s="123"/>
+      <c r="AY44" s="123"/>
+      <c r="AZ44" s="123"/>
+      <c r="BA44" s="123"/>
+      <c r="BB44" s="123"/>
+      <c r="BC44" s="123"/>
+      <c r="BD44" s="123"/>
+      <c r="BE44" s="123"/>
+      <c r="BF44" s="123"/>
+      <c r="BG44" s="123"/>
+      <c r="BH44" s="123"/>
+      <c r="BI44" s="123"/>
+      <c r="BJ44" s="123"/>
+      <c r="BK44" s="123"/>
+      <c r="BL44" s="123"/>
+      <c r="BM44" s="123"/>
+      <c r="BN44" s="123"/>
+      <c r="BO44" s="123"/>
+      <c r="BP44" s="125"/>
     </row>
     <row r="45" spans="1:68" ht="15" thickBot="1"/>
     <row r="46" spans="1:68" s="16" customFormat="1" ht="15.75" thickBot="1">
@@ -10129,63 +8190,6 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="E37:Q37"/>
-    <mergeCell ref="AP36:BP36"/>
-    <mergeCell ref="AP37:BP37"/>
-    <mergeCell ref="AP38:BP38"/>
-    <mergeCell ref="E44:Q44"/>
-    <mergeCell ref="R34:AO34"/>
-    <mergeCell ref="R35:AO35"/>
-    <mergeCell ref="R36:AO36"/>
-    <mergeCell ref="R37:AO37"/>
-    <mergeCell ref="E43:Q43"/>
-    <mergeCell ref="R43:AO43"/>
-    <mergeCell ref="R44:AO44"/>
-    <mergeCell ref="E38:Q38"/>
-    <mergeCell ref="E39:Q39"/>
-    <mergeCell ref="E40:Q40"/>
-    <mergeCell ref="E41:Q41"/>
-    <mergeCell ref="E42:Q42"/>
-    <mergeCell ref="E34:Q34"/>
-    <mergeCell ref="E35:Q35"/>
-    <mergeCell ref="E36:Q36"/>
-    <mergeCell ref="AP44:BP44"/>
-    <mergeCell ref="R38:AO38"/>
-    <mergeCell ref="R39:AO39"/>
-    <mergeCell ref="R40:AO40"/>
-    <mergeCell ref="R41:AO41"/>
-    <mergeCell ref="R42:AO42"/>
-    <mergeCell ref="AP39:BP39"/>
-    <mergeCell ref="AP40:BP40"/>
-    <mergeCell ref="AP41:BP41"/>
-    <mergeCell ref="AP42:BP42"/>
-    <mergeCell ref="AP43:BP43"/>
-    <mergeCell ref="AP34:BP34"/>
-    <mergeCell ref="AP35:BP35"/>
-    <mergeCell ref="AZ12:BI12"/>
-    <mergeCell ref="AZ14:BI14"/>
-    <mergeCell ref="AZ13:BI13"/>
-    <mergeCell ref="AZ15:BI15"/>
-    <mergeCell ref="AQ27:BB27"/>
-    <mergeCell ref="AQ28:BB28"/>
-    <mergeCell ref="Q27:AC27"/>
-    <mergeCell ref="Q28:AC28"/>
-    <mergeCell ref="Q29:AC29"/>
-    <mergeCell ref="Q30:AC30"/>
-    <mergeCell ref="AD27:AP27"/>
-    <mergeCell ref="AD28:AP28"/>
-    <mergeCell ref="AD29:AP29"/>
-    <mergeCell ref="AD30:AP30"/>
-    <mergeCell ref="AQ29:BB29"/>
-    <mergeCell ref="AQ30:BB30"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="I27:P27"/>
-    <mergeCell ref="I28:P28"/>
-    <mergeCell ref="I29:P29"/>
-    <mergeCell ref="I30:P30"/>
     <mergeCell ref="L12:AG12"/>
     <mergeCell ref="AH12:AY12"/>
     <mergeCell ref="D12:K12"/>
@@ -10198,6 +8202,63 @@
     <mergeCell ref="L15:AG15"/>
     <mergeCell ref="L13:AG13"/>
     <mergeCell ref="L14:AG14"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="I27:P27"/>
+    <mergeCell ref="I28:P28"/>
+    <mergeCell ref="I29:P29"/>
+    <mergeCell ref="I30:P30"/>
+    <mergeCell ref="Q27:AC27"/>
+    <mergeCell ref="Q28:AC28"/>
+    <mergeCell ref="Q29:AC29"/>
+    <mergeCell ref="Q30:AC30"/>
+    <mergeCell ref="AD27:AP27"/>
+    <mergeCell ref="AD28:AP28"/>
+    <mergeCell ref="AD29:AP29"/>
+    <mergeCell ref="AD30:AP30"/>
+    <mergeCell ref="AP34:BP34"/>
+    <mergeCell ref="AP35:BP35"/>
+    <mergeCell ref="AZ12:BI12"/>
+    <mergeCell ref="AZ14:BI14"/>
+    <mergeCell ref="AZ13:BI13"/>
+    <mergeCell ref="AZ15:BI15"/>
+    <mergeCell ref="AQ27:BB27"/>
+    <mergeCell ref="AQ28:BB28"/>
+    <mergeCell ref="AQ29:BB29"/>
+    <mergeCell ref="AQ30:BB30"/>
+    <mergeCell ref="R34:AO34"/>
+    <mergeCell ref="R35:AO35"/>
+    <mergeCell ref="R36:AO36"/>
+    <mergeCell ref="R37:AO37"/>
+    <mergeCell ref="E43:Q43"/>
+    <mergeCell ref="R43:AO43"/>
+    <mergeCell ref="E38:Q38"/>
+    <mergeCell ref="E39:Q39"/>
+    <mergeCell ref="E40:Q40"/>
+    <mergeCell ref="E41:Q41"/>
+    <mergeCell ref="E42:Q42"/>
+    <mergeCell ref="E34:Q34"/>
+    <mergeCell ref="E35:Q35"/>
+    <mergeCell ref="E36:Q36"/>
+    <mergeCell ref="R38:AO38"/>
+    <mergeCell ref="R39:AO39"/>
+    <mergeCell ref="E37:Q37"/>
+    <mergeCell ref="AP36:BP36"/>
+    <mergeCell ref="AP37:BP37"/>
+    <mergeCell ref="AP38:BP38"/>
+    <mergeCell ref="E44:Q44"/>
+    <mergeCell ref="R44:AO44"/>
+    <mergeCell ref="AP44:BP44"/>
+    <mergeCell ref="R40:AO40"/>
+    <mergeCell ref="R41:AO41"/>
+    <mergeCell ref="R42:AO42"/>
+    <mergeCell ref="AP39:BP39"/>
+    <mergeCell ref="AP40:BP40"/>
+    <mergeCell ref="AP41:BP41"/>
+    <mergeCell ref="AP42:BP42"/>
+    <mergeCell ref="AP43:BP43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -10217,78 +8278,78 @@
     </row>
     <row r="2" spans="2:43" ht="15" thickBot="1"/>
     <row r="3" spans="2:43" ht="15">
-      <c r="F3" s="116" t="s">
+      <c r="F3" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117" t="s">
+      <c r="G3" s="135"/>
+      <c r="H3" s="135"/>
+      <c r="I3" s="135"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135" t="s">
         <v>86</v>
       </c>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="117"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="117"/>
-      <c r="U3" s="117"/>
-      <c r="V3" s="117"/>
-      <c r="W3" s="117"/>
-      <c r="X3" s="117" t="s">
+      <c r="N3" s="135"/>
+      <c r="O3" s="135"/>
+      <c r="P3" s="135"/>
+      <c r="Q3" s="135"/>
+      <c r="R3" s="135"/>
+      <c r="S3" s="135"/>
+      <c r="T3" s="135"/>
+      <c r="U3" s="135"/>
+      <c r="V3" s="135"/>
+      <c r="W3" s="135"/>
+      <c r="X3" s="135" t="s">
         <v>87</v>
       </c>
-      <c r="Y3" s="117"/>
-      <c r="Z3" s="117"/>
-      <c r="AA3" s="117"/>
-      <c r="AB3" s="117"/>
-      <c r="AC3" s="117"/>
-      <c r="AD3" s="117"/>
-      <c r="AE3" s="117"/>
-      <c r="AF3" s="117"/>
-      <c r="AG3" s="117"/>
-      <c r="AH3" s="140"/>
+      <c r="Y3" s="135"/>
+      <c r="Z3" s="135"/>
+      <c r="AA3" s="135"/>
+      <c r="AB3" s="135"/>
+      <c r="AC3" s="135"/>
+      <c r="AD3" s="135"/>
+      <c r="AE3" s="135"/>
+      <c r="AF3" s="135"/>
+      <c r="AG3" s="135"/>
+      <c r="AH3" s="150"/>
     </row>
     <row r="4" spans="2:43">
-      <c r="F4" s="118" t="s">
+      <c r="F4" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
-      <c r="L4" s="119"/>
-      <c r="M4" s="123" t="s">
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="136"/>
+      <c r="M4" s="138" t="s">
         <v>89</v>
       </c>
-      <c r="N4" s="123"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="123"/>
-      <c r="Q4" s="123"/>
-      <c r="R4" s="123"/>
-      <c r="S4" s="123"/>
-      <c r="T4" s="123"/>
-      <c r="U4" s="123"/>
-      <c r="V4" s="123"/>
-      <c r="W4" s="123"/>
-      <c r="X4" s="123" t="s">
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="138"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="138"/>
+      <c r="U4" s="138"/>
+      <c r="V4" s="138"/>
+      <c r="W4" s="138"/>
+      <c r="X4" s="138" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="123"/>
-      <c r="Z4" s="123"/>
-      <c r="AA4" s="123"/>
-      <c r="AB4" s="123"/>
-      <c r="AC4" s="123"/>
-      <c r="AD4" s="123"/>
-      <c r="AE4" s="123"/>
-      <c r="AF4" s="123"/>
-      <c r="AG4" s="123"/>
-      <c r="AH4" s="138"/>
+      <c r="Y4" s="138"/>
+      <c r="Z4" s="138"/>
+      <c r="AA4" s="138"/>
+      <c r="AB4" s="138"/>
+      <c r="AC4" s="138"/>
+      <c r="AD4" s="138"/>
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138"/>
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="148"/>
       <c r="AI4" s="52" t="s">
         <v>201</v>
       </c>
@@ -10302,41 +8363,41 @@
       <c r="AQ4" s="53"/>
     </row>
     <row r="5" spans="2:43">
-      <c r="F5" s="118" t="s">
+      <c r="F5" s="143" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119"/>
-      <c r="I5" s="119"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="119"/>
-      <c r="L5" s="119"/>
-      <c r="M5" s="123" t="s">
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="138" t="s">
         <v>92</v>
       </c>
-      <c r="N5" s="123"/>
-      <c r="O5" s="123"/>
-      <c r="P5" s="123"/>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="123"/>
-      <c r="W5" s="123"/>
-      <c r="X5" s="123" t="s">
+      <c r="N5" s="138"/>
+      <c r="O5" s="138"/>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="138"/>
+      <c r="R5" s="138"/>
+      <c r="S5" s="138"/>
+      <c r="T5" s="138"/>
+      <c r="U5" s="138"/>
+      <c r="V5" s="138"/>
+      <c r="W5" s="138"/>
+      <c r="X5" s="138" t="s">
         <v>93</v>
       </c>
-      <c r="Y5" s="123"/>
-      <c r="Z5" s="123"/>
-      <c r="AA5" s="123"/>
-      <c r="AB5" s="123"/>
-      <c r="AC5" s="123"/>
-      <c r="AD5" s="123"/>
-      <c r="AE5" s="123"/>
-      <c r="AF5" s="123"/>
-      <c r="AG5" s="123"/>
-      <c r="AH5" s="138"/>
+      <c r="Y5" s="138"/>
+      <c r="Z5" s="138"/>
+      <c r="AA5" s="138"/>
+      <c r="AB5" s="138"/>
+      <c r="AC5" s="138"/>
+      <c r="AD5" s="138"/>
+      <c r="AE5" s="138"/>
+      <c r="AF5" s="138"/>
+      <c r="AG5" s="138"/>
+      <c r="AH5" s="148"/>
       <c r="AI5" s="52"/>
       <c r="AJ5" s="53"/>
       <c r="AL5" s="53"/>
@@ -10347,41 +8408,41 @@
       <c r="AQ5" s="53"/>
     </row>
     <row r="6" spans="2:43" ht="15">
-      <c r="F6" s="118" t="s">
+      <c r="F6" s="143" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="119"/>
-      <c r="L6" s="119"/>
-      <c r="M6" s="123" t="s">
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="138" t="s">
         <v>95</v>
       </c>
-      <c r="N6" s="123"/>
-      <c r="O6" s="123"/>
-      <c r="P6" s="123"/>
-      <c r="Q6" s="123"/>
-      <c r="R6" s="123"/>
-      <c r="S6" s="123"/>
-      <c r="T6" s="123"/>
-      <c r="U6" s="123"/>
-      <c r="V6" s="123"/>
-      <c r="W6" s="123"/>
-      <c r="X6" s="123" t="s">
+      <c r="N6" s="138"/>
+      <c r="O6" s="138"/>
+      <c r="P6" s="138"/>
+      <c r="Q6" s="138"/>
+      <c r="R6" s="138"/>
+      <c r="S6" s="138"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="138"/>
+      <c r="V6" s="138"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="138" t="s">
         <v>96</v>
       </c>
-      <c r="Y6" s="123"/>
-      <c r="Z6" s="123"/>
-      <c r="AA6" s="123"/>
-      <c r="AB6" s="123"/>
-      <c r="AC6" s="123"/>
-      <c r="AD6" s="123"/>
-      <c r="AE6" s="123"/>
-      <c r="AF6" s="123"/>
-      <c r="AG6" s="123"/>
-      <c r="AH6" s="138"/>
+      <c r="Y6" s="138"/>
+      <c r="Z6" s="138"/>
+      <c r="AA6" s="138"/>
+      <c r="AB6" s="138"/>
+      <c r="AC6" s="138"/>
+      <c r="AD6" s="138"/>
+      <c r="AE6" s="138"/>
+      <c r="AF6" s="138"/>
+      <c r="AG6" s="138"/>
+      <c r="AH6" s="148"/>
       <c r="AI6" s="52"/>
       <c r="AJ6" s="53"/>
       <c r="AK6" s="54" t="s">
@@ -10395,41 +8456,41 @@
       <c r="AQ6" s="53"/>
     </row>
     <row r="7" spans="2:43">
-      <c r="F7" s="118" t="s">
+      <c r="F7" s="143" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="119"/>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="119"/>
-      <c r="L7" s="119"/>
-      <c r="M7" s="123" t="s">
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
+      <c r="K7" s="136"/>
+      <c r="L7" s="136"/>
+      <c r="M7" s="138" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="123"/>
-      <c r="O7" s="123"/>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="123"/>
-      <c r="S7" s="123"/>
-      <c r="T7" s="123"/>
-      <c r="U7" s="123"/>
-      <c r="V7" s="123"/>
-      <c r="W7" s="123"/>
-      <c r="X7" s="123" t="s">
+      <c r="N7" s="138"/>
+      <c r="O7" s="138"/>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="138"/>
+      <c r="R7" s="138"/>
+      <c r="S7" s="138"/>
+      <c r="T7" s="138"/>
+      <c r="U7" s="138"/>
+      <c r="V7" s="138"/>
+      <c r="W7" s="138"/>
+      <c r="X7" s="138" t="s">
         <v>99</v>
       </c>
-      <c r="Y7" s="123"/>
-      <c r="Z7" s="123"/>
-      <c r="AA7" s="123"/>
-      <c r="AB7" s="123"/>
-      <c r="AC7" s="123"/>
-      <c r="AD7" s="123"/>
-      <c r="AE7" s="123"/>
-      <c r="AF7" s="123"/>
-      <c r="AG7" s="123"/>
-      <c r="AH7" s="138"/>
+      <c r="Y7" s="138"/>
+      <c r="Z7" s="138"/>
+      <c r="AA7" s="138"/>
+      <c r="AB7" s="138"/>
+      <c r="AC7" s="138"/>
+      <c r="AD7" s="138"/>
+      <c r="AE7" s="138"/>
+      <c r="AF7" s="138"/>
+      <c r="AG7" s="138"/>
+      <c r="AH7" s="148"/>
       <c r="AI7" s="52"/>
       <c r="AJ7" s="53"/>
       <c r="AK7" s="53"/>
@@ -10441,41 +8502,41 @@
       <c r="AQ7" s="53"/>
     </row>
     <row r="8" spans="2:43">
-      <c r="F8" s="118" t="s">
+      <c r="F8" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="119"/>
-      <c r="K8" s="119"/>
-      <c r="L8" s="119"/>
-      <c r="M8" s="123" t="s">
+      <c r="G8" s="136"/>
+      <c r="H8" s="136"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="136"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="136"/>
+      <c r="M8" s="138" t="s">
         <v>101</v>
       </c>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="123"/>
-      <c r="Q8" s="123"/>
-      <c r="R8" s="123"/>
-      <c r="S8" s="123"/>
-      <c r="T8" s="123"/>
-      <c r="U8" s="123"/>
-      <c r="V8" s="123"/>
-      <c r="W8" s="123"/>
-      <c r="X8" s="123" t="s">
+      <c r="N8" s="138"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="138"/>
+      <c r="Q8" s="138"/>
+      <c r="R8" s="138"/>
+      <c r="S8" s="138"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="138"/>
+      <c r="W8" s="138"/>
+      <c r="X8" s="138" t="s">
         <v>102</v>
       </c>
-      <c r="Y8" s="123"/>
-      <c r="Z8" s="123"/>
-      <c r="AA8" s="123"/>
-      <c r="AB8" s="123"/>
-      <c r="AC8" s="123"/>
-      <c r="AD8" s="123"/>
-      <c r="AE8" s="123"/>
-      <c r="AF8" s="123"/>
-      <c r="AG8" s="123"/>
-      <c r="AH8" s="138"/>
+      <c r="Y8" s="138"/>
+      <c r="Z8" s="138"/>
+      <c r="AA8" s="138"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="138"/>
+      <c r="AD8" s="138"/>
+      <c r="AE8" s="138"/>
+      <c r="AF8" s="138"/>
+      <c r="AG8" s="138"/>
+      <c r="AH8" s="148"/>
       <c r="AI8" s="52"/>
       <c r="AJ8" s="53"/>
       <c r="AK8" s="53"/>
@@ -10487,158 +8548,158 @@
       <c r="AQ8" s="53"/>
     </row>
     <row r="9" spans="2:43">
-      <c r="F9" s="118" t="s">
+      <c r="F9" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="119"/>
-      <c r="M9" s="123" t="s">
+      <c r="G9" s="136"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="136"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="136"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="138" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="123"/>
-      <c r="O9" s="123"/>
-      <c r="P9" s="123"/>
-      <c r="Q9" s="123"/>
-      <c r="R9" s="123"/>
-      <c r="S9" s="123"/>
-      <c r="T9" s="123"/>
-      <c r="U9" s="123"/>
-      <c r="V9" s="123"/>
-      <c r="W9" s="123"/>
-      <c r="X9" s="123" t="s">
+      <c r="N9" s="138"/>
+      <c r="O9" s="138"/>
+      <c r="P9" s="138"/>
+      <c r="Q9" s="138"/>
+      <c r="R9" s="138"/>
+      <c r="S9" s="138"/>
+      <c r="T9" s="138"/>
+      <c r="U9" s="138"/>
+      <c r="V9" s="138"/>
+      <c r="W9" s="138"/>
+      <c r="X9" s="138" t="s">
         <v>104</v>
       </c>
-      <c r="Y9" s="123"/>
-      <c r="Z9" s="123"/>
-      <c r="AA9" s="123"/>
-      <c r="AB9" s="123"/>
-      <c r="AC9" s="123"/>
-      <c r="AD9" s="123"/>
-      <c r="AE9" s="123"/>
-      <c r="AF9" s="123"/>
-      <c r="AG9" s="123"/>
-      <c r="AH9" s="138"/>
+      <c r="Y9" s="138"/>
+      <c r="Z9" s="138"/>
+      <c r="AA9" s="138"/>
+      <c r="AB9" s="138"/>
+      <c r="AC9" s="138"/>
+      <c r="AD9" s="138"/>
+      <c r="AE9" s="138"/>
+      <c r="AF9" s="138"/>
+      <c r="AG9" s="138"/>
+      <c r="AH9" s="148"/>
     </row>
     <row r="10" spans="2:43" ht="26.25">
-      <c r="F10" s="118" t="s">
+      <c r="F10" s="143" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="123" t="s">
+      <c r="G10" s="136"/>
+      <c r="H10" s="136"/>
+      <c r="I10" s="136"/>
+      <c r="J10" s="136"/>
+      <c r="K10" s="136"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="123"/>
-      <c r="O10" s="123"/>
-      <c r="P10" s="123"/>
-      <c r="Q10" s="123"/>
-      <c r="R10" s="123"/>
-      <c r="S10" s="123"/>
-      <c r="T10" s="123"/>
-      <c r="U10" s="123"/>
-      <c r="V10" s="123"/>
-      <c r="W10" s="123"/>
-      <c r="X10" s="123" t="s">
+      <c r="N10" s="138"/>
+      <c r="O10" s="138"/>
+      <c r="P10" s="138"/>
+      <c r="Q10" s="138"/>
+      <c r="R10" s="138"/>
+      <c r="S10" s="138"/>
+      <c r="T10" s="138"/>
+      <c r="U10" s="138"/>
+      <c r="V10" s="138"/>
+      <c r="W10" s="138"/>
+      <c r="X10" s="138" t="s">
         <v>106</v>
       </c>
-      <c r="Y10" s="123"/>
-      <c r="Z10" s="123"/>
-      <c r="AA10" s="123"/>
-      <c r="AB10" s="123"/>
-      <c r="AC10" s="123"/>
-      <c r="AD10" s="123"/>
-      <c r="AE10" s="123"/>
-      <c r="AF10" s="123"/>
-      <c r="AG10" s="123"/>
-      <c r="AH10" s="138"/>
+      <c r="Y10" s="138"/>
+      <c r="Z10" s="138"/>
+      <c r="AA10" s="138"/>
+      <c r="AB10" s="138"/>
+      <c r="AC10" s="138"/>
+      <c r="AD10" s="138"/>
+      <c r="AE10" s="138"/>
+      <c r="AF10" s="138"/>
+      <c r="AG10" s="138"/>
+      <c r="AH10" s="148"/>
       <c r="AK10" s="55" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="11" spans="2:43" ht="15">
-      <c r="F11" s="118" t="s">
+      <c r="F11" s="143" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="119"/>
-      <c r="H11" s="119"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="119"/>
-      <c r="K11" s="119"/>
-      <c r="L11" s="119"/>
-      <c r="M11" s="123" t="s">
+      <c r="G11" s="136"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="138" t="s">
         <v>108</v>
       </c>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="123"/>
-      <c r="S11" s="123"/>
-      <c r="T11" s="123"/>
-      <c r="U11" s="123"/>
-      <c r="V11" s="123"/>
-      <c r="W11" s="123"/>
-      <c r="X11" s="123" t="s">
+      <c r="N11" s="138"/>
+      <c r="O11" s="138"/>
+      <c r="P11" s="138"/>
+      <c r="Q11" s="138"/>
+      <c r="R11" s="138"/>
+      <c r="S11" s="138"/>
+      <c r="T11" s="138"/>
+      <c r="U11" s="138"/>
+      <c r="V11" s="138"/>
+      <c r="W11" s="138"/>
+      <c r="X11" s="138" t="s">
         <v>109</v>
       </c>
-      <c r="Y11" s="123"/>
-      <c r="Z11" s="123"/>
-      <c r="AA11" s="123"/>
-      <c r="AB11" s="123"/>
-      <c r="AC11" s="123"/>
-      <c r="AD11" s="123"/>
-      <c r="AE11" s="123"/>
-      <c r="AF11" s="123"/>
-      <c r="AG11" s="123"/>
-      <c r="AH11" s="138"/>
+      <c r="Y11" s="138"/>
+      <c r="Z11" s="138"/>
+      <c r="AA11" s="138"/>
+      <c r="AB11" s="138"/>
+      <c r="AC11" s="138"/>
+      <c r="AD11" s="138"/>
+      <c r="AE11" s="138"/>
+      <c r="AF11" s="138"/>
+      <c r="AG11" s="138"/>
+      <c r="AH11" s="148"/>
       <c r="AL11" s="56" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="12" spans="2:43" ht="15" thickBot="1">
-      <c r="F12" s="120" t="s">
+      <c r="F12" s="144" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="126" t="s">
+      <c r="G12" s="137"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
+      <c r="L12" s="137"/>
+      <c r="M12" s="139" t="s">
         <v>111</v>
       </c>
-      <c r="N12" s="126"/>
-      <c r="O12" s="126"/>
-      <c r="P12" s="126"/>
-      <c r="Q12" s="126"/>
-      <c r="R12" s="126"/>
-      <c r="S12" s="126"/>
-      <c r="T12" s="126"/>
-      <c r="U12" s="126"/>
-      <c r="V12" s="126"/>
-      <c r="W12" s="126"/>
-      <c r="X12" s="126" t="s">
+      <c r="N12" s="139"/>
+      <c r="O12" s="139"/>
+      <c r="P12" s="139"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="139"/>
+      <c r="T12" s="139"/>
+      <c r="U12" s="139"/>
+      <c r="V12" s="139"/>
+      <c r="W12" s="139"/>
+      <c r="X12" s="139" t="s">
         <v>112</v>
       </c>
-      <c r="Y12" s="126"/>
-      <c r="Z12" s="126"/>
-      <c r="AA12" s="126"/>
-      <c r="AB12" s="126"/>
-      <c r="AC12" s="126"/>
-      <c r="AD12" s="126"/>
-      <c r="AE12" s="126"/>
-      <c r="AF12" s="126"/>
-      <c r="AG12" s="126"/>
-      <c r="AH12" s="139"/>
+      <c r="Y12" s="139"/>
+      <c r="Z12" s="139"/>
+      <c r="AA12" s="139"/>
+      <c r="AB12" s="139"/>
+      <c r="AC12" s="139"/>
+      <c r="AD12" s="139"/>
+      <c r="AE12" s="139"/>
+      <c r="AF12" s="139"/>
+      <c r="AG12" s="139"/>
+      <c r="AH12" s="149"/>
     </row>
     <row r="13" spans="2:43" ht="15" thickBot="1"/>
     <row r="14" spans="2:43" s="46" customFormat="1" ht="15.75" thickBot="1">
@@ -10998,20 +9059,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="M5:W5"/>
-    <mergeCell ref="M6:W6"/>
-    <mergeCell ref="M7:W7"/>
-    <mergeCell ref="M8:W8"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="F12:L12"/>
-    <mergeCell ref="F6:L6"/>
-    <mergeCell ref="F7:L7"/>
-    <mergeCell ref="F8:L8"/>
-    <mergeCell ref="F9:L9"/>
-    <mergeCell ref="F10:L10"/>
     <mergeCell ref="X11:AH11"/>
     <mergeCell ref="X12:AH12"/>
     <mergeCell ref="M12:W12"/>
@@ -11028,6 +9075,20 @@
     <mergeCell ref="M11:W11"/>
     <mergeCell ref="M3:W3"/>
     <mergeCell ref="M4:W4"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="F12:L12"/>
+    <mergeCell ref="F6:L6"/>
+    <mergeCell ref="F7:L7"/>
+    <mergeCell ref="F8:L8"/>
+    <mergeCell ref="F9:L9"/>
+    <mergeCell ref="F10:L10"/>
+    <mergeCell ref="M5:W5"/>
+    <mergeCell ref="M6:W6"/>
+    <mergeCell ref="M7:W7"/>
+    <mergeCell ref="M8:W8"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11043,1017 +9104,1017 @@
       <c r="B1" s="74"/>
     </row>
     <row r="2" spans="2:65" ht="15">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="106" t="s">
         <v>360</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155"/>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155"/>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155"/>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155"/>
-      <c r="U2" s="155"/>
-      <c r="V2" s="155"/>
-      <c r="W2" s="155"/>
-      <c r="X2" s="155"/>
-      <c r="Y2" s="155"/>
-      <c r="Z2" s="155"/>
-      <c r="AA2" s="155"/>
-      <c r="AB2" s="155"/>
-      <c r="AC2" s="155"/>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="155"/>
-      <c r="AF2" s="155"/>
-      <c r="AG2" s="155"/>
-      <c r="AH2" s="155"/>
-      <c r="AI2" s="155"/>
-      <c r="AJ2" s="155"/>
-      <c r="AK2" s="155"/>
-      <c r="AL2" s="155"/>
-      <c r="AM2" s="155"/>
-      <c r="AN2" s="155"/>
-      <c r="AO2" s="155"/>
-      <c r="AP2" s="155"/>
-      <c r="AQ2" s="155"/>
-      <c r="AR2" s="155"/>
-      <c r="AS2" s="155"/>
-      <c r="AT2" s="155"/>
-      <c r="AU2" s="155"/>
-      <c r="AV2" s="155"/>
-      <c r="AW2" s="155"/>
-      <c r="AX2" s="155"/>
-      <c r="AY2" s="155"/>
-      <c r="AZ2" s="155"/>
-      <c r="BA2" s="156"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="107"/>
+      <c r="T2" s="107"/>
+      <c r="U2" s="107"/>
+      <c r="V2" s="107"/>
+      <c r="W2" s="107"/>
+      <c r="X2" s="107"/>
+      <c r="Y2" s="107"/>
+      <c r="Z2" s="107"/>
+      <c r="AA2" s="107"/>
+      <c r="AB2" s="107"/>
+      <c r="AC2" s="107"/>
+      <c r="AD2" s="107"/>
+      <c r="AE2" s="107"/>
+      <c r="AF2" s="107"/>
+      <c r="AG2" s="107"/>
+      <c r="AH2" s="107"/>
+      <c r="AI2" s="107"/>
+      <c r="AJ2" s="107"/>
+      <c r="AK2" s="107"/>
+      <c r="AL2" s="107"/>
+      <c r="AM2" s="107"/>
+      <c r="AN2" s="107"/>
+      <c r="AO2" s="107"/>
+      <c r="AP2" s="107"/>
+      <c r="AQ2" s="107"/>
+      <c r="AR2" s="107"/>
+      <c r="AS2" s="107"/>
+      <c r="AT2" s="107"/>
+      <c r="AU2" s="107"/>
+      <c r="AV2" s="107"/>
+      <c r="AW2" s="107"/>
+      <c r="AX2" s="107"/>
+      <c r="AY2" s="107"/>
+      <c r="AZ2" s="107"/>
+      <c r="BA2" s="108"/>
     </row>
     <row r="3" spans="2:65" ht="15.75" thickBot="1">
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="109" t="s">
         <v>361</v>
       </c>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
-      <c r="L3" s="158"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="158"/>
-      <c r="O3" s="158"/>
-      <c r="P3" s="158"/>
-      <c r="Q3" s="158"/>
-      <c r="R3" s="158"/>
-      <c r="S3" s="158"/>
-      <c r="T3" s="158"/>
-      <c r="U3" s="158"/>
-      <c r="V3" s="158"/>
-      <c r="W3" s="158"/>
-      <c r="X3" s="158"/>
-      <c r="Y3" s="158"/>
-      <c r="Z3" s="158"/>
-      <c r="AA3" s="158"/>
-      <c r="AB3" s="158"/>
-      <c r="AC3" s="158"/>
-      <c r="AD3" s="158"/>
-      <c r="AE3" s="158"/>
-      <c r="AF3" s="158"/>
-      <c r="AG3" s="158"/>
-      <c r="AH3" s="158"/>
-      <c r="AI3" s="158"/>
-      <c r="AJ3" s="158"/>
-      <c r="AK3" s="158"/>
-      <c r="AL3" s="158"/>
-      <c r="AM3" s="158"/>
-      <c r="AN3" s="158"/>
-      <c r="AO3" s="158"/>
-      <c r="AP3" s="158"/>
-      <c r="AQ3" s="158"/>
-      <c r="AR3" s="158"/>
-      <c r="AS3" s="158"/>
-      <c r="AT3" s="158"/>
-      <c r="AU3" s="158"/>
-      <c r="AV3" s="158"/>
-      <c r="AW3" s="158"/>
-      <c r="AX3" s="158"/>
-      <c r="AY3" s="158"/>
-      <c r="AZ3" s="158"/>
-      <c r="BA3" s="159"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="110"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="110"/>
+      <c r="R3" s="110"/>
+      <c r="S3" s="110"/>
+      <c r="T3" s="110"/>
+      <c r="U3" s="110"/>
+      <c r="V3" s="110"/>
+      <c r="W3" s="110"/>
+      <c r="X3" s="110"/>
+      <c r="Y3" s="110"/>
+      <c r="Z3" s="110"/>
+      <c r="AA3" s="110"/>
+      <c r="AB3" s="110"/>
+      <c r="AC3" s="110"/>
+      <c r="AD3" s="110"/>
+      <c r="AE3" s="110"/>
+      <c r="AF3" s="110"/>
+      <c r="AG3" s="110"/>
+      <c r="AH3" s="110"/>
+      <c r="AI3" s="110"/>
+      <c r="AJ3" s="110"/>
+      <c r="AK3" s="110"/>
+      <c r="AL3" s="110"/>
+      <c r="AM3" s="110"/>
+      <c r="AN3" s="110"/>
+      <c r="AO3" s="110"/>
+      <c r="AP3" s="110"/>
+      <c r="AQ3" s="110"/>
+      <c r="AR3" s="110"/>
+      <c r="AS3" s="110"/>
+      <c r="AT3" s="110"/>
+      <c r="AU3" s="110"/>
+      <c r="AV3" s="110"/>
+      <c r="AW3" s="110"/>
+      <c r="AX3" s="110"/>
+      <c r="AY3" s="110"/>
+      <c r="AZ3" s="110"/>
+      <c r="BA3" s="111"/>
     </row>
     <row r="4" spans="2:65" ht="15" thickBot="1"/>
     <row r="5" spans="2:65" ht="15">
-      <c r="C5" s="144" t="s">
+      <c r="C5" s="163" t="s">
         <v>300</v>
       </c>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145" t="s">
+      <c r="D5" s="155"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
+      <c r="G5" s="155" t="s">
         <v>301</v>
       </c>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145"/>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="145"/>
-      <c r="R5" s="145"/>
-      <c r="S5" s="145"/>
-      <c r="T5" s="145" t="s">
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="155" t="s">
         <v>302</v>
       </c>
-      <c r="U5" s="145"/>
-      <c r="V5" s="145"/>
-      <c r="W5" s="145"/>
-      <c r="X5" s="145"/>
-      <c r="Y5" s="145"/>
-      <c r="Z5" s="145"/>
-      <c r="AA5" s="145"/>
-      <c r="AB5" s="145"/>
-      <c r="AC5" s="145"/>
-      <c r="AD5" s="145"/>
-      <c r="AE5" s="145"/>
-      <c r="AF5" s="145"/>
-      <c r="AG5" s="145" t="s">
+      <c r="U5" s="155"/>
+      <c r="V5" s="155"/>
+      <c r="W5" s="155"/>
+      <c r="X5" s="155"/>
+      <c r="Y5" s="155"/>
+      <c r="Z5" s="155"/>
+      <c r="AA5" s="155"/>
+      <c r="AB5" s="155"/>
+      <c r="AC5" s="155"/>
+      <c r="AD5" s="155"/>
+      <c r="AE5" s="155"/>
+      <c r="AF5" s="155"/>
+      <c r="AG5" s="155" t="s">
         <v>303</v>
       </c>
-      <c r="AH5" s="145"/>
-      <c r="AI5" s="145"/>
-      <c r="AJ5" s="145"/>
-      <c r="AK5" s="145"/>
-      <c r="AL5" s="145"/>
-      <c r="AM5" s="145"/>
-      <c r="AN5" s="145"/>
-      <c r="AO5" s="145"/>
-      <c r="AP5" s="145"/>
-      <c r="AQ5" s="145"/>
-      <c r="AR5" s="145"/>
-      <c r="AS5" s="145"/>
-      <c r="AT5" s="145"/>
-      <c r="AU5" s="145"/>
-      <c r="AV5" s="145" t="s">
+      <c r="AH5" s="155"/>
+      <c r="AI5" s="155"/>
+      <c r="AJ5" s="155"/>
+      <c r="AK5" s="155"/>
+      <c r="AL5" s="155"/>
+      <c r="AM5" s="155"/>
+      <c r="AN5" s="155"/>
+      <c r="AO5" s="155"/>
+      <c r="AP5" s="155"/>
+      <c r="AQ5" s="155"/>
+      <c r="AR5" s="155"/>
+      <c r="AS5" s="155"/>
+      <c r="AT5" s="155"/>
+      <c r="AU5" s="155"/>
+      <c r="AV5" s="155" t="s">
         <v>304</v>
       </c>
-      <c r="AW5" s="145"/>
-      <c r="AX5" s="145"/>
-      <c r="AY5" s="145"/>
-      <c r="AZ5" s="145"/>
-      <c r="BA5" s="145"/>
-      <c r="BB5" s="145"/>
-      <c r="BC5" s="145"/>
-      <c r="BD5" s="145"/>
-      <c r="BE5" s="145"/>
-      <c r="BF5" s="145"/>
-      <c r="BG5" s="145"/>
-      <c r="BH5" s="145"/>
-      <c r="BI5" s="145"/>
-      <c r="BJ5" s="145"/>
-      <c r="BK5" s="145"/>
-      <c r="BL5" s="145"/>
-      <c r="BM5" s="146"/>
+      <c r="AW5" s="155"/>
+      <c r="AX5" s="155"/>
+      <c r="AY5" s="155"/>
+      <c r="AZ5" s="155"/>
+      <c r="BA5" s="155"/>
+      <c r="BB5" s="155"/>
+      <c r="BC5" s="155"/>
+      <c r="BD5" s="155"/>
+      <c r="BE5" s="155"/>
+      <c r="BF5" s="155"/>
+      <c r="BG5" s="155"/>
+      <c r="BH5" s="155"/>
+      <c r="BI5" s="155"/>
+      <c r="BJ5" s="155"/>
+      <c r="BK5" s="155"/>
+      <c r="BL5" s="155"/>
+      <c r="BM5" s="156"/>
     </row>
     <row r="6" spans="2:65" ht="15">
-      <c r="C6" s="147" t="s">
+      <c r="C6" s="159" t="s">
         <v>305</v>
       </c>
-      <c r="D6" s="141"/>
-      <c r="E6" s="141"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="142" t="s">
+      <c r="D6" s="160"/>
+      <c r="E6" s="160"/>
+      <c r="F6" s="160"/>
+      <c r="G6" s="157" t="s">
         <v>306</v>
       </c>
-      <c r="H6" s="142"/>
-      <c r="I6" s="142"/>
-      <c r="J6" s="142"/>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="142"/>
-      <c r="N6" s="142"/>
-      <c r="O6" s="142"/>
-      <c r="P6" s="142"/>
-      <c r="Q6" s="142"/>
-      <c r="R6" s="142"/>
-      <c r="S6" s="142"/>
-      <c r="T6" s="143" t="s">
+      <c r="H6" s="157"/>
+      <c r="I6" s="157"/>
+      <c r="J6" s="157"/>
+      <c r="K6" s="157"/>
+      <c r="L6" s="157"/>
+      <c r="M6" s="157"/>
+      <c r="N6" s="157"/>
+      <c r="O6" s="157"/>
+      <c r="P6" s="157"/>
+      <c r="Q6" s="157"/>
+      <c r="R6" s="157"/>
+      <c r="S6" s="157"/>
+      <c r="T6" s="151" t="s">
         <v>307</v>
       </c>
-      <c r="U6" s="143"/>
-      <c r="V6" s="143"/>
-      <c r="W6" s="143"/>
-      <c r="X6" s="143"/>
-      <c r="Y6" s="143"/>
-      <c r="Z6" s="143"/>
-      <c r="AA6" s="143"/>
-      <c r="AB6" s="143"/>
-      <c r="AC6" s="143"/>
-      <c r="AD6" s="143"/>
-      <c r="AE6" s="143"/>
-      <c r="AF6" s="143"/>
-      <c r="AG6" s="143" t="s">
+      <c r="U6" s="151"/>
+      <c r="V6" s="151"/>
+      <c r="W6" s="151"/>
+      <c r="X6" s="151"/>
+      <c r="Y6" s="151"/>
+      <c r="Z6" s="151"/>
+      <c r="AA6" s="151"/>
+      <c r="AB6" s="151"/>
+      <c r="AC6" s="151"/>
+      <c r="AD6" s="151"/>
+      <c r="AE6" s="151"/>
+      <c r="AF6" s="151"/>
+      <c r="AG6" s="151" t="s">
         <v>308</v>
       </c>
-      <c r="AH6" s="143"/>
-      <c r="AI6" s="143"/>
-      <c r="AJ6" s="143"/>
-      <c r="AK6" s="143"/>
-      <c r="AL6" s="143"/>
-      <c r="AM6" s="143"/>
-      <c r="AN6" s="143"/>
-      <c r="AO6" s="143"/>
-      <c r="AP6" s="143"/>
-      <c r="AQ6" s="143"/>
-      <c r="AR6" s="143"/>
-      <c r="AS6" s="143"/>
-      <c r="AT6" s="143"/>
-      <c r="AU6" s="143"/>
-      <c r="AV6" s="143" t="s">
+      <c r="AH6" s="151"/>
+      <c r="AI6" s="151"/>
+      <c r="AJ6" s="151"/>
+      <c r="AK6" s="151"/>
+      <c r="AL6" s="151"/>
+      <c r="AM6" s="151"/>
+      <c r="AN6" s="151"/>
+      <c r="AO6" s="151"/>
+      <c r="AP6" s="151"/>
+      <c r="AQ6" s="151"/>
+      <c r="AR6" s="151"/>
+      <c r="AS6" s="151"/>
+      <c r="AT6" s="151"/>
+      <c r="AU6" s="151"/>
+      <c r="AV6" s="151" t="s">
         <v>309</v>
       </c>
-      <c r="AW6" s="143"/>
-      <c r="AX6" s="143"/>
-      <c r="AY6" s="143"/>
-      <c r="AZ6" s="143"/>
-      <c r="BA6" s="143"/>
-      <c r="BB6" s="143"/>
-      <c r="BC6" s="143"/>
-      <c r="BD6" s="143"/>
-      <c r="BE6" s="143"/>
-      <c r="BF6" s="143"/>
-      <c r="BG6" s="143"/>
-      <c r="BH6" s="143"/>
-      <c r="BI6" s="143"/>
-      <c r="BJ6" s="143"/>
-      <c r="BK6" s="143"/>
-      <c r="BL6" s="143"/>
-      <c r="BM6" s="148"/>
+      <c r="AW6" s="151"/>
+      <c r="AX6" s="151"/>
+      <c r="AY6" s="151"/>
+      <c r="AZ6" s="151"/>
+      <c r="BA6" s="151"/>
+      <c r="BB6" s="151"/>
+      <c r="BC6" s="151"/>
+      <c r="BD6" s="151"/>
+      <c r="BE6" s="151"/>
+      <c r="BF6" s="151"/>
+      <c r="BG6" s="151"/>
+      <c r="BH6" s="151"/>
+      <c r="BI6" s="151"/>
+      <c r="BJ6" s="151"/>
+      <c r="BK6" s="151"/>
+      <c r="BL6" s="151"/>
+      <c r="BM6" s="152"/>
     </row>
     <row r="7" spans="2:65" ht="15">
-      <c r="C7" s="147" t="s">
+      <c r="C7" s="159" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="142" t="s">
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="157" t="s">
         <v>310</v>
       </c>
-      <c r="H7" s="142"/>
-      <c r="I7" s="142"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="142"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="142"/>
-      <c r="N7" s="142"/>
-      <c r="O7" s="142"/>
-      <c r="P7" s="142"/>
-      <c r="Q7" s="142"/>
-      <c r="R7" s="142"/>
-      <c r="S7" s="142"/>
-      <c r="T7" s="143" t="s">
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="157"/>
+      <c r="K7" s="157"/>
+      <c r="L7" s="157"/>
+      <c r="M7" s="157"/>
+      <c r="N7" s="157"/>
+      <c r="O7" s="157"/>
+      <c r="P7" s="157"/>
+      <c r="Q7" s="157"/>
+      <c r="R7" s="157"/>
+      <c r="S7" s="157"/>
+      <c r="T7" s="151" t="s">
         <v>311</v>
       </c>
-      <c r="U7" s="143"/>
-      <c r="V7" s="143"/>
-      <c r="W7" s="143"/>
-      <c r="X7" s="143"/>
-      <c r="Y7" s="143"/>
-      <c r="Z7" s="143"/>
-      <c r="AA7" s="143"/>
-      <c r="AB7" s="143"/>
-      <c r="AC7" s="143"/>
-      <c r="AD7" s="143"/>
-      <c r="AE7" s="143"/>
-      <c r="AF7" s="143"/>
-      <c r="AG7" s="142" t="s">
+      <c r="U7" s="151"/>
+      <c r="V7" s="151"/>
+      <c r="W7" s="151"/>
+      <c r="X7" s="151"/>
+      <c r="Y7" s="151"/>
+      <c r="Z7" s="151"/>
+      <c r="AA7" s="151"/>
+      <c r="AB7" s="151"/>
+      <c r="AC7" s="151"/>
+      <c r="AD7" s="151"/>
+      <c r="AE7" s="151"/>
+      <c r="AF7" s="151"/>
+      <c r="AG7" s="157" t="s">
         <v>312</v>
       </c>
-      <c r="AH7" s="142"/>
-      <c r="AI7" s="142"/>
-      <c r="AJ7" s="142"/>
-      <c r="AK7" s="142"/>
-      <c r="AL7" s="142"/>
-      <c r="AM7" s="142"/>
-      <c r="AN7" s="142"/>
-      <c r="AO7" s="142"/>
-      <c r="AP7" s="142"/>
-      <c r="AQ7" s="142"/>
-      <c r="AR7" s="142"/>
-      <c r="AS7" s="142"/>
-      <c r="AT7" s="142"/>
-      <c r="AU7" s="142"/>
-      <c r="AV7" s="143" t="s">
+      <c r="AH7" s="157"/>
+      <c r="AI7" s="157"/>
+      <c r="AJ7" s="157"/>
+      <c r="AK7" s="157"/>
+      <c r="AL7" s="157"/>
+      <c r="AM7" s="157"/>
+      <c r="AN7" s="157"/>
+      <c r="AO7" s="157"/>
+      <c r="AP7" s="157"/>
+      <c r="AQ7" s="157"/>
+      <c r="AR7" s="157"/>
+      <c r="AS7" s="157"/>
+      <c r="AT7" s="157"/>
+      <c r="AU7" s="157"/>
+      <c r="AV7" s="151" t="s">
         <v>313</v>
       </c>
-      <c r="AW7" s="143"/>
-      <c r="AX7" s="143"/>
-      <c r="AY7" s="143"/>
-      <c r="AZ7" s="143"/>
-      <c r="BA7" s="143"/>
-      <c r="BB7" s="143"/>
-      <c r="BC7" s="143"/>
-      <c r="BD7" s="143"/>
-      <c r="BE7" s="143"/>
-      <c r="BF7" s="143"/>
-      <c r="BG7" s="143"/>
-      <c r="BH7" s="143"/>
-      <c r="BI7" s="143"/>
-      <c r="BJ7" s="143"/>
-      <c r="BK7" s="143"/>
-      <c r="BL7" s="143"/>
-      <c r="BM7" s="148"/>
+      <c r="AW7" s="151"/>
+      <c r="AX7" s="151"/>
+      <c r="AY7" s="151"/>
+      <c r="AZ7" s="151"/>
+      <c r="BA7" s="151"/>
+      <c r="BB7" s="151"/>
+      <c r="BC7" s="151"/>
+      <c r="BD7" s="151"/>
+      <c r="BE7" s="151"/>
+      <c r="BF7" s="151"/>
+      <c r="BG7" s="151"/>
+      <c r="BH7" s="151"/>
+      <c r="BI7" s="151"/>
+      <c r="BJ7" s="151"/>
+      <c r="BK7" s="151"/>
+      <c r="BL7" s="151"/>
+      <c r="BM7" s="152"/>
     </row>
     <row r="8" spans="2:65" ht="15">
-      <c r="C8" s="147" t="s">
+      <c r="C8" s="159" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="141"/>
-      <c r="G8" s="142" t="s">
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
+      <c r="G8" s="157" t="s">
         <v>314</v>
       </c>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="142"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="142"/>
-      <c r="N8" s="142"/>
-      <c r="O8" s="142"/>
-      <c r="P8" s="142"/>
-      <c r="Q8" s="142"/>
-      <c r="R8" s="142"/>
-      <c r="S8" s="142"/>
-      <c r="T8" s="143" t="s">
+      <c r="H8" s="157"/>
+      <c r="I8" s="157"/>
+      <c r="J8" s="157"/>
+      <c r="K8" s="157"/>
+      <c r="L8" s="157"/>
+      <c r="M8" s="157"/>
+      <c r="N8" s="157"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="157"/>
+      <c r="Q8" s="157"/>
+      <c r="R8" s="157"/>
+      <c r="S8" s="157"/>
+      <c r="T8" s="151" t="s">
         <v>315</v>
       </c>
-      <c r="U8" s="143"/>
-      <c r="V8" s="143"/>
-      <c r="W8" s="143"/>
-      <c r="X8" s="143"/>
-      <c r="Y8" s="143"/>
-      <c r="Z8" s="143"/>
-      <c r="AA8" s="143"/>
-      <c r="AB8" s="143"/>
-      <c r="AC8" s="143"/>
-      <c r="AD8" s="143"/>
-      <c r="AE8" s="143"/>
-      <c r="AF8" s="143"/>
-      <c r="AG8" s="142" t="s">
+      <c r="U8" s="151"/>
+      <c r="V8" s="151"/>
+      <c r="W8" s="151"/>
+      <c r="X8" s="151"/>
+      <c r="Y8" s="151"/>
+      <c r="Z8" s="151"/>
+      <c r="AA8" s="151"/>
+      <c r="AB8" s="151"/>
+      <c r="AC8" s="151"/>
+      <c r="AD8" s="151"/>
+      <c r="AE8" s="151"/>
+      <c r="AF8" s="151"/>
+      <c r="AG8" s="157" t="s">
         <v>316</v>
       </c>
-      <c r="AH8" s="142"/>
-      <c r="AI8" s="142"/>
-      <c r="AJ8" s="142"/>
-      <c r="AK8" s="142"/>
-      <c r="AL8" s="142"/>
-      <c r="AM8" s="142"/>
-      <c r="AN8" s="142"/>
-      <c r="AO8" s="142"/>
-      <c r="AP8" s="142"/>
-      <c r="AQ8" s="142"/>
-      <c r="AR8" s="142"/>
-      <c r="AS8" s="142"/>
-      <c r="AT8" s="142"/>
-      <c r="AU8" s="142"/>
-      <c r="AV8" s="143" t="s">
+      <c r="AH8" s="157"/>
+      <c r="AI8" s="157"/>
+      <c r="AJ8" s="157"/>
+      <c r="AK8" s="157"/>
+      <c r="AL8" s="157"/>
+      <c r="AM8" s="157"/>
+      <c r="AN8" s="157"/>
+      <c r="AO8" s="157"/>
+      <c r="AP8" s="157"/>
+      <c r="AQ8" s="157"/>
+      <c r="AR8" s="157"/>
+      <c r="AS8" s="157"/>
+      <c r="AT8" s="157"/>
+      <c r="AU8" s="157"/>
+      <c r="AV8" s="151" t="s">
         <v>317</v>
       </c>
-      <c r="AW8" s="143"/>
-      <c r="AX8" s="143"/>
-      <c r="AY8" s="143"/>
-      <c r="AZ8" s="143"/>
-      <c r="BA8" s="143"/>
-      <c r="BB8" s="143"/>
-      <c r="BC8" s="143"/>
-      <c r="BD8" s="143"/>
-      <c r="BE8" s="143"/>
-      <c r="BF8" s="143"/>
-      <c r="BG8" s="143"/>
-      <c r="BH8" s="143"/>
-      <c r="BI8" s="143"/>
-      <c r="BJ8" s="143"/>
-      <c r="BK8" s="143"/>
-      <c r="BL8" s="143"/>
-      <c r="BM8" s="148"/>
+      <c r="AW8" s="151"/>
+      <c r="AX8" s="151"/>
+      <c r="AY8" s="151"/>
+      <c r="AZ8" s="151"/>
+      <c r="BA8" s="151"/>
+      <c r="BB8" s="151"/>
+      <c r="BC8" s="151"/>
+      <c r="BD8" s="151"/>
+      <c r="BE8" s="151"/>
+      <c r="BF8" s="151"/>
+      <c r="BG8" s="151"/>
+      <c r="BH8" s="151"/>
+      <c r="BI8" s="151"/>
+      <c r="BJ8" s="151"/>
+      <c r="BK8" s="151"/>
+      <c r="BL8" s="151"/>
+      <c r="BM8" s="152"/>
     </row>
     <row r="9" spans="2:65" ht="15">
-      <c r="C9" s="147" t="s">
+      <c r="C9" s="159" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="141"/>
-      <c r="E9" s="141"/>
-      <c r="F9" s="141"/>
-      <c r="G9" s="142" t="s">
+      <c r="D9" s="160"/>
+      <c r="E9" s="160"/>
+      <c r="F9" s="160"/>
+      <c r="G9" s="157" t="s">
         <v>318</v>
       </c>
-      <c r="H9" s="142"/>
-      <c r="I9" s="142"/>
-      <c r="J9" s="142"/>
-      <c r="K9" s="142"/>
-      <c r="L9" s="142"/>
-      <c r="M9" s="142"/>
-      <c r="N9" s="142"/>
-      <c r="O9" s="142"/>
-      <c r="P9" s="142"/>
-      <c r="Q9" s="142"/>
-      <c r="R9" s="142"/>
-      <c r="S9" s="142"/>
-      <c r="T9" s="143" t="s">
+      <c r="H9" s="157"/>
+      <c r="I9" s="157"/>
+      <c r="J9" s="157"/>
+      <c r="K9" s="157"/>
+      <c r="L9" s="157"/>
+      <c r="M9" s="157"/>
+      <c r="N9" s="157"/>
+      <c r="O9" s="157"/>
+      <c r="P9" s="157"/>
+      <c r="Q9" s="157"/>
+      <c r="R9" s="157"/>
+      <c r="S9" s="157"/>
+      <c r="T9" s="151" t="s">
         <v>319</v>
       </c>
-      <c r="U9" s="143"/>
-      <c r="V9" s="143"/>
-      <c r="W9" s="143"/>
-      <c r="X9" s="143"/>
-      <c r="Y9" s="143"/>
-      <c r="Z9" s="143"/>
-      <c r="AA9" s="143"/>
-      <c r="AB9" s="143"/>
-      <c r="AC9" s="143"/>
-      <c r="AD9" s="143"/>
-      <c r="AE9" s="143"/>
-      <c r="AF9" s="143"/>
-      <c r="AG9" s="142" t="s">
+      <c r="U9" s="151"/>
+      <c r="V9" s="151"/>
+      <c r="W9" s="151"/>
+      <c r="X9" s="151"/>
+      <c r="Y9" s="151"/>
+      <c r="Z9" s="151"/>
+      <c r="AA9" s="151"/>
+      <c r="AB9" s="151"/>
+      <c r="AC9" s="151"/>
+      <c r="AD9" s="151"/>
+      <c r="AE9" s="151"/>
+      <c r="AF9" s="151"/>
+      <c r="AG9" s="157" t="s">
         <v>320</v>
       </c>
-      <c r="AH9" s="142"/>
-      <c r="AI9" s="142"/>
-      <c r="AJ9" s="142"/>
-      <c r="AK9" s="142"/>
-      <c r="AL9" s="142"/>
-      <c r="AM9" s="142"/>
-      <c r="AN9" s="142"/>
-      <c r="AO9" s="142"/>
-      <c r="AP9" s="142"/>
-      <c r="AQ9" s="142"/>
-      <c r="AR9" s="142"/>
-      <c r="AS9" s="142"/>
-      <c r="AT9" s="142"/>
-      <c r="AU9" s="142"/>
-      <c r="AV9" s="143" t="s">
+      <c r="AH9" s="157"/>
+      <c r="AI9" s="157"/>
+      <c r="AJ9" s="157"/>
+      <c r="AK9" s="157"/>
+      <c r="AL9" s="157"/>
+      <c r="AM9" s="157"/>
+      <c r="AN9" s="157"/>
+      <c r="AO9" s="157"/>
+      <c r="AP9" s="157"/>
+      <c r="AQ9" s="157"/>
+      <c r="AR9" s="157"/>
+      <c r="AS9" s="157"/>
+      <c r="AT9" s="157"/>
+      <c r="AU9" s="157"/>
+      <c r="AV9" s="151" t="s">
         <v>321</v>
       </c>
-      <c r="AW9" s="143"/>
-      <c r="AX9" s="143"/>
-      <c r="AY9" s="143"/>
-      <c r="AZ9" s="143"/>
-      <c r="BA9" s="143"/>
-      <c r="BB9" s="143"/>
-      <c r="BC9" s="143"/>
-      <c r="BD9" s="143"/>
-      <c r="BE9" s="143"/>
-      <c r="BF9" s="143"/>
-      <c r="BG9" s="143"/>
-      <c r="BH9" s="143"/>
-      <c r="BI9" s="143"/>
-      <c r="BJ9" s="143"/>
-      <c r="BK9" s="143"/>
-      <c r="BL9" s="143"/>
-      <c r="BM9" s="148"/>
+      <c r="AW9" s="151"/>
+      <c r="AX9" s="151"/>
+      <c r="AY9" s="151"/>
+      <c r="AZ9" s="151"/>
+      <c r="BA9" s="151"/>
+      <c r="BB9" s="151"/>
+      <c r="BC9" s="151"/>
+      <c r="BD9" s="151"/>
+      <c r="BE9" s="151"/>
+      <c r="BF9" s="151"/>
+      <c r="BG9" s="151"/>
+      <c r="BH9" s="151"/>
+      <c r="BI9" s="151"/>
+      <c r="BJ9" s="151"/>
+      <c r="BK9" s="151"/>
+      <c r="BL9" s="151"/>
+      <c r="BM9" s="152"/>
     </row>
     <row r="10" spans="2:65" ht="15">
-      <c r="C10" s="147" t="s">
+      <c r="C10" s="159" t="s">
         <v>322</v>
       </c>
-      <c r="D10" s="141"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="142" t="s">
+      <c r="D10" s="160"/>
+      <c r="E10" s="160"/>
+      <c r="F10" s="160"/>
+      <c r="G10" s="157" t="s">
         <v>323</v>
       </c>
-      <c r="H10" s="142"/>
-      <c r="I10" s="142"/>
-      <c r="J10" s="142"/>
-      <c r="K10" s="142"/>
-      <c r="L10" s="142"/>
-      <c r="M10" s="142"/>
-      <c r="N10" s="142"/>
-      <c r="O10" s="142"/>
-      <c r="P10" s="142"/>
-      <c r="Q10" s="142"/>
-      <c r="R10" s="142"/>
-      <c r="S10" s="142"/>
-      <c r="T10" s="143" t="s">
+      <c r="H10" s="157"/>
+      <c r="I10" s="157"/>
+      <c r="J10" s="157"/>
+      <c r="K10" s="157"/>
+      <c r="L10" s="157"/>
+      <c r="M10" s="157"/>
+      <c r="N10" s="157"/>
+      <c r="O10" s="157"/>
+      <c r="P10" s="157"/>
+      <c r="Q10" s="157"/>
+      <c r="R10" s="157"/>
+      <c r="S10" s="157"/>
+      <c r="T10" s="151" t="s">
         <v>324</v>
       </c>
-      <c r="U10" s="143"/>
-      <c r="V10" s="143"/>
-      <c r="W10" s="143"/>
-      <c r="X10" s="143"/>
-      <c r="Y10" s="143"/>
-      <c r="Z10" s="143"/>
-      <c r="AA10" s="143"/>
-      <c r="AB10" s="143"/>
-      <c r="AC10" s="143"/>
-      <c r="AD10" s="143"/>
-      <c r="AE10" s="143"/>
-      <c r="AF10" s="143"/>
-      <c r="AG10" s="142" t="s">
+      <c r="U10" s="151"/>
+      <c r="V10" s="151"/>
+      <c r="W10" s="151"/>
+      <c r="X10" s="151"/>
+      <c r="Y10" s="151"/>
+      <c r="Z10" s="151"/>
+      <c r="AA10" s="151"/>
+      <c r="AB10" s="151"/>
+      <c r="AC10" s="151"/>
+      <c r="AD10" s="151"/>
+      <c r="AE10" s="151"/>
+      <c r="AF10" s="151"/>
+      <c r="AG10" s="157" t="s">
         <v>325</v>
       </c>
-      <c r="AH10" s="142"/>
-      <c r="AI10" s="142"/>
-      <c r="AJ10" s="142"/>
-      <c r="AK10" s="142"/>
-      <c r="AL10" s="142"/>
-      <c r="AM10" s="142"/>
-      <c r="AN10" s="142"/>
-      <c r="AO10" s="142"/>
-      <c r="AP10" s="142"/>
-      <c r="AQ10" s="142"/>
-      <c r="AR10" s="142"/>
-      <c r="AS10" s="142"/>
-      <c r="AT10" s="142"/>
-      <c r="AU10" s="142"/>
-      <c r="AV10" s="143" t="s">
+      <c r="AH10" s="157"/>
+      <c r="AI10" s="157"/>
+      <c r="AJ10" s="157"/>
+      <c r="AK10" s="157"/>
+      <c r="AL10" s="157"/>
+      <c r="AM10" s="157"/>
+      <c r="AN10" s="157"/>
+      <c r="AO10" s="157"/>
+      <c r="AP10" s="157"/>
+      <c r="AQ10" s="157"/>
+      <c r="AR10" s="157"/>
+      <c r="AS10" s="157"/>
+      <c r="AT10" s="157"/>
+      <c r="AU10" s="157"/>
+      <c r="AV10" s="151" t="s">
         <v>326</v>
       </c>
-      <c r="AW10" s="143"/>
-      <c r="AX10" s="143"/>
-      <c r="AY10" s="143"/>
-      <c r="AZ10" s="143"/>
-      <c r="BA10" s="143"/>
-      <c r="BB10" s="143"/>
-      <c r="BC10" s="143"/>
-      <c r="BD10" s="143"/>
-      <c r="BE10" s="143"/>
-      <c r="BF10" s="143"/>
-      <c r="BG10" s="143"/>
-      <c r="BH10" s="143"/>
-      <c r="BI10" s="143"/>
-      <c r="BJ10" s="143"/>
-      <c r="BK10" s="143"/>
-      <c r="BL10" s="143"/>
-      <c r="BM10" s="148"/>
+      <c r="AW10" s="151"/>
+      <c r="AX10" s="151"/>
+      <c r="AY10" s="151"/>
+      <c r="AZ10" s="151"/>
+      <c r="BA10" s="151"/>
+      <c r="BB10" s="151"/>
+      <c r="BC10" s="151"/>
+      <c r="BD10" s="151"/>
+      <c r="BE10" s="151"/>
+      <c r="BF10" s="151"/>
+      <c r="BG10" s="151"/>
+      <c r="BH10" s="151"/>
+      <c r="BI10" s="151"/>
+      <c r="BJ10" s="151"/>
+      <c r="BK10" s="151"/>
+      <c r="BL10" s="151"/>
+      <c r="BM10" s="152"/>
     </row>
     <row r="11" spans="2:65" ht="15">
-      <c r="C11" s="147" t="s">
+      <c r="C11" s="159" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="142" t="s">
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="157" t="s">
         <v>327</v>
       </c>
-      <c r="H11" s="142"/>
-      <c r="I11" s="142"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="142"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="142"/>
-      <c r="N11" s="142"/>
-      <c r="O11" s="142"/>
-      <c r="P11" s="142"/>
-      <c r="Q11" s="142"/>
-      <c r="R11" s="142"/>
-      <c r="S11" s="142"/>
-      <c r="T11" s="143" t="s">
+      <c r="H11" s="157"/>
+      <c r="I11" s="157"/>
+      <c r="J11" s="157"/>
+      <c r="K11" s="157"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="157"/>
+      <c r="P11" s="157"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="151" t="s">
         <v>328</v>
       </c>
-      <c r="U11" s="143"/>
-      <c r="V11" s="143"/>
-      <c r="W11" s="143"/>
-      <c r="X11" s="143"/>
-      <c r="Y11" s="143"/>
-      <c r="Z11" s="143"/>
-      <c r="AA11" s="143"/>
-      <c r="AB11" s="143"/>
-      <c r="AC11" s="143"/>
-      <c r="AD11" s="143"/>
-      <c r="AE11" s="143"/>
-      <c r="AF11" s="143"/>
-      <c r="AG11" s="142" t="s">
+      <c r="U11" s="151"/>
+      <c r="V11" s="151"/>
+      <c r="W11" s="151"/>
+      <c r="X11" s="151"/>
+      <c r="Y11" s="151"/>
+      <c r="Z11" s="151"/>
+      <c r="AA11" s="151"/>
+      <c r="AB11" s="151"/>
+      <c r="AC11" s="151"/>
+      <c r="AD11" s="151"/>
+      <c r="AE11" s="151"/>
+      <c r="AF11" s="151"/>
+      <c r="AG11" s="157" t="s">
         <v>329</v>
       </c>
-      <c r="AH11" s="142"/>
-      <c r="AI11" s="142"/>
-      <c r="AJ11" s="142"/>
-      <c r="AK11" s="142"/>
-      <c r="AL11" s="142"/>
-      <c r="AM11" s="142"/>
-      <c r="AN11" s="142"/>
-      <c r="AO11" s="142"/>
-      <c r="AP11" s="142"/>
-      <c r="AQ11" s="142"/>
-      <c r="AR11" s="142"/>
-      <c r="AS11" s="142"/>
-      <c r="AT11" s="142"/>
-      <c r="AU11" s="142"/>
-      <c r="AV11" s="143" t="s">
+      <c r="AH11" s="157"/>
+      <c r="AI11" s="157"/>
+      <c r="AJ11" s="157"/>
+      <c r="AK11" s="157"/>
+      <c r="AL11" s="157"/>
+      <c r="AM11" s="157"/>
+      <c r="AN11" s="157"/>
+      <c r="AO11" s="157"/>
+      <c r="AP11" s="157"/>
+      <c r="AQ11" s="157"/>
+      <c r="AR11" s="157"/>
+      <c r="AS11" s="157"/>
+      <c r="AT11" s="157"/>
+      <c r="AU11" s="157"/>
+      <c r="AV11" s="151" t="s">
         <v>330</v>
       </c>
-      <c r="AW11" s="143"/>
-      <c r="AX11" s="143"/>
-      <c r="AY11" s="143"/>
-      <c r="AZ11" s="143"/>
-      <c r="BA11" s="143"/>
-      <c r="BB11" s="143"/>
-      <c r="BC11" s="143"/>
-      <c r="BD11" s="143"/>
-      <c r="BE11" s="143"/>
-      <c r="BF11" s="143"/>
-      <c r="BG11" s="143"/>
-      <c r="BH11" s="143"/>
-      <c r="BI11" s="143"/>
-      <c r="BJ11" s="143"/>
-      <c r="BK11" s="143"/>
-      <c r="BL11" s="143"/>
-      <c r="BM11" s="148"/>
+      <c r="AW11" s="151"/>
+      <c r="AX11" s="151"/>
+      <c r="AY11" s="151"/>
+      <c r="AZ11" s="151"/>
+      <c r="BA11" s="151"/>
+      <c r="BB11" s="151"/>
+      <c r="BC11" s="151"/>
+      <c r="BD11" s="151"/>
+      <c r="BE11" s="151"/>
+      <c r="BF11" s="151"/>
+      <c r="BG11" s="151"/>
+      <c r="BH11" s="151"/>
+      <c r="BI11" s="151"/>
+      <c r="BJ11" s="151"/>
+      <c r="BK11" s="151"/>
+      <c r="BL11" s="151"/>
+      <c r="BM11" s="152"/>
     </row>
     <row r="12" spans="2:65" ht="15">
-      <c r="C12" s="147" t="s">
+      <c r="C12" s="159" t="s">
         <v>331</v>
       </c>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="142" t="s">
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="157" t="s">
         <v>332</v>
       </c>
-      <c r="H12" s="142"/>
-      <c r="I12" s="142"/>
-      <c r="J12" s="142"/>
-      <c r="K12" s="142"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="142"/>
-      <c r="N12" s="142"/>
-      <c r="O12" s="142"/>
-      <c r="P12" s="142"/>
-      <c r="Q12" s="142"/>
-      <c r="R12" s="142"/>
-      <c r="S12" s="142"/>
-      <c r="T12" s="143" t="s">
+      <c r="H12" s="157"/>
+      <c r="I12" s="157"/>
+      <c r="J12" s="157"/>
+      <c r="K12" s="157"/>
+      <c r="L12" s="157"/>
+      <c r="M12" s="157"/>
+      <c r="N12" s="157"/>
+      <c r="O12" s="157"/>
+      <c r="P12" s="157"/>
+      <c r="Q12" s="157"/>
+      <c r="R12" s="157"/>
+      <c r="S12" s="157"/>
+      <c r="T12" s="151" t="s">
         <v>333</v>
       </c>
-      <c r="U12" s="143"/>
-      <c r="V12" s="143"/>
-      <c r="W12" s="143"/>
-      <c r="X12" s="143"/>
-      <c r="Y12" s="143"/>
-      <c r="Z12" s="143"/>
-      <c r="AA12" s="143"/>
-      <c r="AB12" s="143"/>
-      <c r="AC12" s="143"/>
-      <c r="AD12" s="143"/>
-      <c r="AE12" s="143"/>
-      <c r="AF12" s="143"/>
-      <c r="AG12" s="142" t="s">
+      <c r="U12" s="151"/>
+      <c r="V12" s="151"/>
+      <c r="W12" s="151"/>
+      <c r="X12" s="151"/>
+      <c r="Y12" s="151"/>
+      <c r="Z12" s="151"/>
+      <c r="AA12" s="151"/>
+      <c r="AB12" s="151"/>
+      <c r="AC12" s="151"/>
+      <c r="AD12" s="151"/>
+      <c r="AE12" s="151"/>
+      <c r="AF12" s="151"/>
+      <c r="AG12" s="157" t="s">
         <v>334</v>
       </c>
-      <c r="AH12" s="142"/>
-      <c r="AI12" s="142"/>
-      <c r="AJ12" s="142"/>
-      <c r="AK12" s="142"/>
-      <c r="AL12" s="142"/>
-      <c r="AM12" s="142"/>
-      <c r="AN12" s="142"/>
-      <c r="AO12" s="142"/>
-      <c r="AP12" s="142"/>
-      <c r="AQ12" s="142"/>
-      <c r="AR12" s="142"/>
-      <c r="AS12" s="142"/>
-      <c r="AT12" s="142"/>
-      <c r="AU12" s="142"/>
-      <c r="AV12" s="143" t="s">
+      <c r="AH12" s="157"/>
+      <c r="AI12" s="157"/>
+      <c r="AJ12" s="157"/>
+      <c r="AK12" s="157"/>
+      <c r="AL12" s="157"/>
+      <c r="AM12" s="157"/>
+      <c r="AN12" s="157"/>
+      <c r="AO12" s="157"/>
+      <c r="AP12" s="157"/>
+      <c r="AQ12" s="157"/>
+      <c r="AR12" s="157"/>
+      <c r="AS12" s="157"/>
+      <c r="AT12" s="157"/>
+      <c r="AU12" s="157"/>
+      <c r="AV12" s="151" t="s">
         <v>335</v>
       </c>
-      <c r="AW12" s="143"/>
-      <c r="AX12" s="143"/>
-      <c r="AY12" s="143"/>
-      <c r="AZ12" s="143"/>
-      <c r="BA12" s="143"/>
-      <c r="BB12" s="143"/>
-      <c r="BC12" s="143"/>
-      <c r="BD12" s="143"/>
-      <c r="BE12" s="143"/>
-      <c r="BF12" s="143"/>
-      <c r="BG12" s="143"/>
-      <c r="BH12" s="143"/>
-      <c r="BI12" s="143"/>
-      <c r="BJ12" s="143"/>
-      <c r="BK12" s="143"/>
-      <c r="BL12" s="143"/>
-      <c r="BM12" s="148"/>
+      <c r="AW12" s="151"/>
+      <c r="AX12" s="151"/>
+      <c r="AY12" s="151"/>
+      <c r="AZ12" s="151"/>
+      <c r="BA12" s="151"/>
+      <c r="BB12" s="151"/>
+      <c r="BC12" s="151"/>
+      <c r="BD12" s="151"/>
+      <c r="BE12" s="151"/>
+      <c r="BF12" s="151"/>
+      <c r="BG12" s="151"/>
+      <c r="BH12" s="151"/>
+      <c r="BI12" s="151"/>
+      <c r="BJ12" s="151"/>
+      <c r="BK12" s="151"/>
+      <c r="BL12" s="151"/>
+      <c r="BM12" s="152"/>
     </row>
     <row r="13" spans="2:65" ht="15">
-      <c r="C13" s="147" t="s">
+      <c r="C13" s="159" t="s">
         <v>336</v>
       </c>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="141"/>
-      <c r="G13" s="142" t="s">
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="160"/>
+      <c r="G13" s="157" t="s">
         <v>337</v>
       </c>
-      <c r="H13" s="142"/>
-      <c r="I13" s="142"/>
-      <c r="J13" s="142"/>
-      <c r="K13" s="142"/>
-      <c r="L13" s="142"/>
-      <c r="M13" s="142"/>
-      <c r="N13" s="142"/>
-      <c r="O13" s="142"/>
-      <c r="P13" s="142"/>
-      <c r="Q13" s="142"/>
-      <c r="R13" s="142"/>
-      <c r="S13" s="142"/>
-      <c r="T13" s="143" t="s">
+      <c r="H13" s="157"/>
+      <c r="I13" s="157"/>
+      <c r="J13" s="157"/>
+      <c r="K13" s="157"/>
+      <c r="L13" s="157"/>
+      <c r="M13" s="157"/>
+      <c r="N13" s="157"/>
+      <c r="O13" s="157"/>
+      <c r="P13" s="157"/>
+      <c r="Q13" s="157"/>
+      <c r="R13" s="157"/>
+      <c r="S13" s="157"/>
+      <c r="T13" s="151" t="s">
         <v>338</v>
       </c>
-      <c r="U13" s="143"/>
-      <c r="V13" s="143"/>
-      <c r="W13" s="143"/>
-      <c r="X13" s="143"/>
-      <c r="Y13" s="143"/>
-      <c r="Z13" s="143"/>
-      <c r="AA13" s="143"/>
-      <c r="AB13" s="143"/>
-      <c r="AC13" s="143"/>
-      <c r="AD13" s="143"/>
-      <c r="AE13" s="143"/>
-      <c r="AF13" s="143"/>
-      <c r="AG13" s="142" t="s">
+      <c r="U13" s="151"/>
+      <c r="V13" s="151"/>
+      <c r="W13" s="151"/>
+      <c r="X13" s="151"/>
+      <c r="Y13" s="151"/>
+      <c r="Z13" s="151"/>
+      <c r="AA13" s="151"/>
+      <c r="AB13" s="151"/>
+      <c r="AC13" s="151"/>
+      <c r="AD13" s="151"/>
+      <c r="AE13" s="151"/>
+      <c r="AF13" s="151"/>
+      <c r="AG13" s="157" t="s">
         <v>339</v>
       </c>
-      <c r="AH13" s="142"/>
-      <c r="AI13" s="142"/>
-      <c r="AJ13" s="142"/>
-      <c r="AK13" s="142"/>
-      <c r="AL13" s="142"/>
-      <c r="AM13" s="142"/>
-      <c r="AN13" s="142"/>
-      <c r="AO13" s="142"/>
-      <c r="AP13" s="142"/>
-      <c r="AQ13" s="142"/>
-      <c r="AR13" s="142"/>
-      <c r="AS13" s="142"/>
-      <c r="AT13" s="142"/>
-      <c r="AU13" s="142"/>
-      <c r="AV13" s="143" t="s">
+      <c r="AH13" s="157"/>
+      <c r="AI13" s="157"/>
+      <c r="AJ13" s="157"/>
+      <c r="AK13" s="157"/>
+      <c r="AL13" s="157"/>
+      <c r="AM13" s="157"/>
+      <c r="AN13" s="157"/>
+      <c r="AO13" s="157"/>
+      <c r="AP13" s="157"/>
+      <c r="AQ13" s="157"/>
+      <c r="AR13" s="157"/>
+      <c r="AS13" s="157"/>
+      <c r="AT13" s="157"/>
+      <c r="AU13" s="157"/>
+      <c r="AV13" s="151" t="s">
         <v>340</v>
       </c>
-      <c r="AW13" s="143"/>
-      <c r="AX13" s="143"/>
-      <c r="AY13" s="143"/>
-      <c r="AZ13" s="143"/>
-      <c r="BA13" s="143"/>
-      <c r="BB13" s="143"/>
-      <c r="BC13" s="143"/>
-      <c r="BD13" s="143"/>
-      <c r="BE13" s="143"/>
-      <c r="BF13" s="143"/>
-      <c r="BG13" s="143"/>
-      <c r="BH13" s="143"/>
-      <c r="BI13" s="143"/>
-      <c r="BJ13" s="143"/>
-      <c r="BK13" s="143"/>
-      <c r="BL13" s="143"/>
-      <c r="BM13" s="148"/>
+      <c r="AW13" s="151"/>
+      <c r="AX13" s="151"/>
+      <c r="AY13" s="151"/>
+      <c r="AZ13" s="151"/>
+      <c r="BA13" s="151"/>
+      <c r="BB13" s="151"/>
+      <c r="BC13" s="151"/>
+      <c r="BD13" s="151"/>
+      <c r="BE13" s="151"/>
+      <c r="BF13" s="151"/>
+      <c r="BG13" s="151"/>
+      <c r="BH13" s="151"/>
+      <c r="BI13" s="151"/>
+      <c r="BJ13" s="151"/>
+      <c r="BK13" s="151"/>
+      <c r="BL13" s="151"/>
+      <c r="BM13" s="152"/>
     </row>
     <row r="14" spans="2:65" ht="15">
-      <c r="C14" s="147" t="s">
+      <c r="C14" s="159" t="s">
         <v>341</v>
       </c>
-      <c r="D14" s="141"/>
-      <c r="E14" s="141"/>
-      <c r="F14" s="141"/>
-      <c r="G14" s="142" t="s">
+      <c r="D14" s="160"/>
+      <c r="E14" s="160"/>
+      <c r="F14" s="160"/>
+      <c r="G14" s="157" t="s">
         <v>342</v>
       </c>
-      <c r="H14" s="142"/>
-      <c r="I14" s="142"/>
-      <c r="J14" s="142"/>
-      <c r="K14" s="142"/>
-      <c r="L14" s="142"/>
-      <c r="M14" s="142"/>
-      <c r="N14" s="142"/>
-      <c r="O14" s="142"/>
-      <c r="P14" s="142"/>
-      <c r="Q14" s="142"/>
-      <c r="R14" s="142"/>
-      <c r="S14" s="142"/>
-      <c r="T14" s="143" t="s">
+      <c r="H14" s="157"/>
+      <c r="I14" s="157"/>
+      <c r="J14" s="157"/>
+      <c r="K14" s="157"/>
+      <c r="L14" s="157"/>
+      <c r="M14" s="157"/>
+      <c r="N14" s="157"/>
+      <c r="O14" s="157"/>
+      <c r="P14" s="157"/>
+      <c r="Q14" s="157"/>
+      <c r="R14" s="157"/>
+      <c r="S14" s="157"/>
+      <c r="T14" s="151" t="s">
         <v>343</v>
       </c>
-      <c r="U14" s="143"/>
-      <c r="V14" s="143"/>
-      <c r="W14" s="143"/>
-      <c r="X14" s="143"/>
-      <c r="Y14" s="143"/>
-      <c r="Z14" s="143"/>
-      <c r="AA14" s="143"/>
-      <c r="AB14" s="143"/>
-      <c r="AC14" s="143"/>
-      <c r="AD14" s="143"/>
-      <c r="AE14" s="143"/>
-      <c r="AF14" s="143"/>
-      <c r="AG14" s="142" t="s">
+      <c r="U14" s="151"/>
+      <c r="V14" s="151"/>
+      <c r="W14" s="151"/>
+      <c r="X14" s="151"/>
+      <c r="Y14" s="151"/>
+      <c r="Z14" s="151"/>
+      <c r="AA14" s="151"/>
+      <c r="AB14" s="151"/>
+      <c r="AC14" s="151"/>
+      <c r="AD14" s="151"/>
+      <c r="AE14" s="151"/>
+      <c r="AF14" s="151"/>
+      <c r="AG14" s="157" t="s">
         <v>344</v>
       </c>
-      <c r="AH14" s="142"/>
-      <c r="AI14" s="142"/>
-      <c r="AJ14" s="142"/>
-      <c r="AK14" s="142"/>
-      <c r="AL14" s="142"/>
-      <c r="AM14" s="142"/>
-      <c r="AN14" s="142"/>
-      <c r="AO14" s="142"/>
-      <c r="AP14" s="142"/>
-      <c r="AQ14" s="142"/>
-      <c r="AR14" s="142"/>
-      <c r="AS14" s="142"/>
-      <c r="AT14" s="142"/>
-      <c r="AU14" s="142"/>
-      <c r="AV14" s="143" t="s">
+      <c r="AH14" s="157"/>
+      <c r="AI14" s="157"/>
+      <c r="AJ14" s="157"/>
+      <c r="AK14" s="157"/>
+      <c r="AL14" s="157"/>
+      <c r="AM14" s="157"/>
+      <c r="AN14" s="157"/>
+      <c r="AO14" s="157"/>
+      <c r="AP14" s="157"/>
+      <c r="AQ14" s="157"/>
+      <c r="AR14" s="157"/>
+      <c r="AS14" s="157"/>
+      <c r="AT14" s="157"/>
+      <c r="AU14" s="157"/>
+      <c r="AV14" s="151" t="s">
         <v>345</v>
       </c>
-      <c r="AW14" s="143"/>
-      <c r="AX14" s="143"/>
-      <c r="AY14" s="143"/>
-      <c r="AZ14" s="143"/>
-      <c r="BA14" s="143"/>
-      <c r="BB14" s="143"/>
-      <c r="BC14" s="143"/>
-      <c r="BD14" s="143"/>
-      <c r="BE14" s="143"/>
-      <c r="BF14" s="143"/>
-      <c r="BG14" s="143"/>
-      <c r="BH14" s="143"/>
-      <c r="BI14" s="143"/>
-      <c r="BJ14" s="143"/>
-      <c r="BK14" s="143"/>
-      <c r="BL14" s="143"/>
-      <c r="BM14" s="148"/>
+      <c r="AW14" s="151"/>
+      <c r="AX14" s="151"/>
+      <c r="AY14" s="151"/>
+      <c r="AZ14" s="151"/>
+      <c r="BA14" s="151"/>
+      <c r="BB14" s="151"/>
+      <c r="BC14" s="151"/>
+      <c r="BD14" s="151"/>
+      <c r="BE14" s="151"/>
+      <c r="BF14" s="151"/>
+      <c r="BG14" s="151"/>
+      <c r="BH14" s="151"/>
+      <c r="BI14" s="151"/>
+      <c r="BJ14" s="151"/>
+      <c r="BK14" s="151"/>
+      <c r="BL14" s="151"/>
+      <c r="BM14" s="152"/>
     </row>
     <row r="15" spans="2:65" ht="15">
-      <c r="C15" s="147" t="s">
+      <c r="C15" s="159" t="s">
         <v>346</v>
       </c>
-      <c r="D15" s="141"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="141"/>
-      <c r="G15" s="142" t="s">
+      <c r="D15" s="160"/>
+      <c r="E15" s="160"/>
+      <c r="F15" s="160"/>
+      <c r="G15" s="157" t="s">
         <v>347</v>
       </c>
-      <c r="H15" s="142"/>
-      <c r="I15" s="142"/>
-      <c r="J15" s="142"/>
-      <c r="K15" s="142"/>
-      <c r="L15" s="142"/>
-      <c r="M15" s="142"/>
-      <c r="N15" s="142"/>
-      <c r="O15" s="142"/>
-      <c r="P15" s="142"/>
-      <c r="Q15" s="142"/>
-      <c r="R15" s="142"/>
-      <c r="S15" s="142"/>
-      <c r="T15" s="143" t="s">
+      <c r="H15" s="157"/>
+      <c r="I15" s="157"/>
+      <c r="J15" s="157"/>
+      <c r="K15" s="157"/>
+      <c r="L15" s="157"/>
+      <c r="M15" s="157"/>
+      <c r="N15" s="157"/>
+      <c r="O15" s="157"/>
+      <c r="P15" s="157"/>
+      <c r="Q15" s="157"/>
+      <c r="R15" s="157"/>
+      <c r="S15" s="157"/>
+      <c r="T15" s="151" t="s">
         <v>348</v>
       </c>
-      <c r="U15" s="143"/>
-      <c r="V15" s="143"/>
-      <c r="W15" s="143"/>
-      <c r="X15" s="143"/>
-      <c r="Y15" s="143"/>
-      <c r="Z15" s="143"/>
-      <c r="AA15" s="143"/>
-      <c r="AB15" s="143"/>
-      <c r="AC15" s="143"/>
-      <c r="AD15" s="143"/>
-      <c r="AE15" s="143"/>
-      <c r="AF15" s="143"/>
-      <c r="AG15" s="142" t="s">
+      <c r="U15" s="151"/>
+      <c r="V15" s="151"/>
+      <c r="W15" s="151"/>
+      <c r="X15" s="151"/>
+      <c r="Y15" s="151"/>
+      <c r="Z15" s="151"/>
+      <c r="AA15" s="151"/>
+      <c r="AB15" s="151"/>
+      <c r="AC15" s="151"/>
+      <c r="AD15" s="151"/>
+      <c r="AE15" s="151"/>
+      <c r="AF15" s="151"/>
+      <c r="AG15" s="157" t="s">
         <v>349</v>
       </c>
-      <c r="AH15" s="142"/>
-      <c r="AI15" s="142"/>
-      <c r="AJ15" s="142"/>
-      <c r="AK15" s="142"/>
-      <c r="AL15" s="142"/>
-      <c r="AM15" s="142"/>
-      <c r="AN15" s="142"/>
-      <c r="AO15" s="142"/>
-      <c r="AP15" s="142"/>
-      <c r="AQ15" s="142"/>
-      <c r="AR15" s="142"/>
-      <c r="AS15" s="142"/>
-      <c r="AT15" s="142"/>
-      <c r="AU15" s="142"/>
-      <c r="AV15" s="143" t="s">
+      <c r="AH15" s="157"/>
+      <c r="AI15" s="157"/>
+      <c r="AJ15" s="157"/>
+      <c r="AK15" s="157"/>
+      <c r="AL15" s="157"/>
+      <c r="AM15" s="157"/>
+      <c r="AN15" s="157"/>
+      <c r="AO15" s="157"/>
+      <c r="AP15" s="157"/>
+      <c r="AQ15" s="157"/>
+      <c r="AR15" s="157"/>
+      <c r="AS15" s="157"/>
+      <c r="AT15" s="157"/>
+      <c r="AU15" s="157"/>
+      <c r="AV15" s="151" t="s">
         <v>350</v>
       </c>
-      <c r="AW15" s="143"/>
-      <c r="AX15" s="143"/>
-      <c r="AY15" s="143"/>
-      <c r="AZ15" s="143"/>
-      <c r="BA15" s="143"/>
-      <c r="BB15" s="143"/>
-      <c r="BC15" s="143"/>
-      <c r="BD15" s="143"/>
-      <c r="BE15" s="143"/>
-      <c r="BF15" s="143"/>
-      <c r="BG15" s="143"/>
-      <c r="BH15" s="143"/>
-      <c r="BI15" s="143"/>
-      <c r="BJ15" s="143"/>
-      <c r="BK15" s="143"/>
-      <c r="BL15" s="143"/>
-      <c r="BM15" s="148"/>
+      <c r="AW15" s="151"/>
+      <c r="AX15" s="151"/>
+      <c r="AY15" s="151"/>
+      <c r="AZ15" s="151"/>
+      <c r="BA15" s="151"/>
+      <c r="BB15" s="151"/>
+      <c r="BC15" s="151"/>
+      <c r="BD15" s="151"/>
+      <c r="BE15" s="151"/>
+      <c r="BF15" s="151"/>
+      <c r="BG15" s="151"/>
+      <c r="BH15" s="151"/>
+      <c r="BI15" s="151"/>
+      <c r="BJ15" s="151"/>
+      <c r="BK15" s="151"/>
+      <c r="BL15" s="151"/>
+      <c r="BM15" s="152"/>
     </row>
     <row r="16" spans="2:65" ht="15.75" thickBot="1">
-      <c r="C16" s="149" t="s">
+      <c r="C16" s="161" t="s">
         <v>351</v>
       </c>
-      <c r="D16" s="150"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="151" t="s">
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="158" t="s">
         <v>352</v>
       </c>
-      <c r="H16" s="151"/>
-      <c r="I16" s="151"/>
-      <c r="J16" s="151"/>
-      <c r="K16" s="151"/>
-      <c r="L16" s="151"/>
-      <c r="M16" s="151"/>
-      <c r="N16" s="151"/>
-      <c r="O16" s="151"/>
-      <c r="P16" s="151"/>
-      <c r="Q16" s="151"/>
-      <c r="R16" s="151"/>
-      <c r="S16" s="151"/>
-      <c r="T16" s="152" t="s">
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="158"/>
+      <c r="K16" s="158"/>
+      <c r="L16" s="158"/>
+      <c r="M16" s="158"/>
+      <c r="N16" s="158"/>
+      <c r="O16" s="158"/>
+      <c r="P16" s="158"/>
+      <c r="Q16" s="158"/>
+      <c r="R16" s="158"/>
+      <c r="S16" s="158"/>
+      <c r="T16" s="153" t="s">
         <v>353</v>
       </c>
-      <c r="U16" s="152"/>
-      <c r="V16" s="152"/>
-      <c r="W16" s="152"/>
-      <c r="X16" s="152"/>
-      <c r="Y16" s="152"/>
-      <c r="Z16" s="152"/>
-      <c r="AA16" s="152"/>
-      <c r="AB16" s="152"/>
-      <c r="AC16" s="152"/>
-      <c r="AD16" s="152"/>
-      <c r="AE16" s="152"/>
-      <c r="AF16" s="152"/>
-      <c r="AG16" s="151" t="s">
+      <c r="U16" s="153"/>
+      <c r="V16" s="153"/>
+      <c r="W16" s="153"/>
+      <c r="X16" s="153"/>
+      <c r="Y16" s="153"/>
+      <c r="Z16" s="153"/>
+      <c r="AA16" s="153"/>
+      <c r="AB16" s="153"/>
+      <c r="AC16" s="153"/>
+      <c r="AD16" s="153"/>
+      <c r="AE16" s="153"/>
+      <c r="AF16" s="153"/>
+      <c r="AG16" s="158" t="s">
         <v>354</v>
       </c>
-      <c r="AH16" s="151"/>
-      <c r="AI16" s="151"/>
-      <c r="AJ16" s="151"/>
-      <c r="AK16" s="151"/>
-      <c r="AL16" s="151"/>
-      <c r="AM16" s="151"/>
-      <c r="AN16" s="151"/>
-      <c r="AO16" s="151"/>
-      <c r="AP16" s="151"/>
-      <c r="AQ16" s="151"/>
-      <c r="AR16" s="151"/>
-      <c r="AS16" s="151"/>
-      <c r="AT16" s="151"/>
-      <c r="AU16" s="151"/>
-      <c r="AV16" s="152" t="s">
+      <c r="AH16" s="158"/>
+      <c r="AI16" s="158"/>
+      <c r="AJ16" s="158"/>
+      <c r="AK16" s="158"/>
+      <c r="AL16" s="158"/>
+      <c r="AM16" s="158"/>
+      <c r="AN16" s="158"/>
+      <c r="AO16" s="158"/>
+      <c r="AP16" s="158"/>
+      <c r="AQ16" s="158"/>
+      <c r="AR16" s="158"/>
+      <c r="AS16" s="158"/>
+      <c r="AT16" s="158"/>
+      <c r="AU16" s="158"/>
+      <c r="AV16" s="153" t="s">
         <v>355</v>
       </c>
-      <c r="AW16" s="152"/>
-      <c r="AX16" s="152"/>
-      <c r="AY16" s="152"/>
-      <c r="AZ16" s="152"/>
-      <c r="BA16" s="152"/>
-      <c r="BB16" s="152"/>
-      <c r="BC16" s="152"/>
-      <c r="BD16" s="152"/>
-      <c r="BE16" s="152"/>
-      <c r="BF16" s="152"/>
-      <c r="BG16" s="152"/>
-      <c r="BH16" s="152"/>
-      <c r="BI16" s="152"/>
-      <c r="BJ16" s="152"/>
-      <c r="BK16" s="152"/>
-      <c r="BL16" s="152"/>
-      <c r="BM16" s="153"/>
+      <c r="AW16" s="153"/>
+      <c r="AX16" s="153"/>
+      <c r="AY16" s="153"/>
+      <c r="AZ16" s="153"/>
+      <c r="BA16" s="153"/>
+      <c r="BB16" s="153"/>
+      <c r="BC16" s="153"/>
+      <c r="BD16" s="153"/>
+      <c r="BE16" s="153"/>
+      <c r="BF16" s="153"/>
+      <c r="BG16" s="153"/>
+      <c r="BH16" s="153"/>
+      <c r="BI16" s="153"/>
+      <c r="BJ16" s="153"/>
+      <c r="BK16" s="153"/>
+      <c r="BL16" s="153"/>
+      <c r="BM16" s="154"/>
     </row>
     <row r="19" spans="2:2" ht="17.25">
       <c r="B19" s="76" t="s">
@@ -12077,42 +10138,22 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="AV11:BM11"/>
-    <mergeCell ref="AV12:BM12"/>
-    <mergeCell ref="AV13:BM13"/>
-    <mergeCell ref="AV14:BM14"/>
-    <mergeCell ref="AV15:BM15"/>
-    <mergeCell ref="AV16:BM16"/>
-    <mergeCell ref="AV5:BM5"/>
-    <mergeCell ref="AV6:BM6"/>
-    <mergeCell ref="AV7:BM7"/>
-    <mergeCell ref="AV8:BM8"/>
-    <mergeCell ref="AV9:BM9"/>
-    <mergeCell ref="AV10:BM10"/>
-    <mergeCell ref="AG9:AU9"/>
-    <mergeCell ref="AG10:AU10"/>
-    <mergeCell ref="AG11:AU11"/>
-    <mergeCell ref="AG12:AU12"/>
-    <mergeCell ref="AG13:AU13"/>
-    <mergeCell ref="AG14:AU14"/>
-    <mergeCell ref="AG15:AU15"/>
-    <mergeCell ref="AG16:AU16"/>
-    <mergeCell ref="AG5:AU5"/>
-    <mergeCell ref="AG6:AU6"/>
-    <mergeCell ref="AG7:AU7"/>
-    <mergeCell ref="AG8:AU8"/>
-    <mergeCell ref="T11:AF11"/>
-    <mergeCell ref="T12:AF12"/>
-    <mergeCell ref="T13:AF13"/>
-    <mergeCell ref="T14:AF14"/>
-    <mergeCell ref="T15:AF15"/>
-    <mergeCell ref="T16:AF16"/>
-    <mergeCell ref="T5:AF5"/>
-    <mergeCell ref="T6:AF6"/>
-    <mergeCell ref="T7:AF7"/>
-    <mergeCell ref="T8:AF8"/>
-    <mergeCell ref="T9:AF9"/>
-    <mergeCell ref="T10:AF10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="G5:S5"/>
+    <mergeCell ref="G6:S6"/>
+    <mergeCell ref="G7:S7"/>
+    <mergeCell ref="G8:S8"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="G15:S15"/>
     <mergeCell ref="G16:S16"/>
     <mergeCell ref="G9:S9"/>
@@ -12121,22 +10162,42 @@
     <mergeCell ref="G12:S12"/>
     <mergeCell ref="G13:S13"/>
     <mergeCell ref="G14:S14"/>
-    <mergeCell ref="G5:S5"/>
-    <mergeCell ref="G6:S6"/>
-    <mergeCell ref="G7:S7"/>
-    <mergeCell ref="G8:S8"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="T16:AF16"/>
+    <mergeCell ref="T5:AF5"/>
+    <mergeCell ref="T6:AF6"/>
+    <mergeCell ref="T7:AF7"/>
+    <mergeCell ref="T8:AF8"/>
+    <mergeCell ref="T9:AF9"/>
+    <mergeCell ref="T10:AF10"/>
+    <mergeCell ref="T11:AF11"/>
+    <mergeCell ref="T12:AF12"/>
+    <mergeCell ref="T13:AF13"/>
+    <mergeCell ref="T14:AF14"/>
+    <mergeCell ref="T15:AF15"/>
+    <mergeCell ref="AG14:AU14"/>
+    <mergeCell ref="AG15:AU15"/>
+    <mergeCell ref="AG16:AU16"/>
+    <mergeCell ref="AG5:AU5"/>
+    <mergeCell ref="AG6:AU6"/>
+    <mergeCell ref="AG7:AU7"/>
+    <mergeCell ref="AG8:AU8"/>
+    <mergeCell ref="AG9:AU9"/>
+    <mergeCell ref="AG10:AU10"/>
+    <mergeCell ref="AG11:AU11"/>
+    <mergeCell ref="AG12:AU12"/>
+    <mergeCell ref="AG13:AU13"/>
+    <mergeCell ref="AV16:BM16"/>
+    <mergeCell ref="AV5:BM5"/>
+    <mergeCell ref="AV6:BM6"/>
+    <mergeCell ref="AV7:BM7"/>
+    <mergeCell ref="AV8:BM8"/>
+    <mergeCell ref="AV9:BM9"/>
+    <mergeCell ref="AV10:BM10"/>
+    <mergeCell ref="AV11:BM11"/>
+    <mergeCell ref="AV12:BM12"/>
+    <mergeCell ref="AV13:BM13"/>
+    <mergeCell ref="AV14:BM14"/>
+    <mergeCell ref="AV15:BM15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12144,7 +10205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5C6D57-9A86-4D22-90DF-F0D5383CEF40}">
-  <dimension ref="A1:BL172"/>
+  <dimension ref="A1:BL170"/>
   <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="13.9" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:63" ht="13.9" customHeight="1" thickBot="1">
@@ -12926,21 +10987,11 @@
       <c r="P38" s="92"/>
       <c r="Q38" s="93"/>
     </row>
-    <row r="39" spans="2:64" ht="13.9" customHeight="1">
-      <c r="BL39" t="s">
-        <v>417</v>
-      </c>
-    </row>
     <row r="40" spans="2:64" ht="13.9" customHeight="1">
       <c r="C40" s="73"/>
     </row>
     <row r="41" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B41" t="s">
-        <v>362</v>
-      </c>
-      <c r="BL41" s="76" t="s">
-        <v>418</v>
-      </c>
+      <c r="BL41" s="76"/>
     </row>
     <row r="42" spans="2:64" ht="13.9" customHeight="1">
       <c r="C42" s="78"/>
@@ -12950,9 +11001,7 @@
     <row r="43" spans="2:64" ht="13.9" customHeight="1">
       <c r="C43" s="79"/>
       <c r="D43" s="79"/>
-      <c r="BL43" s="74" t="s">
-        <v>419</v>
-      </c>
+      <c r="BL43" s="74"/>
     </row>
     <row r="44" spans="2:64" ht="13.9" customHeight="1">
       <c r="C44" s="79"/>
@@ -12960,14 +11009,10 @@
       <c r="BL44" s="74"/>
     </row>
     <row r="45" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B45" s="73" t="s">
-        <v>363</v>
-      </c>
+      <c r="B45" s="73"/>
       <c r="C45" s="79"/>
       <c r="D45" s="79"/>
-      <c r="BL45" s="74" t="s">
-        <v>420</v>
-      </c>
+      <c r="BL45" s="74"/>
     </row>
     <row r="46" spans="2:64" ht="13.9" customHeight="1">
       <c r="C46" s="79"/>
@@ -12975,45 +11020,28 @@
       <c r="BL46" s="74"/>
     </row>
     <row r="47" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B47" t="s">
-        <v>364</v>
-      </c>
       <c r="C47" s="79"/>
       <c r="D47" s="79"/>
-      <c r="BL47" s="74" t="s">
-        <v>421</v>
-      </c>
+      <c r="BL47" s="74"/>
     </row>
     <row r="51" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B51" s="76" t="s">
-        <v>365</v>
-      </c>
-      <c r="BL51" s="73" t="s">
-        <v>422</v>
-      </c>
+      <c r="B51" s="76"/>
+      <c r="BL51" s="73"/>
     </row>
     <row r="52" spans="2:64" ht="13.9" customHeight="1">
       <c r="B52" s="74"/>
     </row>
     <row r="53" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B53" s="74" t="s">
-        <v>366</v>
-      </c>
-      <c r="BL53" s="76" t="s">
-        <v>423</v>
-      </c>
+      <c r="B53" s="74"/>
+      <c r="BL53" s="76"/>
     </row>
     <row r="54" spans="2:64" ht="13.9" customHeight="1">
       <c r="B54" s="74"/>
       <c r="BL54" s="74"/>
     </row>
     <row r="55" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B55" s="74" t="s">
-        <v>367</v>
-      </c>
-      <c r="BL55" s="163" t="s">
-        <v>424</v>
-      </c>
+      <c r="B55" s="74"/>
+      <c r="BL55" s="115"/>
     </row>
     <row r="56" spans="2:64" ht="13.9" customHeight="1">
       <c r="B56" s="74"/>
@@ -13021,147 +11049,99 @@
     </row>
     <row r="57" spans="2:64" ht="13.9" customHeight="1">
       <c r="B57" s="74"/>
-      <c r="BL57" s="163" t="s">
-        <v>425</v>
-      </c>
+      <c r="BL57" s="115"/>
     </row>
     <row r="58" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B58" s="160"/>
+      <c r="B58" s="112"/>
       <c r="BL58" s="74"/>
     </row>
     <row r="59" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B59" s="160" t="s">
-        <v>368</v>
-      </c>
-      <c r="BL59" s="163" t="s">
-        <v>426</v>
-      </c>
+      <c r="B59" s="112"/>
+      <c r="BL59" s="115"/>
     </row>
     <row r="60" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B60" s="160"/>
-      <c r="BL60" s="74" t="s">
-        <v>427</v>
-      </c>
+      <c r="B60" s="112"/>
+      <c r="BL60" s="74"/>
     </row>
     <row r="61" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B61" s="160" t="s">
-        <v>369</v>
-      </c>
+      <c r="B61" s="112"/>
     </row>
     <row r="62" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B62" s="160"/>
+      <c r="B62" s="112"/>
     </row>
     <row r="63" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B63" s="160" t="s">
-        <v>370</v>
-      </c>
+      <c r="B63" s="112"/>
     </row>
     <row r="64" spans="2:64" ht="13.9" customHeight="1">
       <c r="B64" s="74"/>
-      <c r="BL64" s="76" t="s">
-        <v>428</v>
-      </c>
+      <c r="BL64" s="76"/>
     </row>
     <row r="65" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B65" s="74" t="s">
-        <v>371</v>
-      </c>
+      <c r="B65" s="74"/>
       <c r="BL65" s="74"/>
     </row>
     <row r="66" spans="2:64" ht="13.9" customHeight="1">
       <c r="B66" s="74"/>
-      <c r="BL66" s="163" t="s">
-        <v>429</v>
-      </c>
+      <c r="BL66" s="115"/>
     </row>
     <row r="67" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B67" s="82" t="s">
-        <v>372</v>
-      </c>
+      <c r="B67" s="82"/>
       <c r="BL67" s="74"/>
     </row>
     <row r="68" spans="2:64" ht="13.9" customHeight="1">
       <c r="B68" s="74"/>
-      <c r="BL68" s="163" t="s">
-        <v>430</v>
-      </c>
+      <c r="BL68" s="115"/>
     </row>
     <row r="69" spans="2:64" ht="13.9" customHeight="1">
       <c r="B69" s="74"/>
-      <c r="BL69" s="74" t="s">
-        <v>431</v>
-      </c>
+      <c r="BL69" s="74"/>
     </row>
     <row r="70" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B70" s="160"/>
+      <c r="B70" s="112"/>
     </row>
     <row r="71" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B71" s="160" t="s">
-        <v>373</v>
-      </c>
+      <c r="B71" s="112"/>
     </row>
     <row r="72" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B72" s="160"/>
+      <c r="B72" s="112"/>
     </row>
     <row r="73" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B73" s="160" t="s">
-        <v>374</v>
-      </c>
-      <c r="BL73" s="76" t="s">
-        <v>432</v>
-      </c>
+      <c r="B73" s="112"/>
+      <c r="BL73" s="76"/>
     </row>
     <row r="74" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B74" s="160"/>
+      <c r="B74" s="112"/>
       <c r="BL74" s="74"/>
     </row>
     <row r="75" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B75" s="160" t="s">
-        <v>375</v>
-      </c>
-      <c r="BL75" s="163" t="s">
-        <v>433</v>
-      </c>
+      <c r="B75" s="112"/>
+      <c r="BL75" s="115"/>
     </row>
     <row r="76" spans="2:64" ht="13.9" customHeight="1">
-      <c r="BL76" s="74" t="s">
-        <v>434</v>
-      </c>
+      <c r="BL76" s="74"/>
     </row>
     <row r="77" spans="2:64" ht="13.9" customHeight="1">
       <c r="BL77" s="74"/>
     </row>
     <row r="78" spans="2:64" ht="13.9" customHeight="1">
-      <c r="BL78" s="163" t="s">
-        <v>435</v>
-      </c>
+      <c r="BL78" s="115"/>
     </row>
     <row r="79" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B79" s="76" t="s">
-        <v>376</v>
-      </c>
-      <c r="BL79" s="74" t="s">
-        <v>436</v>
-      </c>
+      <c r="B79" s="76"/>
+      <c r="BL79" s="74"/>
     </row>
     <row r="80" spans="2:64" ht="13.9" customHeight="1">
       <c r="B80" s="74"/>
     </row>
     <row r="81" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B81" s="74" t="s">
-        <v>377</v>
-      </c>
+      <c r="B81" s="74"/>
     </row>
     <row r="82" spans="2:64" ht="13.9" customHeight="1">
       <c r="B82" s="74"/>
     </row>
     <row r="83" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B83" s="74" t="s">
-        <v>378</v>
-      </c>
-      <c r="BL83" s="76" t="s">
-        <v>437</v>
-      </c>
+      <c r="B83" s="74"/>
+      <c r="BL83" s="76"/>
     </row>
     <row r="84" spans="2:64" ht="13.9" customHeight="1">
       <c r="B84" s="74"/>
@@ -13169,236 +11149,158 @@
     </row>
     <row r="85" spans="2:64" ht="13.9" customHeight="1">
       <c r="B85" s="74"/>
-      <c r="BL85" s="163" t="s">
-        <v>438</v>
-      </c>
+      <c r="BL85" s="115"/>
     </row>
     <row r="86" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B86" s="160"/>
+      <c r="B86" s="112"/>
       <c r="BL86" s="74"/>
     </row>
     <row r="87" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B87" s="160" t="s">
-        <v>379</v>
-      </c>
-      <c r="BL87" s="163" t="s">
-        <v>439</v>
-      </c>
+      <c r="B87" s="112"/>
+      <c r="BL87" s="115"/>
     </row>
     <row r="88" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B88" s="160"/>
+      <c r="B88" s="112"/>
     </row>
     <row r="89" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B89" s="160" t="s">
-        <v>380</v>
-      </c>
+      <c r="B89" s="112"/>
     </row>
     <row r="90" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B90" s="160"/>
+      <c r="B90" s="112"/>
     </row>
     <row r="91" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B91" s="160" t="s">
-        <v>381</v>
-      </c>
-      <c r="BL91" s="76" t="s">
-        <v>440</v>
-      </c>
+      <c r="B91" s="112"/>
+      <c r="BL91" s="76"/>
     </row>
     <row r="92" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B92" s="160"/>
+      <c r="B92" s="112"/>
       <c r="BL92" s="74"/>
     </row>
     <row r="93" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B93" s="161" t="s">
-        <v>382</v>
-      </c>
-      <c r="BL93" s="163" t="s">
-        <v>441</v>
-      </c>
+      <c r="B93" s="113"/>
+      <c r="BL93" s="115"/>
     </row>
     <row r="94" spans="2:64" ht="13.9" customHeight="1">
-      <c r="BL94" s="74" t="s">
-        <v>442</v>
-      </c>
+      <c r="BL94" s="74"/>
     </row>
     <row r="95" spans="2:64" ht="13.9" customHeight="1">
-      <c r="BL95" s="74" t="s">
-        <v>443</v>
-      </c>
+      <c r="BL95" s="74"/>
     </row>
     <row r="97" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B97" s="76" t="s">
-        <v>383</v>
-      </c>
+      <c r="B97" s="76"/>
     </row>
     <row r="98" spans="2:64" ht="13.9" customHeight="1">
       <c r="B98" s="74"/>
     </row>
     <row r="99" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B99" s="74" t="s">
-        <v>384</v>
-      </c>
-      <c r="BL99" s="76" t="s">
-        <v>444</v>
-      </c>
+      <c r="B99" s="74"/>
+      <c r="BL99" s="76"/>
     </row>
     <row r="100" spans="2:64" ht="13.9" customHeight="1">
       <c r="B100" s="74"/>
       <c r="BL100" s="74"/>
     </row>
     <row r="101" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B101" s="74" t="s">
-        <v>385</v>
-      </c>
-      <c r="BL101" s="163" t="s">
-        <v>445</v>
-      </c>
+      <c r="B101" s="74"/>
+      <c r="BL101" s="115"/>
     </row>
     <row r="102" spans="2:64" ht="13.9" customHeight="1">
       <c r="B102" s="74"/>
-      <c r="BL102" s="74" t="s">
-        <v>446</v>
-      </c>
+      <c r="BL102" s="74"/>
     </row>
     <row r="103" spans="2:64" ht="13.9" customHeight="1">
       <c r="B103" s="74"/>
-      <c r="BL103" s="74" t="s">
-        <v>447</v>
-      </c>
+      <c r="BL103" s="74"/>
     </row>
     <row r="104" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B104" s="160"/>
+      <c r="B104" s="112"/>
     </row>
     <row r="105" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B105" s="160" t="s">
-        <v>386</v>
-      </c>
+      <c r="B105" s="112"/>
     </row>
     <row r="106" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B106" s="160"/>
+      <c r="B106" s="112"/>
     </row>
     <row r="107" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B107" s="160" t="s">
-        <v>387</v>
-      </c>
-      <c r="BL107" s="76" t="s">
-        <v>448</v>
-      </c>
+      <c r="B107" s="112"/>
+      <c r="BL107" s="76"/>
     </row>
     <row r="108" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B108" s="160"/>
+      <c r="B108" s="112"/>
       <c r="BL108" s="74"/>
     </row>
     <row r="109" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B109" s="160"/>
-      <c r="BL109" s="163" t="s">
-        <v>449</v>
-      </c>
+      <c r="B109" s="112"/>
+      <c r="BL109" s="115"/>
     </row>
     <row r="110" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B110" s="162"/>
+      <c r="B110" s="114"/>
       <c r="BL110" s="74"/>
     </row>
     <row r="111" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B111" s="162" t="s">
-        <v>388</v>
-      </c>
-      <c r="BL111" s="74" t="s">
-        <v>450</v>
-      </c>
+      <c r="B111" s="114"/>
+      <c r="BL111" s="74"/>
     </row>
     <row r="112" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B112" s="162"/>
+      <c r="B112" s="114"/>
     </row>
     <row r="113" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B113" s="162" t="s">
-        <v>389</v>
-      </c>
+      <c r="B113" s="114"/>
     </row>
     <row r="114" spans="2:64" ht="13.9" customHeight="1">
       <c r="B114" s="74"/>
     </row>
     <row r="115" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B115" s="82" t="s">
-        <v>372</v>
-      </c>
-      <c r="BL115" s="76" t="s">
-        <v>451</v>
-      </c>
+      <c r="B115" s="82"/>
+      <c r="BL115" s="76"/>
     </row>
     <row r="116" spans="2:64" ht="13.9" customHeight="1">
       <c r="B116" s="74"/>
     </row>
     <row r="117" spans="2:64" ht="13.9" customHeight="1">
       <c r="B117" s="74"/>
-      <c r="BL117" t="s">
-        <v>452</v>
-      </c>
     </row>
     <row r="118" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B118" s="160"/>
+      <c r="B118" s="112"/>
       <c r="BL118" s="74"/>
     </row>
     <row r="119" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B119" s="160" t="s">
-        <v>390</v>
-      </c>
-      <c r="BL119" s="163" t="s">
-        <v>453</v>
-      </c>
+      <c r="B119" s="112"/>
+      <c r="BL119" s="115"/>
     </row>
     <row r="120" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B120" s="160"/>
+      <c r="B120" s="112"/>
       <c r="BL120" s="74"/>
     </row>
     <row r="121" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B121" s="160" t="s">
-        <v>391</v>
-      </c>
-      <c r="BL121" s="163" t="s">
-        <v>454</v>
-      </c>
+      <c r="B121" s="112"/>
+      <c r="BL121" s="115"/>
     </row>
     <row r="122" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B122" s="160"/>
+      <c r="B122" s="112"/>
       <c r="BL122" s="74"/>
     </row>
     <row r="123" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B123" s="160" t="s">
-        <v>392</v>
-      </c>
-      <c r="BL123" s="163" t="s">
-        <v>455</v>
-      </c>
+      <c r="B123" s="112"/>
+      <c r="BL123" s="115"/>
     </row>
     <row r="124" spans="2:64" ht="13.9" customHeight="1">
-      <c r="BL124" s="74" t="s">
-        <v>456</v>
-      </c>
+      <c r="BL124" s="74"/>
     </row>
     <row r="127" spans="2:64" ht="13.9" customHeight="1">
-      <c r="B127" s="76" t="s">
-        <v>393</v>
-      </c>
+      <c r="B127" s="76"/>
     </row>
     <row r="128" spans="2:64" ht="13.9" customHeight="1">
       <c r="B128" s="74"/>
-      <c r="BL128" t="s">
-        <v>457</v>
-      </c>
     </row>
     <row r="129" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B129" s="74" t="s">
-        <v>394</v>
-      </c>
+      <c r="B129" s="74"/>
     </row>
     <row r="130" spans="2:2" ht="13.9" customHeight="1">
       <c r="B130" s="74"/>
     </row>
     <row r="131" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B131" s="74" t="s">
-        <v>395</v>
-      </c>
+      <c r="B131" s="74"/>
     </row>
     <row r="132" spans="2:2" ht="13.9" customHeight="1">
       <c r="B132" s="74"/>
@@ -13407,130 +11309,82 @@
       <c r="B133" s="74"/>
     </row>
     <row r="134" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B134" s="160"/>
+      <c r="B134" s="112"/>
     </row>
     <row r="135" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B135" s="161" t="s">
-        <v>396</v>
-      </c>
+      <c r="B135" s="113"/>
     </row>
     <row r="136" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B136" s="160"/>
+      <c r="B136" s="112"/>
     </row>
     <row r="137" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B137" s="161" t="s">
-        <v>397</v>
-      </c>
+      <c r="B137" s="113"/>
     </row>
     <row r="138" spans="2:2" ht="13.9" customHeight="1">
       <c r="B138" s="74"/>
     </row>
     <row r="139" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B139" s="74" t="s">
-        <v>398</v>
-      </c>
+      <c r="B139" s="74"/>
     </row>
     <row r="143" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B143" s="73" t="s">
-        <v>399</v>
-      </c>
+      <c r="B143" s="73"/>
     </row>
     <row r="145" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B145" s="75" t="s">
-        <v>400</v>
-      </c>
+      <c r="B145" s="75"/>
     </row>
     <row r="146" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B146" s="75" t="s">
-        <v>401</v>
-      </c>
+      <c r="B146" s="75"/>
     </row>
     <row r="147" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B147" s="75" t="s">
-        <v>402</v>
-      </c>
+      <c r="B147" s="75"/>
     </row>
     <row r="148" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B148" s="75" t="s">
-        <v>403</v>
-      </c>
+      <c r="B148" s="75"/>
     </row>
     <row r="149" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B149" s="75" t="s">
-        <v>404</v>
-      </c>
+      <c r="B149" s="75"/>
     </row>
     <row r="150" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B150" s="75" t="s">
-        <v>405</v>
-      </c>
+      <c r="B150" s="75"/>
     </row>
     <row r="151" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B151" s="75" t="s">
-        <v>406</v>
-      </c>
+      <c r="B151" s="75"/>
     </row>
     <row r="152" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B152" s="75" t="s">
-        <v>407</v>
-      </c>
+      <c r="B152" s="75"/>
     </row>
     <row r="153" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B153" s="75" t="s">
-        <v>408</v>
-      </c>
+      <c r="B153" s="75"/>
     </row>
     <row r="154" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B154" s="75" t="s">
-        <v>409</v>
-      </c>
+      <c r="B154" s="75"/>
     </row>
     <row r="158" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B158" s="73" t="s">
-        <v>410</v>
-      </c>
+      <c r="B158" s="73"/>
     </row>
     <row r="159" spans="2:2" ht="13.9" customHeight="1">
       <c r="B159" s="74"/>
     </row>
     <row r="160" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B160" s="74" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="164" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B164" t="s">
-        <v>412</v>
-      </c>
+      <c r="B160" s="74"/>
     </row>
     <row r="165" spans="2:2" ht="13.9" customHeight="1">
       <c r="B165" s="74"/>
     </row>
     <row r="166" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B166" s="74" t="s">
-        <v>413</v>
-      </c>
+      <c r="B166" s="74"/>
     </row>
     <row r="167" spans="2:2" ht="13.9" customHeight="1">
       <c r="B167" s="74"/>
     </row>
     <row r="168" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B168" s="74" t="s">
-        <v>414</v>
-      </c>
+      <c r="B168" s="74"/>
     </row>
     <row r="169" spans="2:2" ht="13.9" customHeight="1">
       <c r="B169" s="74"/>
     </row>
     <row r="170" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B170" s="74" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" ht="13.9" customHeight="1">
-      <c r="B172" t="s">
-        <v>416</v>
-      </c>
+      <c r="B170" s="74"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13562,18 +11416,24 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="3:5">
-      <c r="C5" s="74" t="s">
+    <row r="5" spans="3:5" ht="15">
+      <c r="C5" s="165" t="s">
         <v>224</v>
       </c>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
     </row>
     <row r="6" spans="3:5">
-      <c r="E6" s="75" t="s">
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="164" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="7" spans="3:5">
-      <c r="E7" s="75" t="s">
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="164" t="s">
         <v>226</v>
       </c>
     </row>
@@ -13643,7 +11503,7 @@
       </c>
     </row>
     <row r="22" spans="3:5" ht="17.25">
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="166" t="s">
         <v>240</v>
       </c>
     </row>
